--- a/data/Bang_Tham_Dinh_Du_Toan.xlsx
+++ b/data/Bang_Tham_Dinh_Du_Toan.xlsx
@@ -103,13 +103,13 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,25 +476,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P116"/>
+  <dimension ref="A1:M116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="42" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="38" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="38" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -524,72 +521,57 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Tên Vật Tư</t>
+          <t>Tên Quy Cách Kỹ Thuật</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>Thông Số Kỹ Thuật</t>
+          <t>ĐVT</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>HSX/XX (Trình)</t>
+          <t>Số Lượng</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>ĐVT</t>
+          <t>Đơn Giá Đề Nghị (Trình)</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>Số Lượng</t>
+          <t>Thành Tiền Đề Nghị</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>Đơn Giá Đề Nghị (Trình)</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>Thành Tiền Đề Nghị</t>
-        </is>
-      </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
           <t>ĐÁNH GIÁ CỦA TỔ THẨM ĐỊNH (TTĐ)</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Ý KIẾN PHẢN BIỆN CỦA PHÒNG KHVT</t>
         </is>
       </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Đơn Giá Thống Nhất</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Thành Tiền Thống Nhất</t>
+        </is>
+      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Đơn Giá Thống Nhất</t>
+          <t>Giá Trị Giảm</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Thành Tiền Thống Nhất</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>Giá Trị Giảm</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
           <t>Cơ Sở Thống Nhất</t>
-        </is>
-      </c>
-      <c r="P4" s="1" t="inlineStr">
-        <is>
-          <t>Ghi Chú</t>
         </is>
       </c>
     </row>
@@ -602,66 +584,67 @@
           <t>3.82.63.134.ENG.00.000</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Module đầu vào input IUX 760 MI</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Điện áp hoạt động: 17-28VDC
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Module đầu vào input IUX 760 MI - Điện áp hoạt động: 17-28VDC
 Partno: 908531
 Hãng sản xuất: Minimax</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Minimax/ Đức</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="E5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="F5" s="6" t="n">
         <v>13559000</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="G5" s="6" t="n">
         <v>54236000</v>
       </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
-• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 13.559.000 đ/Cái (DTL 19.8.2026. xlsx)
-• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 6.015.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 115/2023. Ttr 2562/KHVT) theo hóa đơn số 00000041. 42. 43. 44. 45. 46 ngày 30.08.2024 ngày 2024-10-31. SL: 117 Cái); Các đợt nhập khác: 17.670.000 đ
-• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [908531], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
-• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Module đầu vào input IUX 760 MI] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
-• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
-KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 6.015.000 đ/Cái.</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr"/>
-      <c r="L5" s="7" t="n">
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t># THUYẾT MINH THẨM ĐỊNH DỰ TOÁN
+## 1. TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
+Tổ Thẩm định đã thực hiện đánh giá toàn diện đối với vật tư **Module đầu vào input IUX 760 MI** (Điện áp hoạt động: 17-28VDC), Partno: 908531, sản xuất bởi **Minimax**, mã ERP: 3.82.63.134.ENG.00.000, số lượng 4 cái, đơn giá trình thẩm định là **13.559.000 đ/cái**. Qua tổng hợp kết quả từ 5 cơ sở thẩm định, phát hiện được sự chênh lệch đáng kể giữa mức giá hiện hành và xu hướng giá lịch sử của nhà máy.
+## 2. Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN
+### 2.1. Cơ sở 1 – Báo Giá Gốc
+Cơ sở này đã đối chiếu các báo giá thương mại và xác nhận đơn giá chào thấp nhất là **13.559.000 đ** từ DTL ngày 19/8/2026. Mức giá này trùng khớp hoàn toàn với đơn giá trình thẩm định của Tổ Thẩm định, cho thấy thị trường đang vận hành ở mức giá tối thiểu hợp lệ. Tuy nhiên, sự đồng nhất này không giải quyết được vấn đề so sánh với lịch sử giá mua sắm nội bộ.
+### 2.2. Cơ sở 2 – ERP Vĩnh Tân 4
+Qua truy xuất từ CSDL lịch sử mua sắm ERP Vĩnh Tân 4, Tổ Thẩm định phát hiện vật tư có 2 đợt mua sắm lịch sử. Đơn giá trung bình cho 4 cái là **11.842.500 đ/cái**, dao động từ **6.015.000 đ đến 17.670.000 đ**. Mức giá trình thẩm định **13.559.000 đ** nằm trong phạm vi dao động lịch sử nhưng cao hơn **+14.5%** so với đơn giá trung bình ERP. Điều này cho thấy vật tư đang được định giá cao hơn mức trung bình của lịch sử mua sắm nhà máy, đòi hỏi sự xem xét lại về tính hợp lý của giá cả.
+### 2.3. Cơ sở 3 – EVN IMIS
+Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, Tổ Thẩm định không tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS. Sự thiếu hụt dữ liệu này làm giảm khả năng đánh giá rủi ro liên quan đến nguồn cung hoặc lịch sử giá của vật tư.
+### 2.4. Cơ sở 4 – Mua Sắm Công e-GP
+Cơ sở này chưa cung cấp thông tin chi tiết nào liên quan đến giá hoặc lịch sử mua sắm vật tư. Do đó, không thể đưa ra bất kỳ kết luận xác thực nào về mặt chứng cứ bổ sung.
+### 2.5. Cơ sở 5 – Thương Mại Điện Tử
+Tương tự như cơ sở 4, Cơ sở 5 cũng không cung cấp dữ liệu hỗ trợ thêm cho việc đánh giá giá trị kỹ thuật và thương mại của vật tư.
+## 3. KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO
+### 3.1. Kết luận chung
+Từ việc tổng hợp 5 cơ sở thẩm định, Tổ Thẩm định kết luận rằng **mức giá trình thẩm định 13.559.000 đ/cái là cao hơn đáng kể so với giá trung bình lịch sử mua sắm ERP Vĩnh Tân 4 (11.842.500 đ/cái)**. Sự chênh lệch này đạt **+14.5%**, vượt quá biên độ an toàn thường được chấp nhận trong quản lý tài chính dự án.
+### 3.2. Đề xuất
+Tổ Thẩm định đề xuất Hội đồng Thẩm định và Ban Lãnh đạo Trình Lãnh đạo **đàm phán điều chỉnh đơn giá phê duyệt** về mức **6.015.000 đ/cái** (giá trung bình ERP) hoặc tối thiểu **12.000.000 đ/cái** (dưới mức hiện hành). Việc điều chỉnh giá sẽ giúp:
+- Tiết kiệm chi phí dự án tổng cộng **30.176.000 đ** (cho 4 cái vật tư);
+- Đảm bảo tính cạnh tranh trong chuỗi cung ứng;
+- Nghiên cứu lại quy trình mua sắm để đảm bảo tính hợp lý về giá trị kỹ thuật và thương mại.
+Tổ Thẩm định xin gửi gửi sự quan tâm của Ban Lãnh đạo và mong nhận được phản hồi kịp thời để tiến hành xử lý phê duyệt điều chỉnh giá.</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="6" t="n">
         <v>6015000</v>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="K5" s="6" t="n">
         <v>24060000</v>
       </c>
-      <c r="N5" s="7" t="n">
+      <c r="L5" s="6" t="n">
         <v>30176000</v>
       </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>Ý kiến Chuyên gia AI &amp; Báo giá thấp nhất DTL (Khối 1)</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>3.82.63.134.ENG.00.000 | Khắc phục tồn tại thiết bị | BBKT 23/2026/PXH-VT4. Vật tư không có trong KH SXKD 2026</t>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -674,64 +657,81 @@
           <t>3.34.40.024.ENG.00.000</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Nút nhấn khẩn cấp - Discovery manual call point, Part no: 58100-953</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Nút nhấn khẩn cấp, Part no: 58100-953, Nguồn cấp: 17 - 28VDC , IP67. NSX: Apollo</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Apollo/ Anh</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Nút nhấn khẩn cấp - Discovery manual call point, Part no: 58100-953 - Nút nhấn khẩn cấp, Part no: 58100-953, Nguồn cấp: 17 - 28VDC , IP67. NSX: Apollo</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="E6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="F6" s="6" t="n">
         <v>14208000</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="G6" s="6" t="n">
         <v>14208000</v>
       </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
-• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 14.208.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
-• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 7.000.000 đ/Cái (HĐ: Nhập kho vật tư (QĐ:161) theo hóa đơn số 0000221 ngày 26.03.2021 ngày 2021-04-14. SL: 1 Cái)
-• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [58100-953], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
-• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Nút nhấn khẩn cấp - Discovery manual call point, Part no: 58100-953] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
-• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
-KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 7.000.000 đ/Cái.</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr"/>
-      <c r="L6" s="7" t="n">
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t># THUYẾT MINH THẨM ĐỊNH ĐÁNH GIÁ SAU - VẬT TỔ: NÚT NHẤN KHẮN CẦN CẦN
+---
+## TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
+Trong quá trình thực hiện việc thẩm định đánh giá sau cho vật tư **Nút nhấn khẩn cấp - Part no: 58100-953**, Tổ Thẩm định đã tiến hành đối chiếu và phân tích chi tiết dựa trên 5 cơ sở chứng cứ được xác nhận. Vật tư này thuộc phân nhóm thiết bị công nghiệp chuyên dụng, mang tên thương hiệu/tiêu chuẩn [Chưa rõ Hãng - Tiêu chuẩn kỹ thuật công nghiệp tiêu chuẩn], được sử dụng trong hệ thống cấp nguồn điện của Nhà máy Nhiệt điện Vĩnh Tân 4 nhằm đảm bảo khả năng hoạt động trong các tình huống khẩn cấp.
+So sánh giá trị giữa các nguồn cung ứng, đơn giá chào bán thấp nhất được ghi nhận từ Cơ sở 2 (Lịch sử nhập kho ERP Vĩnh Tân 4) đạt **7.000.000 đ/Cái** (HĐ: Nhập kho vật tư QĐ:161 theo hóa đơn số 0000221 ngày 26.03.2021 ngày 2021-04-14, SL: 1 Cái). Tuy nhiên, đơn giá trình thẩm định hiện tại là **14.208.000 đ**, cao hơn so với giá tham chiếu thấp nhất trên **+103.0%** (mức chênh lệch vượt quá biên độ an toàn quy định).
+---
+## Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN
+### 1. Phân tích bản chất kỹ thuật thiết bị
+Vật tư Nút nhấn khẩn cấp (Part no: 58100-953) là linh kiện liên kết quan trọng trong hệ thống an toàn điện của Nhà máy Nhiệt điện Vĩnh Tân 4. Theo thông số kỹ thuật, thiết bị có nguồn cấp **17 - 28VDC**, khả năng chống nước theo tiêu chuẩn **IP67**. Đặc điểm kỹ thuật nổi bật bao gồm:
+- **Phân loại:** Thiết bị công nghiệp chuyên dụng
+- **Thương hiệu/tiêu chuẩn:** [Chưa rõ Hãng - Tiêu chuẩn kỹ thuật công nghiệp tiêu chuẩn]
+- **Mục đích sử dụng:** Nhấn khẩn cấp trong các tình huống sự cố điện, đảm bảo dừng hoạt động ngay lập tức khi phát sinh rủi ro
+### 2. Đánh giá tương quan giá trị kỹ thuật và thương mại
+| Nguồn chứng cứ | Thông tin liên quan | Đơn giá / Thông số |
+|----------------|---------------------|--------------------|
+| **Cơ sở 1 (Báo giá gốc)** | Đã đối chiếu các báo giá thương mại | 14.208.000 đ (đơn giá cao nhất) |
+| **Cơ sở 2 (ERP Vĩnh Tân 4)** | Lịch sử nhập kho ERP Vĩnh Tân 4 | 7.000.000 đ/Cái (HĐ: Nhập kho vật tư QĐ:161) |
+| **Cơ sở 3 (EVN IMIS)** | Tra cứu dữ liệu mua sắm từ CSDL EVN IMIS | Không tìm thấy dữ liệu tương đương |
+| **Cơ sở 4 (Mua Sắm Công e-GP)** | Chứng cứ mua sắm công nghệ | Không có dữ liệu cụ thể |
+| **Cơ sở 5 (Thương Mại Điện Tử)** | Chứng cứ thương mại | Không có dữ liệu cụ thể |
+**Nhận định:** So sánh giữa đơn giá trình thẩm định (14.208.000 đ) và giá tham chiếu thấp nhất hợp lệ (7.000.000 đ) cho thấy mức chênh lệch lên tới **+103.0%**. Mức tăng giá này vượt quá biên độ an toàn và không phù hợp với xu hướng giá thị trường, đặc biệt khi so sánh với giá nhập kho thực tế từ Cơ sở 2.
+### 3. Phân tích chi tiết theo từng cơ sở chứng cứ
+**Cơ sở 1 (Báo giá gốc):** Đã thực hiện đối chiếu các báo giá thương mại trên thị trường. Đơn giá chào thấp nhất được ghi nhận là **14.208.000 đ** từ các nhà cung cấp uy tín. Tuy nhiên, cần lưu ý rằng đây là giá thị trường chung, chưa phản ánh đầy đủ các yếu tố kỹ thuật cụ thể của mẫu vật tư này.
+**Cơ sở 2 (ERP Vĩnh Tân 4):** Lịch sử nhập kho cho thấy đơn vị đã nhập kho **7.000.000 đ/Cái** vào ngày 26/03/2021 (HĐ: Nhập kho vật tư QĐ:161). Con số này phản ánh mức giá thực tế đã được sử dụng trong nhà máy, thấp hơn đáng kể so với đơn giá trình thẩm định. Điều này cho thấy có sự chênh lệch lớn giữa giá tham chiếu và giá thực tế sử dụng.
+**Cơ sở 3 (EVN IMIS):** Thời gian tra cứu từ 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [58100-953] không tìm thấy dữ liệu mua sắm tương đương. Kết quả này cho thấy vật tư này chưa được ghi nhận trong hệ thống quản lý mua sắm quốc gia, cần được bổ sung và kiểm tra lại.
+**Cơ sở 4 (Mua Sắm Công e-GP):** Chứng cứ từ nền tảng mua sắm công nghệ không cung cấp thêm thông tin cụ thể về giá hoặc trạng thái tồn kho của vật tư này.
+**Cơ sở 5 (Thương Mại Điện Tử):** Chứng cứ từ kênh thương mại điện tử cũng không cung cấp dữ liệu mua sắm chi tiết và đáng tin cậy.
+### 4. Kết luận về tính nhất quán của dữ liệu
+Từ việc tổng hợp và đối chiếu 5 cơ sở chứng cứ, Tổ Thẩm định nhận thấy:
+- Mức giá đơn giản hóa (14.208.000 đ) không phù hợp với giá tham chiếu thực tế (7.000.000 đ) từ ERP Vĩnh Tân 4
+- Có sự thiếu hụt trong hệ thống dữ liệu mua sắm (Cơ sở 3, 4, 5)
+- Mức chênh lệch giá &gt;103% vượt quá ngưỡng chấp nhận được trong quản lý tài sản nhà máy
+---
+## KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO
+### 1. Kết luận chính
+Tổ Thẩm định nhận định **đơn giá trình thẩm định (14.208.000 đ) là không phù hợp** với giá tham chiếu thực tế và thị trường. Mức chênh lệch **+103.0%** so với giá nhập kho từ Cơ sở 2 (7.000.000 đ) vượt quá biên độ an toàn quy định. Việc duy trì mức giá hiện tại có thể dẫn đến các rủi ro về chi phí vận hành, bảo trì và tuân thủ quy định an toàn.
+### 2. Đề xuất điều chỉnh
+**Đề xuất 1: Điều chỉnh đơn giá phê duyệt**
+Tổ Thẩm định đề xuất Lãnh đạo/Hội đồng Thẩm định xem xét **giảm mức đơn giá** từ **14.208.000 đ** xuống còn **7.000.000 đ/Cái**, tương đương giá tham chiếu thấp nhất từ Cơ sở 2 (ERP Vĩnh Tân 4). Mức điều chỉnh này giúp tối ưu hóa chi phí vận hành và đảm bảo tính kinh tế cho Nhà máy Nhiệt điệ</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr"/>
+      <c r="J6" s="6" t="n">
         <v>7000000</v>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="K6" s="6" t="n">
         <v>7000000</v>
       </c>
-      <c r="N6" s="7" t="n">
+      <c r="L6" s="6" t="n">
         <v>7208000</v>
       </c>
-      <c r="O6" s="6" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>Cơ sở 2: Lịch sử mua sắm ERP Vĩnh Tân 4 (QĐ 161)</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>3.34.40.024.ENG.00.000 | Khắc phục tồn tại thiết bị | BBKT 23/2026/PXH-VT4. Vật tư không có trong KH SXKD 2026</t>
         </is>
       </c>
     </row>
@@ -744,14 +744,9 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Actuator khí nén FlowTek Series 92</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Actuator khí nén:
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Actuator khí nén FlowTek Series 92 - Actuator khí nén:
 Model:
  FlowTek Series 92 (920830-113A0532)
 Type: DOUBLE ACTING
@@ -761,26 +756,21 @@
 Nhà sản xuất: Bray International</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Bray/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="E7" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="F7" s="6" t="n">
         <v>56000000</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="G7" s="6" t="n">
         <v>280000000</v>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>1. TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Actuator khí nén FlowTek Series 92 (Double Acting) - Model: 920830-113A0532.
 • Đơn giá trình thẩm định: 56.000.000 VNĐ/Bộ (Số lượng: 5 Bộ).
@@ -792,24 +782,19 @@
 - Cơ sở 3 (EVN IMIS): Chưa có dữ liệu mua sắm tương đương trên CSDL EVN IMIS toà</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr"/>
-      <c r="L7" s="7" t="n">
+      <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="6" t="n">
         <v>16491600</v>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="K7" s="6" t="n">
         <v>82458000</v>
       </c>
-      <c r="N7" s="7" t="n">
+      <c r="L7" s="6" t="n">
         <v>197542000</v>
       </c>
-      <c r="O7" s="6" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>Cơ sở 5: Tham khảo TMĐT / Giá Web (Landed Cost DDP VT4)</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Khắc phục tồn tại thiết bị | BBKT 547/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
         </is>
       </c>
     </row>
@@ -822,14 +807,9 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Solenoid van 600250-70900533</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Solenoid van:
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Solenoid van 600250-70900533 - Solenoid van:
 Mã thiết bị: 600250-70900533
 Loại van: Van điều khiển ống dẫn (spool control valve) được vận hành bằng khí nén (pilot-operated).
 Điện áp: 24 VAC.
@@ -840,50 +820,40 @@
 Nhà sản xuất: Bray International.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Bray/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="E8" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="F8" s="6" t="n">
         <v>64000000</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="G8" s="6" t="n">
         <v>320000000</v>
       </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t># THUYẾT MINH THẨM ĐỊNH MỤC STT 4
 ## TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
-Tổ Thẩm định thự</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr"/>
-      <c r="L8" s="7" t="n">
+Tổ Thẩm định thực hiện thẩm định đánh giá sau cùng đối với vật tư Solenoid van 600250-70900533 (Hãng SX: Bray International, số lượng 5 Bộ). Đơn giá dự toán trình là 64.000.000 đ/Bộ, cao hơn +610.4% so với đơn giá tham chiếu thấp nhất hợp lệ (9.009.300 đ từ Cơ sở 5). Tổ Thẩm định đề xuất điều chỉnh đơn giá theo giá thị trường quốc tế đã tính đủ chi phí nhập cảnh &amp; vận chuyển DDP Vĩ</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr"/>
+      <c r="J8" s="6" t="n">
         <v>9009300</v>
       </c>
-      <c r="M8" s="7" t="n">
+      <c r="K8" s="6" t="n">
         <v>45046500</v>
       </c>
-      <c r="N8" s="7" t="n">
+      <c r="L8" s="6" t="n">
         <v>274953500</v>
       </c>
-      <c r="O8" s="6" t="inlineStr">
+      <c r="M8" s="7" t="inlineStr">
         <is>
           <t>Cơ sở 5: Tham khảo TMĐT / Giá Web</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Khắc phục tồn tại thiết bị | BBKT 547/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
         </is>
       </c>
     </row>
@@ -896,36 +866,26 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Spiral Wound Gasket DN200 PN40</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Spiral Wound Gasket DN200 PN40 RF – EN 1514-2 – Type CGI – SS316L/PTFE/SS316L/CS</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>QT/ Việt Nam</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Spiral Wound Gasket DN200 PN40 - Spiral Wound Gasket DN200 PN40 RF – EN 1514-2 – Type CGI – SS316L/PTFE/SS316L/CS</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="E9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="F9" s="6" t="n">
         <v>1500000</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="G9" s="6" t="n">
         <v>3000000</v>
       </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Spiral Wound Gasket DN200 PN40 (Mã ERP: Chưa có mã vật tư).
 • Đơn giá trình thẩm định: 1.500.000 VNĐ (Số lượng: 2 Cái).
@@ -940,24 +900,19 @@
 KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 1.500.000 VNĐ/Cái.</t>
         </is>
       </c>
-      <c r="K9" s="6" t="inlineStr"/>
-      <c r="L9" s="7" t="n">
+      <c r="I9" s="7" t="inlineStr"/>
+      <c r="J9" s="6" t="n">
         <v>1500000</v>
       </c>
-      <c r="M9" s="7" t="n">
+      <c r="K9" s="6" t="n">
         <v>3000000</v>
       </c>
-      <c r="N9" s="7" t="n">
+      <c r="L9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="6" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr">
         <is>
           <t>Cơ sở 1: Báo giá nộp kèm</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Thay mới van tổng cấp bồn CO2 bị rò qua van và ty van | BBKT 510/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
         </is>
       </c>
     </row>
@@ -970,36 +925,26 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>GEFA DG1 Ball Valve</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>GEFA DG1 Ball Valve, DN50/65, PN125, Body SS316 (1.4408), High Pressure Ball Valve, Rohrgewinde DIN 2999-Rp, ISO 228/1-G</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Gefa-xx/ Đức</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>GEFA DG1 Ball Valve - GEFA DG1 Ball Valve, DN50/65, PN125, Body SS316 (1.4408), High Pressure Ball Valve, Rohrgewinde DIN 2999-Rp, ISO 228/1-G</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="F10" s="6" t="n">
         <v>61250000</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="G10" s="6" t="n">
         <v>61250000</v>
       </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
 • Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 61.250.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
@@ -1010,24 +955,19 @@
 KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 8.910.000 đ/Cái.</t>
         </is>
       </c>
-      <c r="K10" s="6" t="inlineStr"/>
-      <c r="L10" s="7" t="n">
+      <c r="I10" s="7" t="inlineStr"/>
+      <c r="J10" s="6" t="n">
         <v>8910000</v>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="K10" s="6" t="n">
         <v>8910000</v>
       </c>
-      <c r="N10" s="7" t="n">
+      <c r="L10" s="6" t="n">
         <v>52340000</v>
       </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>Cơ sở 1: Báo giá nộp kèm</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Thay mới van bypass đầu ra bồn CO2 DN50 bị rò qua ty van và đoạn ống kết nối bị rò rỉ tại vị trí ren | BBKT 510/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 3: EVN IMIS Toàn Ngành</t>
         </is>
       </c>
     </row>
@@ -1040,14 +980,9 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Selector valve KMX CO2</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Selector valve KMX CO₂ LP piston controlled, complete
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Selector valve KMX CO2 - Selector valve KMX CO₂ LP piston controlled, complete
 - Size: DN50
 ­	End Connection: Flange DIN 2501 PN40
 ­	Working pressure: 25 bar
@@ -1055,26 +990,21 @@
 ­	Housing: Cast steel, Piston: GJL-250, Piston Rod: AISI 303</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Minimax/ Đức</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="E11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="F11" s="6" t="n">
         <v>452147000</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="G11" s="6" t="n">
         <v>452147000</v>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
 • Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 135.000.000 đ/Cái (CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU)
@@ -1085,24 +1015,19 @@
 KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 4.925.000 đ/Cái.</t>
         </is>
       </c>
-      <c r="K11" s="6" t="inlineStr"/>
-      <c r="L11" s="7" t="n">
+      <c r="I11" s="7" t="inlineStr"/>
+      <c r="J11" s="6" t="n">
         <v>452147000</v>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="K11" s="6" t="n">
         <v>452147000</v>
       </c>
-      <c r="N11" s="7" t="n">
+      <c r="L11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="6" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr">
         <is>
           <t>Cơ sở 1: Báo giá nộp kèm</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Thay mới van chính đầu ra bồn CO2 DN50 bị rò qua van và ty van | BBKT 510/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
         </is>
       </c>
     </row>
@@ -1115,14 +1040,9 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Union G 10-PL A3C</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Union 
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Union G 10-PL A3C - Union 
 - Type: G - Union 
 - Model: G 10-PL A3C 
 - Part no.: 125943 
@@ -1133,26 +1053,21 @@
 - Manufacturer: Minimax Gmb, Germany</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Minimax/ Đức</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="E12" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="F12" s="6" t="n">
         <v>1004000</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="G12" s="6" t="n">
         <v>10040000</v>
       </c>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
 • Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 1.004.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
@@ -1161,24 +1076,19 @@
 • Cơ sở 4 (Mua Sắ</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr"/>
-      <c r="L12" s="7" t="n">
+      <c r="I12" s="7" t="inlineStr"/>
+      <c r="J12" s="6" t="n">
         <v>620000</v>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="K12" s="6" t="n">
         <v>6200000</v>
       </c>
-      <c r="N12" s="7" t="n">
+      <c r="L12" s="6" t="n">
         <v>3840000</v>
       </c>
-      <c r="O12" s="6" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>Cơ sở 2: Lịch sử mua sắm ERP Vĩnh Tân 4 (HĐ 03/2022)</t>
-        </is>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Thay mới các đầu nối, đường ống điều khiển khí nén các van actuator phun CO2 bị rò rỉ và gỉ sét | BBKT 510/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
         </is>
       </c>
     </row>
@@ -1191,14 +1101,9 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Elbow union</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Elbow union 
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Elbow union - Elbow union 
 - Type: W - Elbow union 
 - Model: W 10-PL A3C
 - Part no.: 174678 
@@ -1209,26 +1114,21 @@
 - Manufacturer: Minimax Gmb, Germany</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Minimax/ Đức</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="E13" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="F13" s="6" t="n">
         <v>1315000</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="G13" s="6" t="n">
         <v>6575000</v>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Elbow union (Mã ERP: Chưa có mã vật tư).
 • Đơn giá trình thẩm định: 1.315.000 VNĐ (Số lượng: 5 Cái).
@@ -1243,24 +1143,19 @@
 KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 1.315.000 VNĐ/Cái.</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr"/>
-      <c r="L13" s="7" t="n">
+      <c r="I13" s="7" t="inlineStr"/>
+      <c r="J13" s="6" t="n">
         <v>1315000</v>
       </c>
-      <c r="M13" s="7" t="n">
+      <c r="K13" s="6" t="n">
         <v>6575000</v>
       </c>
-      <c r="N13" s="7" t="n">
+      <c r="L13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="6" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>Cơ sở 1: Báo giá nộp kèm</t>
-        </is>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Thay mới các đầu nối, đường ống điều khiển khí nén các van actuator phun CO2 bị rò rỉ và gỉ sét | BBKT 510/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
         </is>
       </c>
     </row>
@@ -1273,14 +1168,9 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Union tee</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Union tee 
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Union tee - Union tee 
 - Type: T - Union tee 
 - Model: T - PL A3C 
 - Part no.: 125645 
@@ -1291,26 +1181,21 @@
 - Manufacturer: Minimax Gmb, Germany</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Minimax/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="E14" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="F14" s="6" t="n">
         <v>1508000</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="G14" s="6" t="n">
         <v>7540000</v>
       </c>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>I. TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
 | Hạng mục | Nội dung |
@@ -1346,24 +1231,19 @@
 Tổ Thẩm định kính trình Lãnh đạo/Hội đồng Thẩm định xem xét, quyết định.</t>
         </is>
       </c>
-      <c r="K14" s="6" t="inlineStr"/>
-      <c r="L14" s="7" t="n">
+      <c r="I14" s="7" t="inlineStr"/>
+      <c r="J14" s="6" t="n">
         <v>1508000</v>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="K14" s="6" t="n">
         <v>7540000</v>
       </c>
-      <c r="N14" s="7" t="n">
+      <c r="L14" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="6" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>Cơ sở 1: Báo giá nộp kèm</t>
-        </is>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Thay mới các đầu nối, đường ống điều khiển khí nén các van actuator phun CO2 bị rò rỉ và gỉ sét | BBKT 510/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
         </is>
       </c>
     </row>
@@ -1376,64 +1256,57 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Ống B-210-2394/1</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Tube 
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Ống B-210-2394/1 - Tube 
 - Model: B-210-2394/1 
 - OD: 10mm (DN8) 
 - Part no.: 823575
 - Test pressure: 210 (bar)</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Minimax/ Đức</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="E15" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="F15" s="6" t="n">
         <v>1205000</v>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="G15" s="6" t="n">
         <v>24100000</v>
       </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
-• Cơ sở 1 (Báo Giá Gốc): Chưa nạp dữ liệu Báo giá gốc
-• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 64.001.100 đ/Mét (HĐ: Nhập kho vật tư (HĐ: 40/2025) theo hóa đơn số 1956 ngày 30.10.2025 ngày 2025-12-12. SL: 3 Mét); Các đợt nhập khác: 16.649.700 đ, 11.181.019 đ
-• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [B-210-2394], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
-• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Ống B-210-2394/1] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
-• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
-KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 64.001.100 đ/Mét.</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr"/>
-      <c r="L15" s="7" t="n">
-        <v>64001100</v>
-      </c>
-      <c r="M15" s="7" t="n">
-        <v>1280022000</v>
-      </c>
-      <c r="N15" s="7" t="n">
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Ống B-210-2394/1 (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 1.205.000 VNĐ (Số lượng: 20 Mét).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 1.205.000 VNĐ/Mét từ DTL 19.8.2026. xlsx (Trang 2 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Qua rà soát CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 theo từ khóa [Ống B], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [B-210-2394] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [Ống B-210-2394/1] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); kết quả đã rà soát e-GP: vật tư đặc thù, không ghi nhận gói thầu mua sắm tương đồng.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [B-210-2394] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 1.205.000 VNĐ/Mét.</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr"/>
+      <c r="J15" s="6" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>24100000</v>
+      </c>
+      <c r="L15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="6" t="inlineStr"/>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Thay mới các đầu nối, đường ống điều khiển khí nén các van actuator phun CO2 bị rò rỉ và gỉ sét | BBKT 510/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -1446,14 +1319,9 @@
           <t>3.96.13.021.GER.00.000</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Cảm biến đo khối lượng (Loadcell), model: RTNC3/10T</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Cảm biến đo khối lượng (Loadcell):
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Cảm biến đo khối lượng (Loadcell), model: RTNC3/10T - Cảm biến đo khối lượng (Loadcell):
 - Model: RTNC3/10T
 - Odering number: K-RTN-8-C3-10-N-12-N-N-8
 - Maximum capacity (Emax): 10000kg
@@ -1472,26 +1340,21 @@
 - Manufacturer: Hottinger Baldwin Messtechnik GmbH (HBM), Germany</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>HBK/ Đức</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="E16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="F16" s="6" t="n">
         <v>117600000</v>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="G16" s="6" t="n">
         <v>117600000</v>
       </c>
-      <c r="J16" s="6" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
 • Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 117.600.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
@@ -1499,27 +1362,22 @@
 • Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [RTNC3], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
 • Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Cảm biến đo khối lượng (Loadcell), model: RTNC3/10T] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
 • Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
-KẾ</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="inlineStr"/>
-      <c r="L16" s="7" t="n">
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 57.465.833 đ/Cái.</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr"/>
+      <c r="J16" s="6" t="n">
         <v>113232916.5</v>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="K16" s="6" t="n">
         <v>113232916</v>
       </c>
-      <c r="N16" s="7" t="n">
-        <v>4367084</v>
-      </c>
-      <c r="O16" s="6" t="inlineStr">
+      <c r="L16" s="6" t="n">
+        <v>4367083.5</v>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>Cơ sở 2: ERP Vĩnh Tân 4</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>3.96.13.021.GER.00.000 | Thay thế 01 cảm biến đo khối lượng (Loadcell) bồn chứa khí CO2 – Tổ máy S3 bị hư hỏng | BBKT 510/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
         </is>
       </c>
     </row>
@@ -1532,14 +1390,9 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Tủ MCC bucket - MCC unit order code: P0BHC01GH004R-AH400. Type G1, 65kW, TS250H</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>MCC bucket 
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Tủ MCC bucket - MCC unit order code: P0BHC01GH004R-AH400. Type G1, 65kW, TS250H - MCC bucket 
 - MCC unit order code: P0BHC01GH004R-A H400
 - Type: G1
 - Load description: Spare
@@ -1556,40 +1409,48 @@
 - Manufacturer: LS Electric, Korea</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>LS/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="E17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="F17" s="6" t="n">
         <v>284390000</v>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="G17" s="6" t="n">
         <v>284390000</v>
       </c>
-      <c r="J17" s="6" t="inlineStr"/>
-      <c r="K17" s="6" t="inlineStr"/>
-      <c r="L17" s="7" t="n">
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Tủ MCC bucket (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 284.390.000 VNĐ (Số lượng: 1 Bộ).
+• Đánh giá Chứng cứ Thẩm định: Đạt 80/100 điểm (Hạng A - 4/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 284.390.000 VNĐ/Bộ từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 3 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [Tủ MCC bucket] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; kết quả đã đối soát CSDL ERP: 0 bản ghi phù hợp (vật tư chưa từng có lịch sử nhập kho nội bộ nhà máy Vĩnh Tân 4).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [P0BHC01GH004R] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [Susol LS Electric] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 317.370.192 VNĐ/Bộ (Nhà thầu LS ELECTRIC).
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Tủ MCC bucket] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 284.390.000 VNĐ/Bộ.</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr"/>
+      <c r="J17" s="6" t="n">
         <v>284390000</v>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="K17" s="6" t="n">
         <v>284390000</v>
       </c>
-      <c r="N17" s="7" t="n">
+      <c r="L17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="6" t="inlineStr"/>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Khắc phục theo BBKT 1002/2026/VH-VT4 | Vật tư mua mới, chưa đề xuất trong KHSXKD 2026</t>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -1602,14 +1463,9 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Tủ MCC bucket - MCC unit order code: P0BHC01GH004R-BH200. Type S</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>MCC bucket 
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Tủ MCC bucket - MCC unit order code: P0BHC01GH004R-BH200. Type S - MCC bucket 
 - MCC unit order code: P0BHC01GH004R-B H200
 - Load description: Space
 - Type: S
@@ -1617,40 +1473,48 @@
 - Manufacturer: LS Electric, Korea</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>LS/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="E18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="F18" s="6" t="n">
         <v>183501000</v>
       </c>
-      <c r="I18" s="7" t="n">
+      <c r="G18" s="6" t="n">
         <v>183501000</v>
       </c>
-      <c r="J18" s="6" t="inlineStr"/>
-      <c r="K18" s="6" t="inlineStr"/>
-      <c r="L18" s="7" t="n">
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Tủ MCC bucket (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 183.501.000 VNĐ (Số lượng: 1 Bộ).
+• Đánh giá Chứng cứ Thẩm định: Đạt 40/100 điểm (Hạng C - 2/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 183.501.000 VNĐ/Bộ từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 3 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Chưa đối chiếu CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4.
+- Cơ sở 3 (EVN IMIS): Chưa đối chiếu CSDL Hợp đồng mua sắm toàn ngành EVN IMIS.
+- Cơ sở 4 (Mua Sắm Công e-GP): Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khóa [LS Electric], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL Mua sắm công làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Tủ MCC bucket] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 183.501.000 VNĐ/Bộ.</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr"/>
+      <c r="J18" s="6" t="n">
         <v>183501000</v>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="K18" s="6" t="n">
         <v>183501000</v>
       </c>
-      <c r="N18" s="7" t="n">
+      <c r="L18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="6" t="inlineStr"/>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Khắc phục theo BBKT 1002/2026/VH-VT4 | Vật tư mua mới, chưa đề xuất trong KHSXKD 2026</t>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -1663,14 +1527,9 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Tủ MCC bucket - MCC unit order code: P0BHC01GH004R-CH200. Type G1, 8.1kW, TS100H</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>MCC bucket 
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Tủ MCC bucket - MCC unit order code: P0BHC01GH004R-CH200. Type G1, 8.1kW, TS100H - MCC bucket 
 - MCC unit order code: P0BHC01GH004R-C H200
 - Load description: Spare
 - Capacity: 8.1kW
@@ -1686,40 +1545,44 @@
 - Manufacturer: LS Electric, Korea</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>LS/ Việt Nam</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="E19" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="7" t="n">
+      <c r="F19" s="6" t="n">
         <v>233654000</v>
       </c>
-      <c r="I19" s="7" t="n">
+      <c r="G19" s="6" t="n">
         <v>233654000</v>
       </c>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
-      <c r="L19" s="7" t="n">
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 233.654.000 đ/Bộ (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Vật tư chưa có lịch sử mua sắm/nhập kho trong CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4.
+• Cơ sở 3 (EVN IMIS): IMIS EVN: 1.634.636.360 đ/Cái (Công ty Công nghệ thông tin Điện lực miền Nam)
+• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Tủ MCC bucket - MCC unit order code: P0BHC01GH004R-CH200. Type G1, 8.1kW, TS100H] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 233.654.000 đ/Bộ.</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr"/>
+      <c r="J19" s="6" t="n">
         <v>233654000</v>
       </c>
-      <c r="M19" s="7" t="n">
+      <c r="K19" s="6" t="n">
         <v>233654000</v>
       </c>
-      <c r="N19" s="7" t="n">
+      <c r="L19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O19" s="6" t="inlineStr"/>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Khắc phục theo BBKT 1002/2026/VH-VT4 | Vật tư mua mới, chưa đề xuất trong KHSXKD 2026</t>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -1732,52 +1595,55 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Thanh cái đồng mạ bạc Busbar 400V</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Thanh cái đồng mạ bạc
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Thanh cái đồng mạ bạc Busbar 400V - Thanh cái đồng mạ bạc
 Kích thước: Dài x rộng x dày (850x125x10mm)
 Chiều dài: 850mm</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Kungho/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Thanh</t>
         </is>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="E20" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="F20" s="6" t="n">
         <v>48000000</v>
       </c>
-      <c r="I20" s="7" t="n">
+      <c r="G20" s="6" t="n">
         <v>48000000</v>
       </c>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
-      <c r="L20" s="7" t="n">
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Thanh cái đồng mạ bạc Busbar 400V (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 48.000.000 VNĐ (Số lượng: 1 Thanh).
+• Đánh giá Chứng cứ Thẩm định: Đạt 80/100 điểm (Hạng A - 4/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 48.000.000 VNĐ/Thanh từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 3 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [Thanh cái đồng mạ bạc Busbar 400V] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; kết quả đã đối soát CSDL ERP: 0 bản ghi phù hợp (vật tư chưa từng có lịch sử nhập kho nội bộ nhà máy Vĩnh Tân 4).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [400V] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khóa [Busbar], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL Mua sắm công làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Thanh cái đồng mạ bạc Busbar 400V] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 48.000.000 VNĐ/Thanh.</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr"/>
+      <c r="J20" s="6" t="n">
         <v>48000000</v>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="K20" s="6" t="n">
         <v>48000000</v>
       </c>
-      <c r="N20" s="7" t="n">
+      <c r="L20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O20" s="6" t="inlineStr"/>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Thay thế cho vật tư hư hỏng theo BBKT 37/2026/VH-VT4 | Vật tư mua mới, không đề xuất trong KHSXKD 2026</t>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -1790,52 +1656,45 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Thanh cái đồng V phân phối mạ bạc</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Thanh cái đồng V phân phối mạ bạc
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Thanh cái đồng V phân phối mạ bạc - Thanh cái đồng V phân phối mạ bạc
 Kích thước: 28x40x6mm
 Chiều dài: 920mm</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Kungho/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Thanh</t>
         </is>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="E21" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="H21" s="7" t="n">
+      <c r="F21" s="6" t="n">
         <v>48000000</v>
       </c>
-      <c r="I21" s="7" t="n">
+      <c r="G21" s="6" t="n">
         <v>192000000</v>
       </c>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
-      <c r="L21" s="7" t="n">
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Tổ Thẩm định đã rà soát 5 cơ sở chứng cứ (trong đó đã loại trừ 4. Mua Sắm Công e-GP do thẩm định viên đánh giá tính tương thích). Đơn giá thẩm định thống nhất đề xuất là 48.000.000 đ theo 1. Báo Giá Gốc (PDF).</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr"/>
+      <c r="J21" s="6" t="n">
         <v>48000000</v>
       </c>
-      <c r="M21" s="7" t="n">
+      <c r="K21" s="6" t="n">
         <v>192000000</v>
       </c>
-      <c r="N21" s="7" t="n">
+      <c r="L21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="6" t="inlineStr"/>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Thay thế cho vật tư hư hỏng theo BBKT 37/2026/VH-VT4 | Vật tư mua mới, không đề xuất trong KHSXKD 2026</t>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>1. Báo Giá Gốc (PDF)</t>
         </is>
       </c>
     </row>
@@ -1848,53 +1707,56 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Van điện từ 221S25F-S2TBC2</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Van điện từ 221S25F-S2TBC2,
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Van điện từ 221S25F-S2TBC2 - Van điện từ 221S25F-S2TBC2,
 Van 2 chiều, kích thước đường ống 1 inch,
 Điện áp cuộn điện từ (coil) 24 VDC,
 Nhà sản xuất: Parker</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Parker/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="E22" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="7" t="n">
+      <c r="F22" s="6" t="n">
         <v>22000000</v>
       </c>
-      <c r="I22" s="7" t="n">
+      <c r="G22" s="6" t="n">
         <v>22000000</v>
       </c>
-      <c r="J22" s="6" t="inlineStr"/>
-      <c r="K22" s="6" t="inlineStr"/>
-      <c r="L22" s="7" t="n">
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Van điện từ 221S25F-S2TBC2 (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 22.000.000 VNĐ (Số lượng: 1 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 22.000.000 VNĐ/Cái từ CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (Trang 3 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [221S25F] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; kết quả đã đối soát CSDL ERP: 0 bản ghi phù hợp (vật tư chưa từng có lịch sử nhập kho nội bộ nhà máy Vĩnh Tân 4).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [221S25F] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [221S25F] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); kết quả đã rà soát e-GP: vật tư đặc thù, không ghi nhận gói thầu mua sắm tương đồng.
+- Cơ sở 5 (Thương Mại Điện Tử): Mã van điện từ Parker 221S25F-S2TBC2 không có giá niêm yết công khai tại thị trường Việt Nam. [1] (https://www.starline.vn/series/parker-221s)
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 22.000.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr"/>
+      <c r="J22" s="6" t="n">
         <v>22000000</v>
       </c>
-      <c r="M22" s="7" t="n">
+      <c r="K22" s="6" t="n">
         <v>22000000</v>
       </c>
-      <c r="N22" s="7" t="n">
+      <c r="L22" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O22" s="6" t="inlineStr"/>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã ERP | Hệ thống xử lý nước thải (van điền nước bồn A polymer)76/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -1907,36 +1769,26 @@
           <t>2.46.35.037.CHN.00.000</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Swagelok/ Đức</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m - Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="E23" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="H23" s="7" t="n">
+      <c r="F23" s="6" t="n">
         <v>19300000</v>
       </c>
-      <c r="I23" s="7" t="n">
+      <c r="G23" s="6" t="n">
         <v>675500000</v>
       </c>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m (Mã ERP: 2.46.35.037.CHN.00.000).
 • Đơn giá trình thẩm định: 19.300.000 VNĐ (Số lượng: 35 Cái).
@@ -1951,24 +1803,19 @@
 KẾT LUẬN THẨM ĐỊNH: Đề xuất duyệt đơn giá thẩm định thống nhất là 18.522.000 VNĐ/Cái. Tiết kiệm dự toán 27.230.000 VNĐ (-4.0%).</t>
         </is>
       </c>
-      <c r="K23" s="6" t="inlineStr"/>
-      <c r="L23" s="7" t="n">
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="6" t="n">
         <v>18522000</v>
       </c>
-      <c r="M23" s="7" t="n">
+      <c r="K23" s="6" t="n">
         <v>648270000</v>
       </c>
-      <c r="N23" s="7" t="n">
+      <c r="L23" s="6" t="n">
         <v>27230000</v>
       </c>
-      <c r="O23" s="6" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>Cơ sở 1: Báo giá nộp kèm</t>
-        </is>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>2.46.35.037.CHN.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
         </is>
       </c>
     </row>
@@ -1981,50 +1828,53 @@
           <t>2.46.35.019.CHN.00.000</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Swagelok/ Đức</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m - Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="E24" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="7" t="n">
+      <c r="F24" s="6" t="n">
         <v>19000000</v>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="G24" s="6" t="n">
         <v>38000000</v>
       </c>
-      <c r="J24" s="6" t="inlineStr"/>
-      <c r="K24" s="6" t="inlineStr"/>
-      <c r="L24" s="7" t="n">
-        <v>19000000</v>
-      </c>
-      <c r="M24" s="7" t="n">
-        <v>38000000</v>
-      </c>
-      <c r="N24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="6" t="inlineStr"/>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>2.46.35.019.CHN.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m (Mã ERP: 2.46.35.019.CHN.00.000).
+• Đơn giá trình thẩm định: 19.000.000 VNĐ (Số lượng: 2 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 30/100 điểm (🔴 Chưa Hợp Lý (Đơn giá trình cao hơn &gt;20% so với mốc giá tham chiếu)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 19.000.000 VNĐ/Cái từ CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (Trang 4 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [2.46.35.019.CHN.00.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 12.350.000 VNĐ/Cái theo HĐ Nhập kho vật tư (HĐ: 120/2024) theo hóa đơn số 00000008 ngày 13.01.2025 (ký ngày 2025-01-16 00:00:00, cách đây 20 tháng ~ 1.7 năm - quá 12 tháng, tốc độ tăng giá bình quân 32.3%/năm so với CPI ~5.0%/năm).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [SS-T8-S-065-20] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [SS-T8-S-065-20] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 21.230.000 VNĐ/Cái (Nhà thầu Swagelok).
+- Cơ sở 5 (Thương Mại Điện Tử): Đã tra cứu từ khóa [SS-T8-S-065-20] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đề xuất duyệt đơn giá thẩm định thống nhất là 12.350.000 VNĐ/Cái. Tiết kiệm dự toán 13.300.000 VNĐ (-35.0%).</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr"/>
+      <c r="J24" s="6" t="n">
+        <v>12350000</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>24700000</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>13300000</v>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -2037,50 +1887,53 @@
           <t>4.82.22.013.USA.00.000</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Swagelok/ Đức</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6 - Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G25" s="7" t="n">
+      <c r="E25" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="7" t="n">
+      <c r="F25" s="6" t="n">
         <v>1700000</v>
       </c>
-      <c r="I25" s="7" t="n">
+      <c r="G25" s="6" t="n">
         <v>3400000</v>
       </c>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
-      <c r="L25" s="7" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="M25" s="7" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="N25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="6" t="inlineStr"/>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>4.82.22.013.USA.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6 (Mã ERP: 4.82.22.013.USA.00.000).
+• Đơn giá trình thẩm định: 1.700.000 VNĐ (Số lượng: 2 Bộ).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 30/100 điểm (🔴 Chưa Hợp Lý (Đơn giá trình cao hơn &gt;20% so với mốc giá tham chiếu)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 1.700.000 VNĐ/Bộ từ CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (Trang 4 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [4.82.22.013.USA.00.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 1.620.000 VNĐ/Bộ theo HĐ Nhập kho vật tư (HĐ:03/2022) theo hóa đơn số 00000017 ngày 04.03.2022 (ký ngày 2022-03-07 00:00:00, cách đây 54 tháng ~ 4.5 năm - quá 12 tháng, tốc độ tăng giá bình quân 1.1%/năm so với CPI ~5.0%/năm).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [SS-810-6] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); ghi nhận đơn giá trúng thầu/hợp đồng tham chiếu là 1.350.000 VNĐ/Bộ tại Công ty Dịch vụ sửa chữa các nhà máy điện EVNGENCO3 theo HĐ 133/EPS-VN/24_21 (thực hiện cách đây 24 tháng ~ 2 năm - quá 12 tháng).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [SS-810-6] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 1.319.000 VNĐ/Bộ (Nhà thầu Swagelok).
+- Cơ sở 5 (Thương Mại Điện Tử): Đã tra cứu từ khóa [Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đề xuất duyệt đơn giá thẩm định thống nhất là 1.319.000 VNĐ/Bộ. Tiết kiệm dự toán 762.000 VNĐ (-22.4%).</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr"/>
+      <c r="J25" s="6" t="n">
+        <v>1319000</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>2638000</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>762000</v>
+      </c>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 4: Mua Sắm Công e-GP</t>
         </is>
       </c>
     </row>
@@ -2093,50 +1946,58 @@
           <t>4.82.22.025.CHN.00.000</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Đầu nối - Union Swagelok Model: SS-600-6</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>Đầu nối - Union Swagelok Model: SS-600-6</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Swagelok/ Đức</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Đầu nối - Union Swagelok Model: SS-600-6 - Đầu nối - Union Swagelok Model: SS-600-6</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="E26" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H26" s="7" t="n">
+      <c r="F26" s="6" t="n">
         <v>2600000</v>
       </c>
-      <c r="I26" s="7" t="n">
+      <c r="G26" s="6" t="n">
         <v>260000000</v>
       </c>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
-      <c r="L26" s="7" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="M26" s="7" t="n">
-        <v>260000000</v>
-      </c>
-      <c r="N26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="6" t="inlineStr"/>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>4.82.22.025.CHN.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Đầu nối - Union Swagelok Model: SS-600-6 - Đầu nối - Union Swagelok Model: SS-600-6 (Mã ERP: 4.82.22.025.CHN.00.000).
+• Đơn giá trình thẩm định: 2.600.000 đ (Số lượng: 100.0 Cái).
+• Đánh giá Chứng cứ Thẩm định: 5/5 cơ sở chứng cứ đã rà soát.
+• Mức độ Hợp lý Đơn giá: 50/100 điểm.
+🔍 Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN:
+- Phân tích Bản chất Kỹ thuật Thiết bị: Vật tư thuộc phân nhóm [Thiết bị Công nghiệp Chuyên dụng] với thương hiệu/tiêu chuẩn [Chưa rõ Hãng - Tiêu chuẩn kỹ thuật công nghiệp tiêu chuẩn]. Đây là dòng vật tư linh kiện có yêu cầu kỹ thuật đặc thù, đòi hỏi độ tin cậy và tiêu chuẩn an toàn cao trong vận hành nhà máy nhiệt điện.
+- Đánh giá Tương quan Giá trị Kỹ thuật &amp; Thương mại: Đơn giá trình 2.600.000 đ cao hơn +303.3% so với đơn giá tham chiếu thấp nhất hợp lệ (644.760 đ từ Cơ sở 3: EVN IMIS). Với đặc tính kỹ thuật vật tư hiện tại, mức chênh lệch này vượt quá biên độ an toàn và Tổ Thẩm định đề xuất xem xét điều chỉnh.
+💡 KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO:
+🔴 CẢNH BÁO BẤT THƯỜNG ĐƠN GIÁ: Tổ Thẩm định đề xuất Lãnh đạo/Hội đồng Thẩm định đàm phán điều chỉnh đơn giá phê duyệt về mức 644.760 đ căn cứ theo Cơ sở 3: EVN IMIS (Dự kiến tiết kiệm 195.524.000 đ cho Nhà máy).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đơn giá trình (2,600,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 4). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG báo giá 3,000,000 đ (+15.4%). Đơn giá trình phù hợp theo quy định lựa chọn mức giá thấp nhất giữa các báo giá hợp lệ.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Vật tư có lịch sử nhập kho theo Nhập kho vật tư (HĐ: 25/2025) theo hóa đơn số 00000091 ngày 24.06.2025 (ngày ký 2025-07-24 00:00:00) với đơn giá 2.600.000 đ/Cái (Tổng số 6 đợt mua sắm lịch sử có đơn giá dao động từ 630.000 đ đến 2.600.000 đ/Cái. Đơn giá trình nằm trong khoảng dao động giá lịch sử của Nhà máy và thấp hơn -0.0% so với đợt mua HĐ 132/2023 giá 2.600.000 đ). Đơn giá trình đợt này là 2.600.000 đ/Cái (giảm 0.0% so với ERP cũ cách đây 14 tháng). Đơn giá trình phù hợp theo thực tế.
+- Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 14/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [SS-600-6], vật tư có lịch sử mua sắm tương đương tại GENCO1 - Công ty Nhiệt Điện Nghi Sơn (thời gian N/A) với đơn giá 644.760 đ/Cái (Tổng số 3 đợt mua sắm toàn ngành EVN có đơn giá dao động từ 644.760 đ đến 645.390 đ/Cái. Đơn giá trình cao hơn +302.9% so với mức giá IMIS EVN cao nhất 645.390 đ). Đơn giá trình đợt này là 2.600.000 đ/Cái (tăng +303.3% so với giá IMIS EVN). Cần kết hợp đối chiếu thêm với Báo giá mới (Khối 1) và CSDL ERP Vĩnh Tân 4 (Khối 2).
+- Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [SS-600-6] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 10:36 ngày 14/09/2026; ghi nhận đơn giá trúng thầu tham chiếu quy đổi trước thuế VAT 8% là 735.269 đ (giá gốc e-GP gồm VAT 8%: 794.090 đ, Mã TBMT: IB2400563322, Bên mời thầu: CÔNG TY NHIỆT ĐIỆN NGHI SƠN - CHI NHÁNH TỔNG CÔNG TY PHÁT ĐIỆN 1, Danh mục: Đầu nối ống thẳng). Đơn giá trình (2.600.000 đ) hiện cao hơn 253.6% (+1.864.731 đ). Tổ Thẩm định đề nghị xem xét tham chiếu giá Mua sắm công để tối ưu chi phí.
+- Cơ sở 5 (Thương Mại Điện Tử): Thẩm định viên loại trừ trực tiếp tại Bảng đối chiếu do không tương thích kỹ thuật.
+KẾT LUẬN THẨM ĐỊNH: Đề xuất giá thẩm định phê duyệt chốt là 644.760 đ (Cơ sở: Cơ sở 3: EVN IMIS | Giá trị tiết kiệm dự kiến: 195.524.000 đ).</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr"/>
+      <c r="J26" s="6" t="n">
+        <v>644760</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>64476000</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>195524000</v>
+      </c>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 3: EVN IMIS</t>
         </is>
       </c>
     </row>
@@ -2149,50 +2010,53 @@
           <t>4.82.82.014.GER.00.000</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Cùm cố định ống/ Tube Support Strip, model: MS-TSS-6, 10 Channels, 3/8 inch, 10 mm Tube Size</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Cùm cố định ống/ Tube Support Strip, model: MS-TSS-6, 10 Channels, 3/8 inch, 10 mm Tube Size</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Swagelok/ Đức</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Cùm cố định ống/ Tube Support Strip, model: MS-TSS-6, 10 Channels, 3/8 inch, 10 mm Tube Size - Cùm cố định ống/ Tube Support Strip, model: MS-TSS-6, 10 Channels, 3/8 inch, 10 mm Tube Size</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G27" s="7" t="n">
+      <c r="E27" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="H27" s="7" t="n">
+      <c r="F27" s="6" t="n">
         <v>200000</v>
       </c>
-      <c r="I27" s="7" t="n">
+      <c r="G27" s="6" t="n">
         <v>3000000</v>
       </c>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
-      <c r="L27" s="7" t="n">
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Cùm cố định ống/ Tube Support Strip, model: MS-TSS-6, 10 Channels, 3/8 inch, 10 mm Tube Size (Mã ERP: 4.82.82.014.GER.00.000).
+• Đơn giá trình thẩm định: 200.000 VNĐ (Số lượng: 15 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 80/100 điểm (Hạng A - 4/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 200.000 VNĐ/Cái từ CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (Trang 4 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [4.82.82.014.GER.00.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 200.000 VNĐ/Cái theo HĐ Nhập kho vật tư (QĐ: 1511/2025) theo hóa đơn số 644 ngày 26.09.2025 (ký ngày 2025-11-24 00:00:00, cách đây 10 tháng - trong hạn 12 tháng).
+- Cơ sở 3 (EVN IMIS): Qua rà soát CSDL Hợp đồng mua sắm EVN IMIS theo từ khóa [TSS-6], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL EVN IMIS làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [Tube Support Strip] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 1.067.000 VNĐ/Cái (Nhà thầu Swagelok).
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Cùm cố định ống/ Tube Support Strip, model: MS-TSS-6, 10 Channels, 3/8 inch, 10 mm Tube Size] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 200.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr"/>
+      <c r="J27" s="6" t="n">
         <v>200000</v>
       </c>
-      <c r="M27" s="7" t="n">
+      <c r="K27" s="6" t="n">
         <v>3000000</v>
       </c>
-      <c r="N27" s="7" t="n">
+      <c r="L27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O27" s="6" t="inlineStr"/>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>4.82.82.014.GER.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -2205,14 +2069,9 @@
           <t>5.33.70.184.GER.99.000</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Bộ điều khiển định vị Positioner, Model: TZIDC-V18345- 2020521001</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Bộ điều khiển định vị Positioner:
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Bộ điều khiển định vị Positioner, Model: TZIDC-V18345- 2020521001 - Bộ điều khiển định vị Positioner:
 - Model: TZIDC-V18345- 2020521001
 -Type: Double acting 
 -Sofw.Rev: 3 
@@ -2223,40 +2082,48 @@
 -NSX: ABB</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>ABB/ Đức</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="E28" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="7" t="n">
+      <c r="F28" s="6" t="n">
         <v>85000000</v>
       </c>
-      <c r="I28" s="7" t="n">
+      <c r="G28" s="6" t="n">
         <v>425000000</v>
       </c>
-      <c r="J28" s="6" t="inlineStr"/>
-      <c r="K28" s="6" t="inlineStr"/>
-      <c r="L28" s="7" t="n">
-        <v>85000000</v>
-      </c>
-      <c r="M28" s="7" t="n">
-        <v>425000000</v>
-      </c>
-      <c r="N28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="6" t="inlineStr"/>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>5.33.70.184.GER.99.000 | Thay thế các bộ positioner điều khiển damper gió SA bị xì khí nén của tổ máy S2 | Vật tư được đề xuất trong KHSXKD năm 2026,nhưng phát sinh hư hỏng thêm 2 bộ vượt nhu cầu dự kiến, nên đề xuất mua sắm bổ sung. Tên vật tư được đặt lại theo quy tắc chuẩn hóa.</t>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Bộ điều khiển định vị Positioner, Model: TZIDC-V18345- 2020521001 (Mã ERP: 5.33.70.184.GER.99.000).
+• Đơn giá trình thẩm định: 85.000.000 VNĐ (Số lượng: 5 Bộ).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 85/100 điểm (🟡 Hợp Lý (Nằm trong biên độ giá trung bình thị trường)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 85.000.000 VNĐ/Bộ từ CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (Trang 4 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [5.33.70.184.GER.99.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 85.000.000 VNĐ/Bộ theo HĐ Nhập kho vật tư (HĐ:37/2026) hóa đơn số 00000035 ngày 28.05.2026 (ký ngày 2026-06-03 00:00:00, cách đây 3 tháng - trong hạn 12 tháng).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [TZIDC] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); ghi nhận đơn giá trúng thầu/hợp đồng tham chiếu là 83.484.000 VNĐ/Bộ tại Công ty Nhiệt điện Cần Thơ theo HĐ 31/HĐ-NĐCT-NEWAY (thực hiện cách đây 36 tháng ~ 3 năm - quá 12 tháng).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [TZIDC-V18345- 2020521001] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 102.600.000 VNĐ/Bộ (Nhà thầu ABB).
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Bộ điều khiển định vị Positioner, Model: TZIDC-V18345- 2020521001] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đề xuất duyệt đơn giá thẩm định thống nhất là 83.484.000 VNĐ/Bộ. Tiết kiệm dự toán 7.580.000 VNĐ (-1.8%).</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr"/>
+      <c r="J28" s="6" t="n">
+        <v>83484000</v>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>417420000</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <v>7580000</v>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 3: EVN IMIS</t>
         </is>
       </c>
     </row>
@@ -2269,14 +2136,9 @@
           <t>3.96.13.144.USA.00.000</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Cảm biến nhiệt độ Model: S14405PD3S350B0, Type: RTD PT100 3 Wire</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Cảm biến nhiệt độ - Model: S14405PD3S350B0
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Cảm biến nhiệt độ Model: S14405PD3S350B0, Type: RTD PT100 3 Wire - Cảm biến nhiệt độ - Model: S14405PD3S350B0
 - NSX: MINCO 
 - Element: Platinum 
 - Element length: 6.4 mm 
@@ -2288,40 +2150,48 @@
 - Range: 0 - 260 °C</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Minco/ Mỹ</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G29" s="7" t="n">
+      <c r="E29" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="7" t="n">
+      <c r="F29" s="6" t="n">
         <v>30000000</v>
       </c>
-      <c r="I29" s="7" t="n">
+      <c r="G29" s="6" t="n">
         <v>30000000</v>
       </c>
-      <c r="J29" s="6" t="inlineStr"/>
-      <c r="K29" s="6" t="inlineStr"/>
-      <c r="L29" s="7" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="M29" s="7" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="N29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="6" t="inlineStr"/>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>3.96.13.144.USA.00.000 | BBKT- 1008/2026/VH-VT4_ Kiểm tra, khắc phục cảm biến nhiệt độ số 2 gối chặn BFPT B S2 báo lỗi.Vật tư có trong KH SXKD 2026 (mã KH TXBS.26.562). | Mua sắm dự phòng hết tồn kho thiết bị giám sát quan trọng.</t>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Cảm biến nhiệt độ Model: S14405PD3S350B0, Type: RTD PT100 3 Wire (Mã ERP: 3.96.13.144.USA.00.000).
+• Đơn giá trình thẩm định: 30.000.000 VNĐ (Số lượng: 1 Bộ).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 85/100 điểm (🟡 Hợp Lý (Nằm trong biên độ giá trung bình thị trường)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 30.000.000 VNĐ/Bộ từ CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (Trang 5 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [3.96.13.144.USA.00.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 30.000.000 VNĐ/Bộ theo HĐ Nhập kho vật tư (HĐ:36/2026) theo hóa đơn số 00000842 ngày 15.06.2026 (ký ngày 2026-07-22 00:00:00, cách đây 2 tháng - trong hạn 12 tháng).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [RTD PT100] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); ghi nhận đơn giá trúng thầu/hợp đồng tham chiếu là 33.399.000 VNĐ/Bộ tại Công ty Cổ phần Thủy điện Thác Mơ theo HĐ 31/2024/HĐ-TMP-KHVT (thực hiện cách đây 21 tháng ~ 1.8 năm - quá 12 tháng).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [RTD PT100] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 27.923.445 VNĐ/Bộ.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Cảm biến nhiệt độ Model: S14405PD3S350B0, Type: RTD PT100 3 Wire] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đề xuất duyệt đơn giá thẩm định thống nhất là 27.923.445 VNĐ/Bộ. Tiết kiệm dự toán 2.076.555 VNĐ (-6.9%).</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="6" t="n">
+        <v>27923445</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>27923445</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>2076555</v>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 4: Mua Sắm Công e-GP</t>
         </is>
       </c>
     </row>
@@ -2334,51 +2204,54 @@
           <t>3.96.13.320.USA.00.000</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb. - Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
 NSX: MERRICK</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Merrick/ Mỹ</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G30" s="7" t="n">
+      <c r="E30" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H30" s="7" t="n">
+      <c r="F30" s="6" t="n">
         <v>56105000</v>
       </c>
-      <c r="I30" s="7" t="n">
+      <c r="G30" s="6" t="n">
         <v>112210000</v>
       </c>
-      <c r="J30" s="6" t="inlineStr"/>
-      <c r="K30" s="6" t="inlineStr"/>
-      <c r="L30" s="7" t="n">
-        <v>23000000</v>
-      </c>
-      <c r="M30" s="7" t="n">
-        <v>46000000</v>
-      </c>
-      <c r="N30" s="7" t="n">
-        <v>66210000</v>
-      </c>
-      <c r="O30" s="6" t="inlineStr"/>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>3.96.13.320.USA.00.000 | BBKT- 1033/2026/VH-VT4_ Kiểm tra, khắc phục cảm biến khối lượng than – máy cấp A tổ máy S3 báo sai giá trị.Vật tư không có trong KH SXKD 2026. | Mua sắm dự phòng hết tồn kho thiết bị giám sát quan trọng.</t>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb. (Mã ERP: 3.96.13.320.USA.00.000).
+• Đơn giá trình thẩm định: 56.105.000 VNĐ (Số lượng: 2 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 56.105.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 4 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [3.96.13.320.USA.00.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 92.340.500 VNĐ/Cái theo HĐ Nhập kho vật tư (HĐ: 105/2024) theo hóa đơn số 265 ngày 12.05.2025 (ký ngày 2025-05-13 00:00:00, cách đây 16 tháng ~ 1.3 năm - quá 12 tháng, tốc độ tăng giá bình quân -29.4%/năm so với CPI ~5.0%/năm).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [N39188] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 56.105.500 VNĐ/Cái (Nhà thầu Merrick).
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 56.105.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr"/>
+      <c r="J30" s="6" t="n">
+        <v>56105000</v>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>112210000</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -2391,54 +2264,66 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Bộ đo mức LEVEL TRANSMITTER; Loại: Ultrasonic LT (sóng siêu âm)</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>LEVEL TRANSMITTER Loại: Ultrasonic LT (sóng siêu âm) 
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Bộ đo mức LEVEL TRANSMITTER; Loại: Ultrasonic LT (sóng siêu âm) - LEVEL TRANSMITTER Loại: Ultrasonic LT (sóng siêu âm) 
 Model: LST400 Y0/S15/N1/P6/A1/H1/SC6/B2/CR/M5
 Range: 0.5m to 15m Signal: 4 - 20 mA 
 Supply power: 115 to 230 V AC or 24 V DC.
 NSX: ABB</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>ABB/ Đức</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G31" s="7" t="n">
+      <c r="E31" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="7" t="n">
+      <c r="F31" s="6" t="n">
         <v>189000000</v>
       </c>
-      <c r="I31" s="7" t="n">
+      <c r="G31" s="6" t="n">
         <v>189000000</v>
       </c>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
-      <c r="L31" s="7" t="n">
-        <v>189000000</v>
-      </c>
-      <c r="M31" s="7" t="n">
-        <v>189000000</v>
-      </c>
-      <c r="N31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="6" t="inlineStr"/>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã VT | BBKT- 955/2026/VH-VT4_ Kiểm tra, khắc phục cảm biến báo mức nước tổng kênh tuần hoàn tổ máy S1 báo sai giá trị. | Vật tư không có trong KH SXKD 2026.</t>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Bộ đo mức LEVEL TRANSMITTER; Loại: Ultrasonic LT (sóng siêu âm) - LEVEL TRANSMITTER Loại: Ultrasonic LT (sóng siêu âm) 
+Model: LST400 Y0/S15/N1/P6/A1/H1/SC6/B2/CR/M5
+Range: 0.5m to 15m Signal: 4 - 20 mA 
+Supply power: 115 to 230 V AC or 24 V DC.
+NSX: ABB (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 189.000.000 đ (Số lượng: 1.0 Cái).
+• Đánh giá Chứng cứ Thẩm định: 5/5 cơ sở chứng cứ đã rà soát.
+• Mức độ Hợp lý Đơn giá: 50/100 điểm.
+🔍 Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN:
+- Phân tích Bản chất Kỹ thuật Thiết bị: Vật tư thuộc phân nhóm [Thiết bị Đo lường &amp; Cảm biến Tự động hóa] với thương hiệu/tiêu chuẩn [ABB (Thụy Sĩ/Đức) - Xuất xứ G7/Châu Âu (Tiêu chuẩn kỹ thuật an toàn cao)]. Đây là dòng vật tư linh kiện có yêu cầu kỹ thuật đặc thù, đòi hỏi độ tin cậy và tiêu chuẩn an toàn cao trong vận hành nhà máy nhiệt điện.
+- Đánh giá Tương quan Giá trị Kỹ thuật &amp; Thương mại: Đơn giá trình 189.000.000 đ cao hơn +149.5% so với đơn giá tham chiếu thấp nhất hợp lệ (75.764.141 đ từ Cơ sở 5: Tham khảo TMĐT / Giá Web). Với đặc tính kỹ thuật vật tư hiện tại, mức chênh lệch này vượt quá biên độ an toàn và Tổ Thẩm định đề xuất xem xét điều chỉnh.
+💡 KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO:
+🔴 CẢNH BÁO BẤT THƯỜNG ĐƠN GIÁ: Tổ Thẩm định đề xuất Lãnh đạo/Hội đồng Thẩm định đàm phán điều chỉnh đơn giá phê duyệt về mức 75.764.141 đ căn cứ theo Cơ sở 5: Tham khảo TMĐT / Giá Web (Dự kiến tiết kiệm 113.235.859 đ cho Nhà máy).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đơn giá trình (189,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 5). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG báo giá 193,000,000 đ (+2.1%). Đơn giá trình phù hợp theo quy định lựa chọn mức giá thấp nhất giữa các báo giá hợp lệ.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Vật tư chưa có lịch sử mua sắm/nhập kho trong CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4. Căn cứ đơn giá sẽ được thẩm định và xác định dựa trên Báo giá mới nhận (Khối 1), CSDL IMIS EVN (Khối 3) và Mua Sắm Công (Khối 4).
+- Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 13/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [LST400], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện trong Tập đoàn. Căn cứ đơn giá sẽ được đối chiếu dựa trên CSDL ERP Vĩnh Tân 4 (Khối 2) và Mua Sắm Công (Khối 4).
+- Cơ sở 4 (Mua Sắm Công e-GP): 
+- Cơ sở 5 (Thương Mại Điện Tử): 
+KẾT LUẬN THẨM ĐỊNH: Đề xuất giá thẩm định phê duyệt chốt là 75.764.141 đ (Cơ sở: Cơ sở 5: Tham khảo TMĐT / Giá Web | Giá trị tiết kiệm dự kiến: 113.235.859 đ).</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr"/>
+      <c r="J31" s="6" t="n">
+        <v>75764141</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>75764141</v>
+      </c>
+      <c r="L31" s="6" t="n">
+        <v>113235859</v>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 5: Tham khảo TMĐT / Giá Web</t>
         </is>
       </c>
     </row>
@@ -2451,14 +2336,9 @@
           <t>3.96.11.033.SIN.00.000</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Cảm biến áp suất (Pressure transmitter) Model: 2051CG1A02A1AS5M5D4T1Q4</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>Cảm biến áp suất (Pressure transmitter) 
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Cảm biến áp suất (Pressure transmitter) Model: 2051CG1A02A1AS5M5D4T1Q4 - Cảm biến áp suất (Pressure transmitter) 
 Model: 2051CG1A02A1AS5M5D4T1Q4 
 Output Hart: 4-20mA 
 Supply: 10.5 – 42.4 VDC 
@@ -2466,40 +2346,48 @@
 NSX: Rosemount</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>Rosemount/ Singapore</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G32" s="7" t="n">
+      <c r="E32" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="7" t="n">
+      <c r="F32" s="6" t="n">
         <v>145000000</v>
       </c>
-      <c r="I32" s="7" t="n">
+      <c r="G32" s="6" t="n">
         <v>145000000</v>
       </c>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
-      <c r="L32" s="7" t="n">
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Cảm biến áp suất (Pressure transmitter) Model: 2051CG1A02A1AS5M5D4T1Q4 (Mã ERP: 3.96.11.033.SIN.00.000).
+• Đơn giá trình thẩm định: 145.000.000 VNĐ (Số lượng: 1 Bộ).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 145.000.000 VNĐ/Bộ từ CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (Trang 6 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [3.96.11.033.SIN.00.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 145.000.000 VNĐ/Bộ theo HĐ Nhập kho vật tư (HĐ:20/2026) theo hóa đơn số 00000016 ngày 02.04.2026 (ký ngày 2026-04-13 00:00:00, cách đây 5 tháng - trong hạn 12 tháng).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [VDC] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [2051CG1A02A1AS5M5D4T1Q4] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 156.600.000 VNĐ/Bộ (Nhà thầu Rosemount).
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Cảm biến áp suất (Pressure transmitter) Model: 2051CG1A02A1AS5M5D4T1Q4] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 145.000.000 VNĐ/Bộ.</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr"/>
+      <c r="J32" s="6" t="n">
         <v>145000000</v>
       </c>
-      <c r="M32" s="7" t="n">
+      <c r="K32" s="6" t="n">
         <v>145000000</v>
       </c>
-      <c r="N32" s="7" t="n">
+      <c r="L32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O32" s="6" t="inlineStr"/>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>3.96.11.033.SIN.00.000 | BBKT- 1027/2026/VH-VT4_ Kiểm tra, khắc phục bộ chuyển đổi tín hiệu đo áp suất gió SA tầng F tổ máy S1 báo sai giá trị. | Vật tư không có trong KH SXKD 2026.</t>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -2512,14 +2400,9 @@
           <t>5.33.70.823.SIN.98.000</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Bộ đo áp suất - Differential pressure transmitter with Intergral Manifold, Transmitter model: 2051CD1A02A1AS5 M5D4T1Q4</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Bộ đo áp suất - Differential pressure transmitter with Intergral Manifold, Transmitter model: 2051CD1A02A1AS5 M5D4T1Q4
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Bộ đo áp suất - Differential pressure transmitter with Intergral Manifold, Transmitter model: 2051CD1A02A1AS5 M5D4T1Q4 - Bộ đo áp suất - Differential pressure transmitter with Intergral Manifold, Transmitter model: 2051CD1A02A1AS5 M5D4T1Q4
 Output Hart: 4-20mA 
 Supply: 10.5 – 42.4 VDC 
 CAL: 0 to 600 mmH20) 
@@ -2527,40 +2410,48 @@
 NSX: Rosemount</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Rosemount/ Singapore</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G33" s="7" t="n">
+      <c r="E33" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="7" t="n">
+      <c r="F33" s="6" t="n">
         <v>247000000</v>
       </c>
-      <c r="I33" s="7" t="n">
+      <c r="G33" s="6" t="n">
         <v>247000000</v>
       </c>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
-      <c r="L33" s="7" t="n">
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Bộ đo áp suất (Mã ERP: 5.33.70.823.SIN.98.000).
+• Đơn giá trình thẩm định: 247.000.000 VNĐ (Số lượng: 1 Bộ).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 247.000.000 VNĐ/Bộ từ CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (Trang 6 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [5.33.70.823.SIN.98.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 247.000.000 VNĐ/Bộ theo HĐ Nhập kho vật tư (HĐ: 12/2025) theo hóa đơn số 00000036 ngày 24.03.2025 (ký ngày 2025-03-27 00:00:00, cách đây 18 tháng ~ 1.5 năm - quá 12 tháng, tốc độ tăng giá bình quân 0%/năm so với CPI ~5.0%/năm).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [M5D4T1Q4] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [M5D4T1Q4] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); kết quả đã rà soát e-GP: vật tư đặc thù, không ghi nhận gói thầu mua sắm tương đồng.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Bộ đo áp suất] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 247.000.000 VNĐ/Bộ.</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr"/>
+      <c r="J33" s="6" t="n">
         <v>247000000</v>
       </c>
-      <c r="M33" s="7" t="n">
+      <c r="K33" s="6" t="n">
         <v>247000000</v>
       </c>
-      <c r="N33" s="7" t="n">
+      <c r="L33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="6" t="inlineStr"/>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>5.33.70.823.SIN.98.000 | BBKT- 1013/2026/VH-VT4_ Kiểm tra, khắc phục điểm đo chênh áp đầu hút quạt gió cấp 2B tổ máy S3 báo lỗi. | Vật tư không có trong KH SXKD 2026.</t>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -2573,53 +2464,56 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Công tơ nước dạng cơ, kích thước DN50</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>Công tơ nước dạng cơ, kích thước DN50, 4 lỗ bulong Ø16 ở mỗi đầu bích;
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN50 - Công tơ nước dạng cơ, kích thước DN50, 4 lỗ bulong Ø16 ở mỗi đầu bích;
 Vật liệu: Cast iron;
 Môi chất làm việc: nước sạch (nước khử khoáng);
 Công tơ có giấy chứng nhận hiệu chuẩn.</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>Zenner/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G34" s="7" t="n">
+      <c r="E34" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="7" t="n">
+      <c r="F34" s="6" t="n">
         <v>5001000</v>
       </c>
-      <c r="I34" s="7" t="n">
+      <c r="G34" s="6" t="n">
         <v>5001000</v>
       </c>
-      <c r="J34" s="6" t="inlineStr"/>
-      <c r="K34" s="6" t="inlineStr"/>
-      <c r="L34" s="7" t="n">
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Công tơ nước dạng cơ, kích thước DN50 (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 5.001.000 VNĐ (Số lượng: 1 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 5.001.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 5 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Qua rà soát CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 theo từ khóa [Công tơ nước dạng cơ], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [Công tơ nước dạng cơ] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khóa [Zenner], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL Mua sắm công làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 5 (Thương Mại Điện Tử): Đã tra cứu từ khóa [DN50] trên thị trường Thương mại điện tử / Website nhà cung cấp (Ảnh chụp màn hình web) tại đường link [https://bonphat.vn/dong-ho-nuoc-zenner/?orderby=price] lúc 13:23 ngày 9/9/2026 kèm ảnh chụp màn hình minh chứng niêm yết; ghi nhận mức giá niêm yết công khai tham chiếu là 6.360.000 đ [Giá niêm yết web: 5.300.000 đ; sau khi cộng chi phí vận chuyển quốc tế, thuế NK &amp; hải quan (+20%), giá Landed Cost DDP Vĩnh Tân 4 là 6.360.000 đ]. Đơn giá trình (5.001.000 đ) thấp hơn hoặc tương đương đơn giá thị trường đã tính chi phí nhập cảnh Landed Cost.
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 5.001.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr"/>
+      <c r="J34" s="6" t="n">
         <v>5001000</v>
       </c>
-      <c r="M34" s="7" t="n">
+      <c r="K34" s="6" t="n">
         <v>5001000</v>
       </c>
-      <c r="N34" s="7" t="n">
+      <c r="L34" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O34" s="6" t="inlineStr"/>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Lắp đặt cho đường nước Demi cấp vận hành hệ thống Hydro | Báo cáo số 2558/KTATChưa đề xuất trong KHSXKD.</t>
+      <c r="M34" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -2632,53 +2526,56 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Công tơ nước dạng cơ, kích thước DN15, ren ngoài 2 đầu</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Công tơ nước dạng cơ, kích thước DN15, ren ngoài 2 đầu;
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN15, ren ngoài 2 đầu - Công tơ nước dạng cơ, kích thước DN15, ren ngoài 2 đầu;
 Vật liệu: Cast iron;
 Môi chất làm việc: nước sạch (nước khử khoáng);
 Công tơ có giấy chứng nhận hiệu chuẩn.</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>Zenner/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G35" s="7" t="n">
+      <c r="E35" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H35" s="7" t="n">
+      <c r="F35" s="6" t="n">
         <v>375000</v>
       </c>
-      <c r="I35" s="7" t="n">
+      <c r="G35" s="6" t="n">
         <v>375000</v>
       </c>
-      <c r="J35" s="6" t="inlineStr"/>
-      <c r="K35" s="6" t="inlineStr"/>
-      <c r="L35" s="7" t="n">
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Công tơ nước dạng cơ, kích thước DN15, ren ngoài 2 đầu (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 375.000 VNĐ (Số lượng: 1 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 20/100 điểm (Hạng C - 1/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 375.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 5 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Chưa đối chiếu CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4.
+- Cơ sở 3 (EVN IMIS): Chưa đối chiếu CSDL Hợp đồng mua sắm toàn ngành EVN IMIS.
+- Cơ sở 4 (Mua Sắm Công e-GP): Chưa đối chiếu Cổng Mạng Đấu thầu Quốc gia e-GP.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Công tơ nước dạng cơ, kích thước DN15, ren ngoài 2 đầu] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 375.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr"/>
+      <c r="J35" s="6" t="n">
         <v>375000</v>
       </c>
-      <c r="M35" s="7" t="n">
+      <c r="K35" s="6" t="n">
         <v>375000</v>
       </c>
-      <c r="N35" s="7" t="n">
+      <c r="L35" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O35" s="6" t="inlineStr"/>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Lắp đặt cho đường nước Demi cấp cho phòng thí nghiệm | Báo cáo số 2558/KTATChưa đề xuất trong KHSXKD.</t>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -2691,50 +2588,53 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Đầu chuyển hàn – ren ngoài DN15, vật liệu inox 304</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>Đầu chuyển hàn – ren ngoài DN15, vật liệu inox 304</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>Kungho/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Đầu chuyển hàn – ren ngoài DN15, vật liệu inox 304 - Đầu chuyển hàn – ren ngoài DN15, vật liệu inox 304</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="E36" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="7" t="n">
+      <c r="F36" s="6" t="n">
         <v>28000</v>
       </c>
-      <c r="I36" s="7" t="n">
+      <c r="G36" s="6" t="n">
         <v>56000</v>
       </c>
-      <c r="J36" s="6" t="inlineStr"/>
-      <c r="K36" s="6" t="inlineStr"/>
-      <c r="L36" s="7" t="n">
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Đầu chuyển hàn – ren ngoài DN15, vật liệu inox 304 (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 28.000 VNĐ (Số lượng: 2 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 28.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 5 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Qua rà soát CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 theo từ khóa [Đầu chuyển hàn – ren ngoài DN15], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 3 (EVN IMIS): Qua rà soát CSDL Hợp đồng mua sắm EVN IMIS theo từ khóa [Đầu chuyển hàn – ren ngoài DN15], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL EVN IMIS làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 4 (Mua Sắm Công e-GP): Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khóa [Đầu chuyển hàn], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL Mua sắm công làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Đầu chuyển hàn – ren ngoài DN15, vật liệu inox 304] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 28.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr"/>
+      <c r="J36" s="6" t="n">
         <v>28000</v>
       </c>
-      <c r="M36" s="7" t="n">
+      <c r="K36" s="6" t="n">
         <v>56000</v>
       </c>
-      <c r="N36" s="7" t="n">
+      <c r="L36" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O36" s="6" t="inlineStr"/>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Lắp đặt cho đường nước Demi cấp cho phòng thí nghiệm | Báo cáo số 2558/KTATChưa đề xuất trong KHSXKD.</t>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -2747,50 +2647,49 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Rắc co ren trong DN15, vật liệu inox 304</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Rắc co ren trong DN15, vật liệu inox 304</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>Kungho/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Rắc co ren trong DN15, vật liệu inox 304 - Rắc co ren trong DN15, vật liệu inox 304</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G37" s="7" t="n">
+      <c r="E37" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H37" s="7" t="n">
+      <c r="F37" s="6" t="n">
         <v>104000</v>
       </c>
-      <c r="I37" s="7" t="n">
+      <c r="G37" s="6" t="n">
         <v>208000</v>
       </c>
-      <c r="J37" s="6" t="inlineStr"/>
-      <c r="K37" s="6" t="inlineStr"/>
-      <c r="L37" s="7" t="n">
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 104.000 đ/Bộ (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 230.000 đ/Bộ (HĐ: Nhập kho vật tư (QĐ:1022/2026) theo hóa đơn số 490 ngày 07.07.2026 ngày 2026-07-31. SL: 1 Bộ); Các đợt nhập khác: 606.000 đ, 640.000 đ
+• Cơ sở 3 (EVN IMIS): IMIS EVN: 117.600 đ/Cái (Trung tâm Dịch vụ sửa chữa EVN - Chi nhánh Tập đoàn Điện lực Việt Nam)
+• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Rắc co ren trong DN15, vật liệu inox 304] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 104.000 đ/Bộ.</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr"/>
+      <c r="J37" s="6" t="n">
         <v>104000</v>
       </c>
-      <c r="M37" s="7" t="n">
+      <c r="K37" s="6" t="n">
         <v>208000</v>
       </c>
-      <c r="N37" s="7" t="n">
+      <c r="L37" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O37" s="6" t="inlineStr"/>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Lắp đặt cho đường nước Demi cấp cho phòng thí nghiệm | Báo cáo số 2558/KTATChưa đề xuất trong KHSXKD.</t>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -2803,53 +2702,56 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Công tơ nước dạng cơ, kích thước DN125</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>Công tơ nước dạng cơ, kích thước DN125, 8 lỗ bulong Ø16 ở mỗi đầu bích;
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN125 - Công tơ nước dạng cơ, kích thước DN125, 8 lỗ bulong Ø16 ở mỗi đầu bích;
 Vật liệu: Cast iron;
 Môi chất làm việc: nước sạch (nước khử khoáng);
 Công tơ có giấy chứng nhận hiệu chuẩn.</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>Zenner/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G38" s="7" t="n">
+      <c r="E38" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="7" t="n">
+      <c r="F38" s="6" t="n">
         <v>9660000</v>
       </c>
-      <c r="I38" s="7" t="n">
+      <c r="G38" s="6" t="n">
         <v>19320000</v>
       </c>
-      <c r="J38" s="6" t="inlineStr"/>
-      <c r="K38" s="6" t="inlineStr"/>
-      <c r="L38" s="7" t="n">
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Công tơ nước dạng cơ, kích thước DN125 (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 9.660.000 VNĐ (Số lượng: 2 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 9.660.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 5 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Qua rà soát CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 theo từ khóa [Công tơ nước dạng cơ], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [Công tơ nước dạng] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [Công tơ nước dạng cơ, kích thước DN125] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); kết quả đã rà soát e-GP: vật tư đặc thù, không ghi nhận gói thầu mua sắm tương đồng.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Công tơ nước dạng] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 9.660.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr"/>
+      <c r="J38" s="6" t="n">
         <v>9660000</v>
       </c>
-      <c r="M38" s="7" t="n">
+      <c r="K38" s="6" t="n">
         <v>19320000</v>
       </c>
-      <c r="N38" s="7" t="n">
+      <c r="L38" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O38" s="6" t="inlineStr"/>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Lắp đặt cho đường nước Demi cấp vận hành hệ thống hoàn nguyên CPP 4-4MR | Báo cáo số 2558/KTATChưa đề xuất trong KHSXKD.</t>
+      <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -2862,53 +2764,56 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Công tơ nước dạng cơ, kích thước DN150</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Công tơ nước dạng cơ, kích thước DN150, 8 lỗ bulong Ø20 ở mỗi đầu bích;
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN150 - Công tơ nước dạng cơ, kích thước DN150, 8 lỗ bulong Ø20 ở mỗi đầu bích;
 Vật liệu: Cast iron;
 Môi chất làm việc: nước sạch (nước khử khoáng);
 Công tơ có giấy chứng nhận hiệu chuẩn.</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>Zenner/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G39" s="7" t="n">
+      <c r="E39" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="H39" s="7" t="n">
+      <c r="F39" s="6" t="n">
         <v>13800000</v>
       </c>
-      <c r="I39" s="7" t="n">
+      <c r="G39" s="6" t="n">
         <v>82800000</v>
       </c>
-      <c r="J39" s="6" t="inlineStr"/>
-      <c r="K39" s="6" t="inlineStr"/>
-      <c r="L39" s="7" t="n">
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Công tơ nước dạng cơ, kích thước DN150 (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 13.800.000 VNĐ (Số lượng: 6 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 40/100 điểm (Hạng C - 2/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 13.800.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 5 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [Công tơ nước dạng cơ] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; kết quả đã đối soát CSDL ERP: 0 bản ghi phù hợp (vật tư chưa từng có lịch sử nhập kho nội bộ nhà máy Vĩnh Tân 4).
+- Cơ sở 3 (EVN IMIS): Chưa đối chiếu CSDL Hợp đồng mua sắm toàn ngành EVN IMIS.
+- Cơ sở 4 (Mua Sắm Công e-GP): Chưa đối chiếu Cổng Mạng Đấu thầu Quốc gia e-GP.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Công tơ nước dạng cơ, kích thước DN150] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 13.800.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr"/>
+      <c r="J39" s="6" t="n">
         <v>13800000</v>
       </c>
-      <c r="M39" s="7" t="n">
+      <c r="K39" s="6" t="n">
         <v>82800000</v>
       </c>
-      <c r="N39" s="7" t="n">
+      <c r="L39" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O39" s="6" t="inlineStr"/>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Lắp đặt cho đường nước Demi cấp vận hành cho lò hơi, tuabin 3 tổ máy | Báo cáo số 2558/KTATChưa đề xuất trong KHSXKD.</t>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -2921,53 +2826,56 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Công tơ nước dạng cơ, kích thước DN200 PN16</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>Công tơ nước dạng cơ, kích thước DN200 PN16, 12 lỗ bulong Ø20 ở mỗi đầu bích;
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN200 PN16 - Công tơ nước dạng cơ, kích thước DN200 PN16, 12 lỗ bulong Ø20 ở mỗi đầu bích;
 Vật liệu: Cast iron;
 Môi chất làm việc: nước sạch (nước khử khoáng);
 Công tơ có giấy chứng nhận hiệu chuẩn.</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>Zenner/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G40" s="7" t="n">
+      <c r="E40" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H40" s="7" t="n">
+      <c r="F40" s="6" t="n">
         <v>14000000</v>
       </c>
-      <c r="I40" s="7" t="n">
+      <c r="G40" s="6" t="n">
         <v>28000000</v>
       </c>
-      <c r="J40" s="6" t="inlineStr"/>
-      <c r="K40" s="6" t="inlineStr"/>
-      <c r="L40" s="7" t="n">
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Công tơ nước dạng cơ, kích thước DN200 PN16 (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 14.000.000 VNĐ (Số lượng: 2 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 60/100 điểm (Hạng B - 3/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 14.000.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 5 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Chưa đối chiếu CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4.
+- Cơ sở 3 (EVN IMIS): Chưa đối chiếu CSDL Hợp đồng mua sắm toàn ngành EVN IMIS.
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [zenner] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 21.708.000 VNĐ/Cái (Nhà thầu Zenner).
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Công tơ nước dạng cơ, kích thước DN200 PN16] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 14.000.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr"/>
+      <c r="J40" s="6" t="n">
         <v>14000000</v>
       </c>
-      <c r="M40" s="7" t="n">
+      <c r="K40" s="6" t="n">
         <v>28000000</v>
       </c>
-      <c r="N40" s="7" t="n">
+      <c r="L40" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O40" s="6" t="inlineStr"/>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Lắp đặt cho đường nước Demi cấp vận hành hệ thống xử lý nước VT4-4MR | Báo cáo số 2558/KTATChưa đề xuất trong KHSXKD.</t>
+      <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -2980,53 +2888,56 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Công tơ nước dạng cơ, kích thước DN100</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Công tơ nước dạng cơ, kích thước DN100, 8 lỗ bulong Ø16 ở mỗi đầu bích;
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN100 - Công tơ nước dạng cơ, kích thước DN100, 8 lỗ bulong Ø16 ở mỗi đầu bích;
 Vật liệu: Cast iron;
 Môi chất làm việc: nước sạch (nước dịch vụ);
 Công tơ có giấy chứng nhận hiệu chuẩn.</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>Zenner/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G41" s="7" t="n">
+      <c r="E41" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="7" t="n">
+      <c r="F41" s="6" t="n">
         <v>6726000</v>
       </c>
-      <c r="I41" s="7" t="n">
+      <c r="G41" s="6" t="n">
         <v>6726000</v>
       </c>
-      <c r="J41" s="6" t="inlineStr"/>
-      <c r="K41" s="6" t="inlineStr"/>
-      <c r="L41" s="7" t="n">
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Công tơ nước dạng cơ, kích thước DN100 (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 6.726.000 VNĐ (Số lượng: 1 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 6.726.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 5 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [Công tơ nước dạng cơ] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; kết quả đã đối soát CSDL ERP: 0 bản ghi phù hợp (vật tư chưa từng có lịch sử nhập kho nội bộ nhà máy Vĩnh Tân 4).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [Công tơ nước] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [DN100 (D114)] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 9.774.000 VNĐ/Cái (Nhà thầu Zenner).
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Công tơ nước dạng cơ, kích thước DN100] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 6.726.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr"/>
+      <c r="J41" s="6" t="n">
         <v>6726000</v>
       </c>
-      <c r="M41" s="7" t="n">
+      <c r="K41" s="6" t="n">
         <v>6726000</v>
       </c>
-      <c r="N41" s="7" t="n">
+      <c r="L41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O41" s="6" t="inlineStr"/>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Lắp đặt cho đường nước Service cấp bù áp nước chữa cháy | Báo cáo số 2558/KTATChưa đề xuất trong KHSXKD.</t>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -3039,53 +2950,56 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Cảm biến đo lưu lượng siêu âm
-(Ultrasonic Flowmeter Transducer)</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>Cảm biến đo lưu lượng siêu âm (Ultrasonic Flowmeter Transducer)
+(Ultrasonic Flowmeter Transducer) - Cảm biến đo lưu lượng siêu âm (Ultrasonic Flowmeter Transducer)
 Model: LTE1-B
 NSX: Jain Technology</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>Jain/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G42" s="7" t="n">
+      <c r="E42" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H42" s="7" t="n">
+      <c r="F42" s="6" t="n">
         <v>162000000</v>
       </c>
-      <c r="I42" s="7" t="n">
+      <c r="G42" s="6" t="n">
         <v>324000000</v>
       </c>
-      <c r="J42" s="6" t="inlineStr"/>
-      <c r="K42" s="6" t="inlineStr"/>
-      <c r="L42" s="7" t="n">
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Cảm biến đo lưu lượng siêu âm (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 162.000.000 VNĐ (Số lượng: 2 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 162.000.000 VNĐ/Cái từ CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (Trang 6 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Qua rà soát CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 theo từ khóa [Cảm biến đo lưu lượng siêu âm], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [LTE1] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khóa [Ultrasonic Flowmeter Transducer], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL Mua sắm công làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Cảm biến đo lưu lượng siêu âm] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 162.000.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr"/>
+      <c r="J42" s="6" t="n">
         <v>162000000</v>
       </c>
-      <c r="M42" s="7" t="n">
+      <c r="K42" s="6" t="n">
         <v>324000000</v>
       </c>
-      <c r="N42" s="7" t="n">
+      <c r="L42" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O42" s="6" t="inlineStr"/>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã VT | BBKT- 1041/2026/VH-VT4_ Kiểm tra, khắc phục thiết bị giám sát lưu lượng bơm nước biển  S2 báo lỗi.Vật tư không có trong KH SXKD 2026. | Vật tư đề xuất nâng cấp tương đương.</t>
+      <c r="M42" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -3098,53 +3012,56 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Hợp chất Silicone tiếp âm và bôi trơn(Silicone Compound)</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>Hợp chất Silicone tiếp âm và bôi trơn(Silicone Compound)
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Hợp chất Silicone tiếp âm và bôi trơn(Silicone Compound) - Hợp chất Silicone tiếp âm và bôi trơn(Silicone Compound)
 Applicatinon: Sealant and Lubricant
 Cautinon: Mix thoroughly before use
 NSX: Jain Technology</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>Jain/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>Hộp</t>
         </is>
       </c>
-      <c r="G43" s="7" t="n">
+      <c r="E43" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="H43" s="7" t="n">
+      <c r="F43" s="6" t="n">
         <v>1300000</v>
       </c>
-      <c r="I43" s="7" t="n">
+      <c r="G43" s="6" t="n">
         <v>5200000</v>
       </c>
-      <c r="J43" s="6" t="inlineStr"/>
-      <c r="K43" s="6" t="inlineStr"/>
-      <c r="L43" s="7" t="n">
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Hợp chất Silicone tiếp âm và bôi trơn(Silicone Compound) (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 1.300.000 VNĐ (Số lượng: 4 Hộp).
+• Đánh giá Chứng cứ Thẩm định: Đạt 80/100 điểm (Hạng A - 4/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 1.300.000 VNĐ/Hộp từ CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (Trang 7 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [Hợp chất Silicone tiếp âm và bôi trơn(Silicone Compound)] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; kết quả đã đối soát CSDL ERP: 0 bản ghi phù hợp (vật tư chưa từng có lịch sử nhập kho nội bộ nhà máy Vĩnh Tân 4).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [Hợp chất Silicone] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [Acoustic Silicone] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); kết quả đã rà soát e-GP: vật tư đặc thù, không ghi nhận gói thầu mua sắm tương đồng.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Hợp chất Silicone tiếp âm và bôi trơn(Silicone Compound)] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 1.300.000 VNĐ/Hộp. Tuy nhiên cần làm rõ bao nhiêu kg hoặc bao nhiêu ml trong 1 hộp.</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr"/>
+      <c r="J43" s="6" t="n">
         <v>1300000</v>
       </c>
-      <c r="M43" s="7" t="n">
+      <c r="K43" s="6" t="n">
         <v>5200000</v>
       </c>
-      <c r="N43" s="7" t="n">
+      <c r="L43" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O43" s="6" t="inlineStr"/>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã VT | BBKT- 1041/2026/VH-VT4_ Kiểm tra, khắc phục thiết bị giám sát lưu lượng bơm nước biển  S2 báo lỗi.Vật tư không có trong KH SXKD 2026. |</t>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -3157,53 +3074,56 @@
           <t>5.33.85.167.JPN.00.000</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Đầu dò Oxy thừa Zirconia/ Zirconia Detector, Model: NS-3000, Style: S2</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>Đầu dò Oxy thừa Zirconia/ Zirconia Detector, Model: NS-3000, Style: S2
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Đầu dò Oxy thừa Zirconia/ Zirconia Detector, Model: NS-3000, Style: S2 - Đầu dò Oxy thừa Zirconia/ Zirconia Detector, Model: NS-3000, Style: S2
 - Suffix: -4-1-X3-2-2-2-1-1
 - AMB.Temp: -20 ~ 150 ºC
 NSX: Horiba</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>Horiba/ Nhật Bản</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G44" s="7" t="n">
+      <c r="E44" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="7" t="n">
+      <c r="F44" s="6" t="n">
         <v>669500000</v>
       </c>
-      <c r="I44" s="7" t="n">
+      <c r="G44" s="6" t="n">
         <v>669500000</v>
       </c>
-      <c r="J44" s="6" t="inlineStr"/>
-      <c r="K44" s="6" t="inlineStr"/>
-      <c r="L44" s="7" t="n">
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Đầu dò Oxy thừa Zirconia/ Zirconia Detector, Model: NS-3000, Style: S2 (Mã ERP: 5.33.85.167.JPN.00.000).
+• Đơn giá trình thẩm định: 669.500.000 VNĐ (Số lượng: 1 Bộ).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 30/100 điểm (🔴 Chưa Hợp Lý (Đơn giá trình cao hơn &gt;20% so với mốc giá tham chiếu)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 669.500.000 VNĐ/Bộ từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 6 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [5.33.85.167.JPN.00.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 526.506.500 VNĐ/Bộ theo HĐ Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000001 ngày 16.01.2026 (ký ngày 2026-02-05 00:00:00, cách đây 7 tháng - trong hạn 12 tháng).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [NS-3000] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [NS-3000] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 736.965.900 VNĐ/Bộ (Nhà thầu Horiba).
+- Cơ sở 5 (Thương Mại Điện Tử): Đã tra cứu từ khóa [AMB] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 669.500.000 VNĐ/Bộ.</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr"/>
+      <c r="J44" s="6" t="n">
         <v>669500000</v>
       </c>
-      <c r="M44" s="7" t="n">
+      <c r="K44" s="6" t="n">
         <v>669500000</v>
       </c>
-      <c r="N44" s="7" t="n">
+      <c r="L44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O44" s="6" t="inlineStr"/>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>5.33.85.167.JPN.00.000 | BBKT- 1159/2026/VH-VT4_ Kiểm tra, khắc phục thiết bị đo nồng độ oxy thừa trong khói thoát lò hơi nhánh 1A tổ máy S1 báo lỗi.Vật tư có trong KH SXKD 2026 (mã KH:TX.26.2202, 01 bộ). | Mua sắm dự phòng hết tồn kho thiết bị giám sát quan trọng.</t>
+      <c r="M44" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -3216,14 +3136,9 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD) - Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)
 Model: MA3145-230-2-R
 - Điện áp hoạt động tối đa (Max working voltage): ≥ 270 VAC.
 - Điện áp định mức (Voltage rating): 230 VAC.
@@ -3231,40 +3146,48 @@
 NSX: Cooper Crouse-Hinds MTL / Eaton</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>Eaton/ Slovenia</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G45" s="7" t="n">
+      <c r="E45" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="7" t="n">
+      <c r="F45" s="6" t="n">
         <v>35000000</v>
       </c>
-      <c r="I45" s="7" t="n">
+      <c r="G45" s="6" t="n">
         <v>105000000</v>
       </c>
-      <c r="J45" s="6" t="inlineStr"/>
-      <c r="K45" s="6" t="inlineStr"/>
-      <c r="L45" s="7" t="n">
-        <v>35000000</v>
-      </c>
-      <c r="M45" s="7" t="n">
-        <v>105000000</v>
-      </c>
-      <c r="N45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="6" t="inlineStr"/>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã VT | BBKT- 1089/2026/VH-VT4_ Kiểm tra, khắc phục các con đo lưu lượng nước biển S3 không. hiển thị. | Vật tư không có trong KH SXKD 2026.</t>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 35.000.000 VNĐ (Số lượng: 3 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 30/100 điểm (🔴 Chưa Hợp Lý (Đơn giá trình cao hơn &gt;20% so với mốc giá tham chiếu)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 35.000.000 VNĐ/Cái từ CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (Trang 7 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Qua rà soát CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 theo từ khóa [Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [MA3145] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khóa [MTL], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL Mua sắm công làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [SPD] trên thị trường TMĐT / Website nhà cung cấp (Ảnh chụp màn hình web) tại link [https://vxb.com/products/industrial-surge-protector-ma3145-230-2-r-230v-ac?srsltid=AfmBOopEhi9Lkdsb_EPwJJlLIDGRGUVGGC4dgWQ-JeTAw6mec1pbe0ma]; ghi nhận đơn giá niêm yết công khai tham chiếu là 21.609.600 VNĐ/Cái [Giá web gốc: 18.008.000 đ; sau khi tính phụ thu chi phí vận chuyển quốc tế &amp; thuế nhập khẩu (Landed Cost DDP Vĩnh Tân 4 +20%), đơn giá tham chiếu đề xuất là 21.609.600 đ].
+KẾT LUẬN THẨM ĐỊNH: Đề xuất duyệt đơn giá thẩm định thống nhất là 21.609.600 VNĐ/Cái. Tiết kiệm dự toán 40.171.200 VNĐ (-38.3%).</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr"/>
+      <c r="J45" s="6" t="n">
+        <v>21609600</v>
+      </c>
+      <c r="K45" s="6" t="n">
+        <v>64828800</v>
+      </c>
+      <c r="L45" s="6" t="n">
+        <v>40171200</v>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 5: Tham khảo TMĐT / Giá Web</t>
         </is>
       </c>
     </row>
@@ -3277,52 +3200,62 @@
           <t>3.96.13.071.KOR.00.000</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Dây tín hiệu quang cho cảm biến phát hiện ngọn lửa</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>Dây tín hiệu quang cho cảm biến phát hiện ngọn lửa, Model cảm biến: NBFS-FC2000, Length: 2825 mm, Sensor MTG Size: PT1"M, Material: Stainless Steel
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Dây tín hiệu quang cho cảm biến phát hiện ngọn lửa - Dây tín hiệu quang cho cảm biến phát hiện ngọn lửa, Model cảm biến: NBFS-FC2000, Length: 2825 mm, Sensor MTG Size: PT1"M, Material: Stainless Steel
 Dây tín hiệu quang cho cảm biến phát hiện ngọn lửa (Model cảm biến phát hiện ngọn lửa: NBFS-FC2000). - Overall dimension: 20Ø*2825mm with 80Ø*8t Flange - Length: 2825 mm - Sensor MTG Size: PT1"M - Material: Stainless Steel - Fiber Optic Conductor: + Material: Glass Optical Multi Component + Clad Diameter: 0.025mm ent + Bundle Diameter: 3mm + Operating Temperature: Max. 400°C(750°F) - OD tube: Flexible tube 3/8’’ - Detail “C” - Lens: + Material : Quartz + Operating Temperature: Max. 1680°C 
 NSX: Nambukeng</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>Nambukeng/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>Sợi</t>
         </is>
       </c>
-      <c r="G46" s="7" t="n">
+      <c r="E46" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H46" s="7" t="n">
+      <c r="F46" s="6" t="n">
         <v>135000000</v>
       </c>
-      <c r="I46" s="7" t="n">
+      <c r="G46" s="6" t="n">
         <v>270000000</v>
       </c>
-      <c r="J46" s="6" t="inlineStr"/>
-      <c r="K46" s="6" t="inlineStr"/>
-      <c r="L46" s="7" t="n">
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Dây tín hiệu quang cho cảm biến phát hiện ngọn lửa (Mã ERP: 3.96.13.071.KOR.00.000).
+• Đơn giá trình thẩm định: 135.000.000 VNĐ (Số lượng: 2 Sợi).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 135.000.000 VNĐ/Sợi từ CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (Trang 8 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [3.96.13.071.KOR.00.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 135.000.000 VNĐ/Sợi theo HĐ Nhập kho vật tư (HĐ: 88/2025) theo hóa đơn số 00000977 ngày 29.10.2025 (ký ngày 2025-11-06 00:00:00, cách đây 10 tháng - trong hạn 12 tháng).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [NB-DFS30S] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [DFS30S] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); kết quả đã rà soát e-GP: vật tư đặc thù, không ghi nhận gói thầu mua sắm tương đồng.
+- Cơ sở 5 (Thương Mại Điện Tử): Đã tra cứu tại https://www.nambukeng.co.kr/page_UGhL00, không có giá niêm yet. Dựa vào thông tin trên trang web bạn đang xem, không có thông tin về giá cho sản phẩm ống dẫn hướng (Inner Guide Pipe Assembly) này.
+Vì đây là thiết bị công nghiệp chuyên dụng (chịu nhiệt độ cao lên tới 1680°C và sử dụng cáp quang học), giá cả thường không được niêm yết công khai mà sẽ phụ thuộc vào các yếu tố như:
+Chiều dài yêu cầu: Bảng thông số có ghi rõ chiều dài ống là do khách hàng yêu cầu ("L=Request").
+Mã sản phẩm: Sự khác biệt về kích thước mặt bích và trọng lượng giữa mẫu NBFS-FC500 và NBFS-FC2000.
+Số lượng đặt hàng.
+Để có báo giá chính xác nhất, bạn cần liên hệ trực tiếp với nhà sản xuất NAMBUK ENG qua thông tin liên hệ ở góc trái trang web:
+Điện thoại: 055-231-9227
+Email: nambuk@nambukeng.co.kr
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 135.000.000 VNĐ/Sợi.</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr"/>
+      <c r="J46" s="6" t="n">
         <v>135000000</v>
       </c>
-      <c r="M46" s="7" t="n">
+      <c r="K46" s="6" t="n">
         <v>270000000</v>
       </c>
-      <c r="N46" s="7" t="n">
+      <c r="L46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O46" s="6" t="inlineStr"/>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>3.96.13.071.KOR.00.000 | BBKT- 1103/2026/VH-VT4_ Kiểm tra, khắc phục bộ giám sát ngọn lửa vòi than E1, E3 – S2 bị lỗi.  | Vật tư có trong KH SXKD 2026 (mã TX.26.2210, 01 sợi).</t>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -3335,54 +3268,53 @@
           <t>3.34.40.009.IND.00.000</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Công tắc lưu lượng (Flow Switch)</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>Công tắc lưu lượng (Flow Switch)
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Công tắc lưu lượng (Flow Switch) - Công tắc lưu lượng (Flow Switch)
 Model: WP/FS-25VFL
 Switch : SPDT Snap Acting Micro
 Rating : 5A 250VAC 
 NSX: Dag Process Instruments Pvt. Ltd</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>Dag Process Instruments Pvt. Ltd/ Ấn Độ</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G47" s="7" t="n">
+      <c r="E47" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="7" t="n">
+      <c r="F47" s="6" t="n">
         <v>38000000</v>
       </c>
-      <c r="I47" s="7" t="n">
+      <c r="G47" s="6" t="n">
         <v>38000000</v>
       </c>
-      <c r="J47" s="6" t="inlineStr"/>
-      <c r="K47" s="6" t="inlineStr"/>
-      <c r="L47" s="7" t="n">
-        <v>38000000</v>
-      </c>
-      <c r="M47" s="7" t="n">
-        <v>38000000</v>
-      </c>
-      <c r="N47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="6" t="inlineStr"/>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã VT | BBKT- 1122/2026/VH-VT4_ Kiểm tra, lỗi tín hiệu lưu lượng gió chèn 1B – ESP -  S1 báo lỗi. | Vật tư không có trong KH SXKD 2026.</t>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 38.000.000 đ/Cái (CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 32.500.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 12/2025) theo hóa đơn số 00000036 ngày 24.03.2025 ngày 2025-03-27. SL: 1 Cái)
+• Cơ sở 3 (EVN IMIS): IMIS EVN: 5.365.000 đ/Cái (GENCO1 - Công ty Nhiệt Điện Nghi Sơn)
+• Cơ sở 4 (Mua Sắm Công e-GP): e-GP MSC: 2.712.960 đ/Cái (Kết quả trúng thầu)
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 2.712.960 đ/Cái.</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr"/>
+      <c r="J47" s="6" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="K47" s="6" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="L47" s="6" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -3395,14 +3327,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Thiết bị đo lưu lượng (Flow Transmitter): - Model: 2051CD2A02A1AS5M5D4T1C1Q4</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>Thiết bị đo lưu lượng (Flow Transmitter): - Model: 2051CD2A02A1AS5M5D4T1C1Q4
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Thiết bị đo lưu lượng (Flow Transmitter): - Model: 2051CD2A02A1AS5M5D4T1C1Q4 - Thiết bị đo lưu lượng (Flow Transmitter): - Model: 2051CD2A02A1AS5M5D4T1C1Q4
 Output Hart: 4-20mA 
 Supply: 10.5 – 42.4 VDC 
 CAL: 0 to 1470,24 mmH20) 
@@ -3410,40 +3337,48 @@
 NSX: Rosemount</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>Rosemount/ Singapore</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G48" s="7" t="n">
+      <c r="E48" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H48" s="7" t="n">
+      <c r="F48" s="6" t="n">
         <v>230000000</v>
       </c>
-      <c r="I48" s="7" t="n">
+      <c r="G48" s="6" t="n">
         <v>230000000</v>
       </c>
-      <c r="J48" s="6" t="inlineStr"/>
-      <c r="K48" s="6" t="inlineStr"/>
-      <c r="L48" s="7" t="n">
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Thiết bị đo lưu lượng (Flow Transmitter): (Mã ERP: 0).
+• Đơn giá trình thẩm định: 230.000.000 VNĐ (Số lượng: 1 Bộ).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 230.000.000 VNĐ/Bộ từ CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (Trang 9 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Qua rà soát CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 theo từ khóa [0], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [2051CD2A02A1AS5M5D4T] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [Rosemount] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 345.600.000 VNĐ/Bộ (Nhà thầu Emerson).
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [2051CD2A02A1AS5M5D4T] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 230.000.000 VNĐ/Bộ.</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr"/>
+      <c r="J48" s="6" t="n">
         <v>230000000</v>
       </c>
-      <c r="M48" s="7" t="n">
+      <c r="K48" s="6" t="n">
         <v>230000000</v>
       </c>
-      <c r="N48" s="7" t="n">
+      <c r="L48" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O48" s="6" t="inlineStr"/>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>5.33.70.894.SIN.00.000 | BBKT- 1104/2026/VH-VT4_ Kiểm tra, khắc phục điểm đo lưu lượng gió cấp 2A tổ máy S2 báo lỗi.  | Vật tư không có trong KH SXKD 2026.</t>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -3456,14 +3391,9 @@
           <t>3.96.13.165.KOR.00.000</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Cảm biến tiệm cận/proximity sensor</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Cảm biến tiệm cận/proximity sensor
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Cảm biến tiệm cận/proximity sensor - Cảm biến tiệm cận/proximity sensor
 - Model: PR30-10AC
 Đường kính cạnh phát hiện: 30mm
 - Điện áp hoạt động: 100-240 Vac
@@ -3471,40 +3401,48 @@
 - Protection: IP67</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>Autonics/ China</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G49" s="7" t="n">
+      <c r="E49" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H49" s="7" t="n">
+      <c r="F49" s="6" t="n">
         <v>1219000</v>
       </c>
-      <c r="I49" s="7" t="n">
+      <c r="G49" s="6" t="n">
         <v>2438000</v>
       </c>
-      <c r="J49" s="6" t="inlineStr"/>
-      <c r="K49" s="6" t="inlineStr"/>
-      <c r="L49" s="7" t="n">
-        <v>1219000</v>
-      </c>
-      <c r="M49" s="7" t="n">
-        <v>2438000</v>
-      </c>
-      <c r="N49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="6" t="inlineStr"/>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>3.96.13.165.KOR.00.000 | Sửa chữa Tời điện số 15 tấn A Khu vực máy nghiền S3 theo BBKT 675/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương, kích thước theo file BBKT đính kèm</t>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Cảm biến tiệm cận/proximity sensor (Mã ERP: 3.96.13.165.KOR.00.000).
+• Đơn giá trình thẩm định: 1.219.000 VNĐ (Số lượng: 2 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 30/100 điểm (🔴 Chưa Hợp Lý (Đơn giá trình cao hơn &gt;20% so với mốc giá tham chiếu)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 1.219.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 6 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [3.96.13.165.KOR.00.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 598.000 VNĐ/Cái theo HĐ Nhập kho vật tư (HĐ:123/2022) theo hóa đơn số 993, 994 ngày 26.12.2022 (ký ngày 2022-12-27 00:00:00, cách đây 45 tháng ~ 3.8 năm - quá 12 tháng, tốc độ tăng giá bình quân 27.7%/năm so với CPI ~5.0%/năm).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [PR30-10AC] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); ghi nhận đơn giá trúng thầu/hợp đồng tham chiếu là 911.127 VNĐ/Cái tại Công ty Nhiệt điện Mông Dương theo HĐ 25/2024/MS_LG (thực hiện cách đây 30 tháng ~ 2.5 năm - quá 12 tháng).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [Autonics] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 382.320 VNĐ/Cái (Nhà thầu Autonics).
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [PR30-10AC] trên thị trường TMĐT / Website nhà cung cấp (Ảnh chụp màn hình web) tại link [https://codienhaiau.com/product/cam-bien-tiem-can-autonics-pr30-10ac/?gad_source=1&amp;gad_campaignid=1706335864&amp;gbraid=0AAAAAC85AUTUiMQTlpM5INcrwVMXyjNgE&amp;gclid=Cj0KCQjwh4TVBhCWARIsAG0czmrEBf0rCtRZxyppABKTkeZNdnQbQjEdU_MosKpjMQgAV1w4sHqu_DUaAslmEALw_wcB]; ghi nhận đơn giá niêm yết công khai tham chiếu là 627.600 VNĐ/Cái [Giá web gốc: 523.000 đ; sau khi tính phụ thu chi phí vận chuyển quốc tế &amp; thuế nhập khẩu (Landed Cost DDP Vĩnh Tân 4 +20%), đơn giá tham chiếu đề xuất là 627.600 đ].
+KẾT LUẬN THẨM ĐỊNH: Đề xuất duyệt đơn giá thẩm định thống nhất là 911.127 VNĐ/Cái. Tiết kiệm dự toán 615.746 VNĐ (-25.3%).</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr"/>
+      <c r="J49" s="6" t="n">
+        <v>911127</v>
+      </c>
+      <c r="K49" s="6" t="n">
+        <v>1822254</v>
+      </c>
+      <c r="L49" s="6" t="n">
+        <v>615746</v>
+      </c>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 3: EVN IMIS</t>
         </is>
       </c>
     </row>
@@ -3517,14 +3455,9 @@
           <t>3.96.13.114.KOR.99.000</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Cảm biến tiệm cận/proximity sensor</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>Cảm biến tiệm cận/proximity sensor
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Cảm biến tiệm cận/proximity sensor - Cảm biến tiệm cận/proximity sensor
 - Model: PR18-8AO
 - Đường kính đầu dò: 18mm
 - Điện áp hoạt động: 100-240 Vac
@@ -3532,40 +3465,53 @@
 - Protection: IP67</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>Autonics/ China</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G50" s="7" t="n">
+      <c r="E50" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="7" t="n">
+      <c r="F50" s="6" t="n">
         <v>1150000</v>
       </c>
-      <c r="I50" s="7" t="n">
+      <c r="G50" s="6" t="n">
         <v>1150000</v>
       </c>
-      <c r="J50" s="6" t="inlineStr"/>
-      <c r="K50" s="6" t="inlineStr"/>
-      <c r="L50" s="7" t="n">
-        <v>1150000</v>
-      </c>
-      <c r="M50" s="7" t="n">
-        <v>1150000</v>
-      </c>
-      <c r="N50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="6" t="inlineStr"/>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>3.96.13.114.KOR.99.000 | Sửa chữa Tời điện số 15 tấn A Khu vực máy nghiền S3 theo BBKT 675/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Cảm biến tiệm cận/proximity sensor (Mã ERP: 3.96.13.114.KOR.99.000).
+• Đơn giá trình thẩm định: 1.150.000 VNĐ (Số lượng: 1 Bộ).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 30/100 điểm (🔴 Chưa Hợp Lý (Đơn giá trình cao hơn &gt;20% so với mốc giá tham chiếu)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 1.150.000 VNĐ/Bộ từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 7 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [3.96.13.114.KOR.99.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 598.667 VNĐ/Bộ theo HĐ Nhập kho vật tư (HĐ:136/2021) theo hóa đơn số 240 ngày 19.04.2022 (ký ngày 2022-04-20 00:00:00, cách đây 53 tháng ~ 4.4 năm - quá 12 tháng, tốc độ tăng giá bình quân 20.9%/năm so với CPI ~5.0%/năm).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [PR18-8AO] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); ghi nhận đơn giá trúng thầu/hợp đồng tham chiếu là 589.722 VNĐ/Bộ tại Công ty TNHH MTV Thủy điện Trung Sơn theo HĐ 30/204/HĐHH-TĐTS (thực hiện cách đây 26 tháng ~ 2.2 năm - quá 12 tháng).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [PR18-8AO] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 807.840 VNĐ/Bộ (Nhà thầu Autonics).
+- Cơ sở 5 (Thương Mại Điện Tử): Đã tra cứu từ khóa [Cảm biến tiệm cận/proximity sensor - Cảm biến tiệm cận/proximity sensor
+- Model: PR18-8AO
+- Đường kính đầu dò: 18mm
+- Điện áp hoạt động: 100-240 Vac
+- Ngõ ra điều khiển: NO
+- Protection: IP67] trên thị trường Thương mại điện tử / Website nhà cung cấp (Ảnh chụp màn hình web) tại đường link [https://codienhaiau.com/product/cam-bien-tiem-can-autonics-pr18-8ao/?gad_source=1&amp;gad_campaignid=1706335864&amp;gbraid=0AAAAAC85AUTUiMQTlpM5INcrwVMXyjNgE&amp;gclid=Cj0KCQjwh4TVBhCWARIsAG0czmrU01Hm6VugVdeERV3wnBY3tqrsDhcmqrdCW6WmaThX_1roS-FpvV4aAiEXEALw_wcB] lúc 08:33 ngày 10/9/2026 kèm ảnh chụp màn hình minh chứng niêm yết; ghi nhận mức giá niêm yết công khai tham chiếu là 577.200 đ [Giá niêm yết web: 481.000 đ; sau khi cộng chi phí vận chuyển quốc tế, thuế NK &amp; hải quan (+20%), giá Landed Cost DDP Vĩnh Tân 4 là 577.200 đ]. Đơn giá trình (1.150.000 đ) hiện cao hơn 99.2% (+572.800 đ) so với đơn giá Landed Cost DDP Vĩnh Tân 4 (577.200 đ).
+KẾT LUẬN THẨM ĐỊNH: Đề xuất duyệt đơn giá thẩm định thống nhất là 577.200 VNĐ/Bộ. Tiết kiệm dự toán 572.800 VNĐ (-49.8%).</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr"/>
+      <c r="J50" s="6" t="n">
+        <v>577200</v>
+      </c>
+      <c r="K50" s="6" t="n">
+        <v>577200</v>
+      </c>
+      <c r="L50" s="6" t="n">
+        <v>572800</v>
+      </c>
+      <c r="M50" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 5: Tham khảo TMĐT / Giá Web</t>
         </is>
       </c>
     </row>
@@ -3578,53 +3524,56 @@
           <t>2.05.80.082.KOR.00.000</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Hanger clamps (out doors) (kẹp giữ đường ray cáp điện)</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>Hanger clamps (out doors) (kẹp giữ đường ray cáp điện): Model: EH-2-001
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Hanger clamps (out doors) (kẹp giữ đường ray cáp điện) - Hanger clamps (out doors) (kẹp giữ đường ray cáp điện): Model: EH-2-001
  - Material: Galvanized Steel 
 +Epoxy Insulator Dome
  - Maker: Eunchang T&amp;C</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>Eunchang/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G51" s="7" t="n">
+      <c r="E51" s="6" t="n">
         <v>1284</v>
       </c>
-      <c r="H51" s="7" t="n">
+      <c r="F51" s="6" t="n">
         <v>465000</v>
       </c>
-      <c r="I51" s="7" t="n">
+      <c r="G51" s="6" t="n">
         <v>597060000</v>
       </c>
-      <c r="J51" s="6" t="inlineStr"/>
-      <c r="K51" s="6" t="inlineStr"/>
-      <c r="L51" s="7" t="n">
-        <v>535000</v>
-      </c>
-      <c r="M51" s="7" t="n">
-        <v>686940000</v>
-      </c>
-      <c r="N51" s="7" t="n">
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Hanger clamps (out doors) (kẹp giữ đường ray cáp điện) (Mã ERP: 2.05.80.082.KOR.00.000).
+• Đơn giá trình thẩm định: 465.000 VNĐ (Số lượng: 1284 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 465.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 7 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [2.05.80.082.KOR.00.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 465.000 VNĐ/Cái theo HĐ Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 (ký ngày 2026-01-23 00:00:00, cách đây 8 tháng - trong hạn 12 tháng).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [EH-2-001] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [EH-2-001] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 511.500 VNĐ/Cái (Nhà thầu Eunchang T&amp;C).
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Hanger clamps (out doors) (kẹp giữ đường ray cáp điện)] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 465.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr"/>
+      <c r="J51" s="6" t="n">
+        <v>465000</v>
+      </c>
+      <c r="K51" s="6" t="n">
+        <v>597060000</v>
+      </c>
+      <c r="L51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O51" s="6" t="inlineStr"/>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>2.05.80.082.KOR.00.000 | Sửa chữa tời điện các vị trí S3 theo BBKT 675/2026/VH-VT4; 435/2026/VH-VT4; 475/2026/VH-VT4; 558/2026/VH-VT4; 468/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -3637,52 +3586,55 @@
           <t>3.34.20.134.CHN.00.000</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Pendant control station:
+Type: XAC-A12713 - Pendant control station:
 Type: XAC-A12713</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>Pendant control station:
-Type: XAC-A12713</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>Schnerder/ Czech Republic</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G52" s="7" t="n">
+      <c r="E52" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H52" s="7" t="n">
+      <c r="F52" s="6" t="n">
         <v>5784000</v>
       </c>
-      <c r="I52" s="7" t="n">
+      <c r="G52" s="6" t="n">
         <v>5784000</v>
       </c>
-      <c r="J52" s="6" t="inlineStr"/>
-      <c r="K52" s="6" t="inlineStr"/>
-      <c r="L52" s="7" t="n">
-        <v>5784000</v>
-      </c>
-      <c r="M52" s="7" t="n">
-        <v>5784000</v>
-      </c>
-      <c r="N52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="6" t="inlineStr"/>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>3.34.20.134.CHN.00.000 | Sửa chữa tời điện Tời điện số 15 tấn B Khu vực máy nghiền S3 theo BBKT 675/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Pendant control station: (Mã ERP: 3.34.20.134.CHN.00.000).
+• Đơn giá trình thẩm định: 5.784.000 VNĐ (Số lượng: 1 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 30/100 điểm (🔴 Chưa Hợp Lý (Đơn giá trình cao hơn &gt;20% so với mốc giá tham chiếu)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 5.784.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 7 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [3.34.20.134.CHN.00.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 2.369.000 VNĐ/Cái theo HĐ Nhập kho vật tư (HĐ:132/2023) theo hóa đơn số 00000011 ngày 22.01.2024 (ký ngày 2024-02-27 00:00:00, cách đây 31 tháng ~ 2.6 năm - quá 12 tháng, tốc độ tăng giá bình quân 55.8%/năm so với CPI ~5.0%/năm).
+- Cơ sở 3 (EVN IMIS): Qua rà soát CSDL Hợp đồng mua sắm EVN IMIS theo từ khóa [XAC-A12713], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL EVN IMIS làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [XAC-A12713] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); kết quả đã rà soát e-GP: vật tư đặc thù, không ghi nhận gói thầu mua sắm tương đồng.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Pendant control station:] trên thị trường TMĐT / Website nhà cung cấp (Ảnh chụp màn hình web) tại link [https://cautrucdaiviet.vn/tay-bam-dieu-khien-cau-truc-xac-mit]; ghi nhận đơn giá niêm yết công khai tham chiếu là 420.000 VNĐ/Cái [Giá web gốc: 350.000 đ; sau khi tính phụ thu chi phí vận chuyển quốc tế &amp; thuế nhập khẩu (Landed Cost DDP Vĩnh Tân 4 +20%), đơn giá tham chiếu đề xuất là 420.000 đ].
+KẾT LUẬN THẨM ĐỊNH: Đề xuất duyệt đơn giá thẩm định thống nhất là 420.000 VNĐ/Cái. Tiết kiệm dự toán 5.364.000 VNĐ (-92.7%).</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr"/>
+      <c r="J52" s="6" t="n">
+        <v>420000</v>
+      </c>
+      <c r="K52" s="6" t="n">
+        <v>420000</v>
+      </c>
+      <c r="L52" s="6" t="n">
+        <v>5364000</v>
+      </c>
+      <c r="M52" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 5: Tham khảo TMĐT / Giá Web</t>
         </is>
       </c>
     </row>
@@ -3695,54 +3647,53 @@
           <t>5.05.65.658.KOR.00.000</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>Collector (chổi tiếp điện từ thanh ray)</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>Collector (chổi tiếp điện từ thanh ray):
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Collector (chổi tiếp điện từ thanh ray) - Collector (chổi tiếp điện từ thanh ray):
 - Iđm: 60A;
 - Uđm: 400VAC;
 - Material: Copper
 - Maker: Eunchang T&amp;C</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>Eunchang/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G53" s="7" t="n">
+      <c r="E53" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="H53" s="7" t="n">
+      <c r="F53" s="6" t="n">
         <v>2265000</v>
       </c>
-      <c r="I53" s="7" t="n">
+      <c r="G53" s="6" t="n">
         <v>81540000</v>
       </c>
-      <c r="J53" s="6" t="inlineStr"/>
-      <c r="K53" s="6" t="inlineStr"/>
-      <c r="L53" s="7" t="n">
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 2.265.000 đ/Bộ (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 2.270.000 đ/Bộ (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: 8 Bộ); Các đợt nhập khác: 1.520.000 đ
+• Cơ sở 3 (EVN IMIS): IMIS EVN: 32.000.000 đ/Cái (Công ty Dịch vụ sửa chữa các nhà máy điện EVNGENCO3)
+• Cơ sở 4 (Mua Sắm Công e-GP): e-GP MSC: 2.497.000 đ/Cái (Kết quả trúng thầu)
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 2.265.000 đ/Bộ.</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr"/>
+      <c r="J53" s="6" t="n">
         <v>2265000</v>
       </c>
-      <c r="M53" s="7" t="n">
+      <c r="K53" s="6" t="n">
         <v>81540000</v>
       </c>
-      <c r="N53" s="7" t="n">
+      <c r="L53" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O53" s="6" t="inlineStr"/>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>5.05.65.658.KOR.00.000 | Sửa chữa tời điện các vị trí S3 theo BBKT 435/2026/VH-VT4; 475/2026/VH-VT4; 558/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -3755,52 +3706,51 @@
           <t>4.90.80.030.KOR.00.000</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Bao che giữa các khớp nối đường ray cáp điện (Joint cover)</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>Joint cover (bao che giữa các khớp nối đường ray cáp điện):
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Bao che giữa các khớp nối đường ray cáp điện (Joint cover) - Joint cover (bao che giữa các khớp nối đường ray cáp điện):
 - Material: PVC
 - Maker: Eunchang T&amp;C</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>Eunchang/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G54" s="7" t="n">
+      <c r="E54" s="6" t="n">
         <v>235</v>
       </c>
-      <c r="H54" s="7" t="n">
+      <c r="F54" s="6" t="n">
         <v>66000</v>
       </c>
-      <c r="I54" s="7" t="n">
+      <c r="G54" s="6" t="n">
         <v>15510000</v>
       </c>
-      <c r="J54" s="6" t="inlineStr"/>
-      <c r="K54" s="6" t="inlineStr"/>
-      <c r="L54" s="7" t="n">
-        <v>66000</v>
-      </c>
-      <c r="M54" s="7" t="n">
-        <v>15510000</v>
-      </c>
-      <c r="N54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="6" t="inlineStr"/>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>4.90.80.030.KOR.00.000 | Sửa chữa tời điện các vị trí S3 theo BBKT 435/2026/VH-VT4; 475/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 66.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 26.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:116/2022) theo hóa đơn số 00000008 ngày 27.02.2023 ngày 2023-02-27. SL: 300 Cái); Các đợt nhập khác: 24.800 đ, 80.000 đ
+• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Bao che giữa các], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Bao che giữa các khớp nối đường ray cáp điện (Joint cover)] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 26.000 đ/Cái.</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr"/>
+      <c r="J54" s="6" t="n">
+        <v>26000</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>6110000</v>
+      </c>
+      <c r="L54" s="6" t="n">
+        <v>9400000</v>
+      </c>
+      <c r="M54" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -3813,51 +3763,50 @@
           <t>4.90.80.027.KOR.00.000</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Nắp che phía cuối đường ray cáp điện (End cap)</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>Nắp che phía cuối đường ray cáp điện (End cap)- Material: PVC
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Nắp che phía cuối đường ray cáp điện (End cap) - Nắp che phía cuối đường ray cáp điện (End cap)- Material: PVC
 - Maker: Eunchang T&amp;C</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>Eunchang/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G55" s="7" t="n">
+      <c r="E55" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="H55" s="7" t="n">
+      <c r="F55" s="6" t="n">
         <v>68000</v>
       </c>
-      <c r="I55" s="7" t="n">
+      <c r="G55" s="6" t="n">
         <v>2176000</v>
       </c>
-      <c r="J55" s="6" t="inlineStr"/>
-      <c r="K55" s="6" t="inlineStr"/>
-      <c r="L55" s="7" t="n">
-        <v>68000</v>
-      </c>
-      <c r="M55" s="7" t="n">
-        <v>2176000</v>
-      </c>
-      <c r="N55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="6" t="inlineStr"/>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>4.90.80.027.KOR.00.000 | Sửa chữa tời điện các vị trí S3 theo BBKT 435/2026/VH-VT4; 475/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 68.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 21.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:116/2022) theo hóa đơn số 00000008 ngày 27.02.2023 ngày 2023-02-27. SL: 32 Cái); Các đợt nhập khác: 18.000 đ, 710.000 đ
+• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Nắp che phía cuối], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Nắp che phía cuối đường ray cáp điện (End cap)] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 21.000 đ/Cái.</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr"/>
+      <c r="J55" s="6" t="n">
+        <v>21000</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>672000</v>
+      </c>
+      <c r="L55" s="6" t="n">
+        <v>1504000</v>
+      </c>
+      <c r="M55" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -3870,14 +3819,9 @@
           <t>2.08.37.001.KOR.97.000</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Trolley-bar (thanh ray cấp nguồn)</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>Trolley-bar (thanh ray cấp nguồn):
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Trolley-bar (thanh ray cấp nguồn) - Trolley-bar (thanh ray cấp nguồn):
 - Iđm: 60A;
 - Uđm: 400VAC;
 - Length: 3m / cây
@@ -3885,40 +3829,44 @@
 - Maker: EunchangT&amp;C</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>Eunchang/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>Cây</t>
         </is>
       </c>
-      <c r="G56" s="7" t="n">
+      <c r="E56" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="H56" s="7" t="n">
+      <c r="F56" s="6" t="n">
         <v>909000</v>
       </c>
-      <c r="I56" s="7" t="n">
+      <c r="G56" s="6" t="n">
         <v>25452000</v>
       </c>
-      <c r="J56" s="6" t="inlineStr"/>
-      <c r="K56" s="6" t="inlineStr"/>
-      <c r="L56" s="7" t="n">
-        <v>909000</v>
-      </c>
-      <c r="M56" s="7" t="n">
-        <v>25452000</v>
-      </c>
-      <c r="N56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="6" t="inlineStr"/>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>2.08.37.001.KOR.97.000 | Sửa chữa tời điện Tời điện 15 tấn quạt gió 2B theo BBKT 435/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 909.000 đ/Cây (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 921.500 đ/Cây (HĐ: Nhập kho vật tư (HĐ:105/2021) theo hóa đơn số 00000004 ngày 09.12.2021 ngày 2021-12-13. SL: 100 Cây); Các đợt nhập khác: 890.000 đ, 864.000 đ
+• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Trolley bar (thanh ray], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Trolley-bar (thanh ray cấp nguồn)] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 909.000 đ/Cây.</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr"/>
+      <c r="J56" s="6" t="n">
+        <v>890000</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>24920000</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>532000</v>
+      </c>
+      <c r="M56" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -3931,54 +3879,53 @@
           <t>4.82.32.060.KOR.99.000</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>Joint keeper (khớp nối các thanh ray)</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>Joint keeper (khớp nối các thanh ray):
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Joint keeper (khớp nối các thanh ray) - Joint keeper (khớp nối các thanh ray):
 - Iđm: 60A;
 - Uđm: 400VAC;
 - Material: Copper
 - Maker: Eunchang T&amp;C</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>Eunchang/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G57" s="7" t="n">
+      <c r="E57" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="H57" s="7" t="n">
+      <c r="F57" s="6" t="n">
         <v>47000</v>
       </c>
-      <c r="I57" s="7" t="n">
+      <c r="G57" s="6" t="n">
         <v>1128000</v>
       </c>
-      <c r="J57" s="6" t="inlineStr"/>
-      <c r="K57" s="6" t="inlineStr"/>
-      <c r="L57" s="7" t="n">
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 47.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 48.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 86/2024) theo hóa đơn số 81 ngày 26.11.2024 ngày 2024-12-23. SL: 236 Cái); Các đợt nhập khác: 76.000 đ, 47.000 đ
+• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Joint keeper (khớp nối], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+• Cơ sở 4 (Mua Sắm Công e-GP): e-GP MSC: 51.700 đ/Cái (Kết quả trúng thầu)
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 47.000 đ/Cái.</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr"/>
+      <c r="J57" s="6" t="n">
         <v>47000</v>
       </c>
-      <c r="M57" s="7" t="n">
+      <c r="K57" s="6" t="n">
         <v>1128000</v>
       </c>
-      <c r="N57" s="7" t="n">
+      <c r="L57" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O57" s="6" t="inlineStr"/>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>4.82.32.060.KOR.99.000 | Sửa chữa tời điện Tời điện 15 tấn quạt gió 2B theo BBKT 435/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="M57" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -3991,50 +3938,53 @@
           <t>3.34.20.131.CHN.00.000</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Pendant control station, Type: XAC-A8713</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>Pendant control station, Type: XAC-A8713</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>Schnerder/ Czech Republic</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Pendant control station, Type: XAC-A8713 - Pendant control station, Type: XAC-A8713</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G58" s="7" t="n">
+      <c r="E58" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H58" s="7" t="n">
+      <c r="F58" s="6" t="n">
         <v>6900000</v>
       </c>
-      <c r="I58" s="7" t="n">
+      <c r="G58" s="6" t="n">
         <v>6900000</v>
       </c>
-      <c r="J58" s="6" t="inlineStr"/>
-      <c r="K58" s="6" t="inlineStr"/>
-      <c r="L58" s="7" t="n">
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Pendant control station, Type: XAC-A8713 (Mã ERP: 3.34.20.131.CHN.00.000).
+• Đơn giá trình thẩm định: 6.900.000 VNĐ (Số lượng: 1 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 40/100 điểm (Hạng C - 2/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 6.900.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 7 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Chưa đối chiếu CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4.
+- Cơ sở 3 (EVN IMIS): Chưa đối chiếu CSDL Hợp đồng mua sắm toàn ngành EVN IMIS.
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [A8713] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 7.452.000 VNĐ/Cái (Nhà thầu Schneider Electric).
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Pendant control station, Type: XAC-A8713] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 6.900.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr"/>
+      <c r="J58" s="6" t="n">
         <v>6900000</v>
       </c>
-      <c r="M58" s="7" t="n">
+      <c r="K58" s="6" t="n">
         <v>6900000</v>
       </c>
-      <c r="N58" s="7" t="n">
+      <c r="L58" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O58" s="6" t="inlineStr"/>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>3.34.20.131.CHN.00.000 | Sửa chữa Tời điện 30 tấn quạt khói theo BBKT 475/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="M58" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -4047,15 +3997,10 @@
           <t>3.34.20.133.CHN.99.000</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>Pendant control station:
-Type: XAC-A6913</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>Pendant control station:
+Type: XAC-A6913 - Pendant control station:
 Type: XAC-A6913
 Control station composition: 06 push buttons + 01 emergency stop
 Product compatibility: 
@@ -4063,40 +4008,48 @@
 Color: Yellow</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>Schnerder/ Czech Republic</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G59" s="7" t="n">
+      <c r="E59" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H59" s="7" t="n">
+      <c r="F59" s="6" t="n">
         <v>13319000</v>
       </c>
-      <c r="I59" s="7" t="n">
+      <c r="G59" s="6" t="n">
         <v>13319000</v>
       </c>
-      <c r="J59" s="6" t="inlineStr"/>
-      <c r="K59" s="6" t="inlineStr"/>
-      <c r="L59" s="7" t="n">
-        <v>13319000</v>
-      </c>
-      <c r="M59" s="7" t="n">
-        <v>13319000</v>
-      </c>
-      <c r="N59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="6" t="inlineStr"/>
-      <c r="P59" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã | Sửa chữa Tời điện Tời điện 10 tấn quạt khói theo BBKT 475/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Pendant control station: (Mã ERP: 3.34.20.133.CHN.99.000).
+• Đơn giá trình thẩm định: 13.319.000 VNĐ (Số lượng: 1 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 30/100 điểm (🔴 Chưa Hợp Lý (Đơn giá trình cao hơn &gt;20% so với mốc giá tham chiếu)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 13.319.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 7 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [3.34.20.133.CHN.99.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; kết quả đã đối soát CSDL ERP: 0 bản ghi phù hợp (vật tư chưa từng có lịch sử nhập kho nội bộ nhà máy Vĩnh Tân 4).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [A6913] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [XAC] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 3.290.400 VNĐ/Cái (Nhà thầu Schneider Electric).
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Pendant control station:] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đề xuất duyệt đơn giá thẩm định thống nhất là 3.290.400 VNĐ/Cái. Tiết kiệm dự toán 10.028.600 VNĐ (-75.3%).</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr"/>
+      <c r="J59" s="6" t="n">
+        <v>3290400</v>
+      </c>
+      <c r="K59" s="6" t="n">
+        <v>3290400</v>
+      </c>
+      <c r="L59" s="6" t="n">
+        <v>10028600</v>
+      </c>
+      <c r="M59" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 4: Mua Sắm Công e-GP</t>
         </is>
       </c>
     </row>
@@ -4109,51 +4062,55 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Lưỡi gà móc cẩu 3 tấn</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>Lưỡi gà móc cẩu 3 tấn
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 3 tấn - Lưỡi gà móc cẩu 3 tấn
 Kích thước: rộng 25mm x dài 60mm</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>MT/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G60" s="7" t="n">
+      <c r="E60" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H60" s="7" t="n">
+      <c r="F60" s="6" t="n">
         <v>610000</v>
       </c>
-      <c r="I60" s="7" t="n">
+      <c r="G60" s="6" t="n">
         <v>610000</v>
       </c>
-      <c r="J60" s="6" t="inlineStr"/>
-      <c r="K60" s="6" t="inlineStr"/>
-      <c r="L60" s="7" t="n">
-        <v>610000</v>
-      </c>
-      <c r="M60" s="7" t="n">
-        <v>610000</v>
-      </c>
-      <c r="N60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="6" t="inlineStr"/>
-      <c r="P60" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã | Sửa chữa Tời điện Tời điện 3 tấn nằm ngoài BSKK theo BBKT 558/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Lưỡi gà móc cẩu 3 tấn (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 610.000 VNĐ (Số lượng: 1 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 30/100 điểm (🔴 Chưa Hợp Lý (Đơn giá trình cao hơn &gt;20% so với mốc giá tham chiếu)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 716.000 VNĐ/Cái từ DTL 19.8.2026. xlsx (Trang 6 Báo giá); đơn giá chào đối chiếu cao hơn đơn giá trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [Lưỡi gà móc cẩu 3 tấn] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 585.000 VNĐ/Cái theo HĐ Nhập kho vật tư (HĐ: 57/2024) theo hóa đơn số 615 ngày 27.08.2024 (ký ngày 2024-09-06 00:00:00, cách đây 24 tháng ~ 2 năm - quá 12 tháng, tốc độ tăng giá bình quân 2.1%/năm so với CPI ~5.0%/năm).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [Lưỡi gà móc cẩu 3 tấn
+Kích thước: rộng 25mm x dài 60mm] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [Lưỡi gà móc cẩu] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 314.600 VNĐ/Cái.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Lưỡi gà móc cẩu 3 tấn] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đề xuất duyệt đơn giá thẩm định thống nhất là 314.600 VNĐ/Cái. Tiết kiệm dự toán 295.400 VNĐ (-48.4%).</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr"/>
+      <c r="J60" s="6" t="n">
+        <v>314600</v>
+      </c>
+      <c r="K60" s="6" t="n">
+        <v>314600</v>
+      </c>
+      <c r="L60" s="6" t="n">
+        <v>295400</v>
+      </c>
+      <c r="M60" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 4: Mua Sắm Công e-GP</t>
         </is>
       </c>
     </row>
@@ -4166,51 +4123,50 @@
           <t>3.80.42.186.KOR.00.000</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>Cáp tròn điều khiển cẩu trục có cáp chịu lực</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>Cáp tròn điều khiển cẩu trục có cáp chịu lực: Mã sản phẩm: 1.5SQx20C 
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Cáp tròn điều khiển cẩu trục có cáp chịu lực - Cáp tròn điều khiển cẩu trục có cáp chịu lực: Mã sản phẩm: 1.5SQx20C 
 Đường kính: 1.5mm2 /lõi (bao gồm 20 sợi lõi). Vật liệu lõi: Đồng</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>Dae Duk/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="G61" s="7" t="n">
+      <c r="E61" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="H61" s="7" t="n">
+      <c r="F61" s="6" t="n">
         <v>909000</v>
       </c>
-      <c r="I61" s="7" t="n">
+      <c r="G61" s="6" t="n">
         <v>18180000</v>
       </c>
-      <c r="J61" s="6" t="inlineStr"/>
-      <c r="K61" s="6" t="inlineStr"/>
-      <c r="L61" s="7" t="n">
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 909.000 đ/Mét (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 1.791.000 đ/Mét (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: 20 Mét)
+• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Cáp tròn điều khiển], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+• Cơ sở 4 (Mua Sắm Công e-GP): e-GP MSC: 1.970.100 đ/Cái (Kết quả trúng thầu)
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 909.000 đ/Mét.</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr"/>
+      <c r="J61" s="6" t="n">
         <v>909000</v>
       </c>
-      <c r="M61" s="7" t="n">
+      <c r="K61" s="6" t="n">
         <v>18180000</v>
       </c>
-      <c r="N61" s="7" t="n">
+      <c r="L61" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O61" s="6" t="inlineStr"/>
-      <c r="P61" s="6" t="inlineStr">
-        <is>
-          <t>3.80.42.186.KOR.00.000 | Sửa chữa Tời điện Tời điện 3 tấn nằm ngoài BSKK theo BBKT 558/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="M61" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -4223,50 +4179,53 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>Cáp thép 6x36 IWRC, đường kính cáp 12mm, loại 3 tấn: 80 mét</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>Cáp thép 6x36 IWRC, đường kính cáp 12mm, loại 3 tấn: 80 mét</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>Uni/ Mỹ</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Cáp thép 6x36 IWRC, đường kính cáp 12mm, loại 3 tấn: 80 mét - Cáp thép 6x36 IWRC, đường kính cáp 12mm, loại 3 tấn: 80 mét</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="G62" s="7" t="n">
+      <c r="E62" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="H62" s="7" t="n">
+      <c r="F62" s="6" t="n">
         <v>202000</v>
       </c>
-      <c r="I62" s="7" t="n">
+      <c r="G62" s="6" t="n">
         <v>16160000</v>
       </c>
-      <c r="J62" s="6" t="inlineStr"/>
-      <c r="K62" s="6" t="inlineStr"/>
-      <c r="L62" s="7" t="n">
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Cáp thép 6x36 IWRC, đường kính cáp 12mm, loại 3 tấn: 80 mét (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 202.000 VNĐ (Số lượng: 80 Mét).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 202.000 VNĐ/Mét từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 8 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Qua rà soát CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 theo từ khóa [Cáp thép 6x36 IWRC], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 3 (EVN IMIS): Qua rà soát CSDL Hợp đồng mua sắm EVN IMIS theo từ khóa [Cáp thép 6x36 IWRC,], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL EVN IMIS làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 4 (Mua Sắm Công e-GP): Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khóa [IWRC], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL Mua sắm công làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Cáp thép 6x36 IWRC,] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 202.000 VNĐ/Mét.</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr"/>
+      <c r="J62" s="6" t="n">
         <v>202000</v>
       </c>
-      <c r="M62" s="7" t="n">
+      <c r="K62" s="6" t="n">
         <v>16160000</v>
       </c>
-      <c r="N62" s="7" t="n">
+      <c r="L62" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O62" s="6" t="inlineStr"/>
-      <c r="P62" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã | Sửa chữa Tời điện Tời điện 3 tấn nằm ngoài BSKK theo BBKT 558/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="M62" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -4279,52 +4238,51 @@
           <t>2.50.05.003.CHN.00.000</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>Cáp inox 304 
+Kích thước: Ø 3 mm - Cáp inox 304 
 Kích thước: Ø 3 mm</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>Cáp inox 304 
-Kích thước: Ø 3 mm</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>Kungho/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="G63" s="7" t="n">
+      <c r="E63" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="H63" s="7" t="n">
+      <c r="F63" s="6" t="n">
         <v>37000</v>
       </c>
-      <c r="I63" s="7" t="n">
+      <c r="G63" s="6" t="n">
         <v>2220000</v>
       </c>
-      <c r="J63" s="6" t="inlineStr"/>
-      <c r="K63" s="6" t="inlineStr"/>
-      <c r="L63" s="7" t="n">
-        <v>37000</v>
-      </c>
-      <c r="M63" s="7" t="n">
-        <v>2220000</v>
-      </c>
-      <c r="N63" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="6" t="inlineStr"/>
-      <c r="P63" s="6" t="inlineStr">
-        <is>
-          <t>2.50.05.003.CHN.00.000 | Sửa chữa Tời điện 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 37.000 đ/Mét (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 86.000 đ/Mét (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: 90 Mét); Các đợt nhập khác: 67.000 đ, 12.000 đ
+• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Cáp inox 304 Kích], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+• Cơ sở 4 (Mua Sắm Công e-GP): e-GP MSC: 10.000 đ/Cái (Kết quả trúng thầu)
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 10.000 đ/Mét.</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr"/>
+      <c r="J63" s="6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="K63" s="6" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="L63" s="6" t="n">
+        <v>780000</v>
+      </c>
+      <c r="M63" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 4: Mua Sắm Công e-GP</t>
         </is>
       </c>
     </row>
@@ -4337,51 +4295,50 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>Phe cài trục ngoài cho đường kính 28mm</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>Phe cài trục ngoài cho đường kính 28mm.
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Phe cài trục ngoài cho đường kính 28mm - Phe cài trục ngoài cho đường kính 28mm.
 Vật liệu: Inox 304</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>Kungho/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G64" s="7" t="n">
+      <c r="E64" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H64" s="7" t="n">
+      <c r="F64" s="6" t="n">
         <v>56000</v>
       </c>
-      <c r="I64" s="7" t="n">
+      <c r="G64" s="6" t="n">
         <v>56000</v>
       </c>
-      <c r="J64" s="6" t="inlineStr"/>
-      <c r="K64" s="6" t="inlineStr"/>
-      <c r="L64" s="7" t="n">
-        <v>56000</v>
-      </c>
-      <c r="M64" s="7" t="n">
-        <v>56000</v>
-      </c>
-      <c r="N64" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="6" t="inlineStr"/>
-      <c r="P64" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã | Sửa chữa Tời điện Tời điện 3 tấn nằm ngoài BSKK theo BBKT 558/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 56.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 50.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:43) theo hóa đơn số 0000015 ngày 21.06.2021 ngày 2021-06-26. SL: 201 Cái); Các đợt nhập khác: 48.400 đ, 371.800 đ
+• Cơ sở 3 (EVN IMIS): IMIS EVN: 530.145 đ/Cái (Công ty Thủy điện Sông Tranh)
+• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Phe cài trục ngoài cho đường kính 28mm] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 50.000 đ/Cái.</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr"/>
+      <c r="J64" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K64" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L64" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M64" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -4394,56 +4351,63 @@
           <t>2.06.60.032.TPE.00.000</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>Thanh ray C
 Loại: CH2201
-Size: 32x30x1.5mm dài 3m</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>Thanh ray C
+Size: 32x30x1.5mm dài 3m - Thanh ray C
 Loại: CH2201
 Size: 32x30x1.5mm dài 3m
 Vật liệu: Inox 304
 Hãng: ITS Đài loan</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>ITS/ Đài Loan</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>Thanh</t>
         </is>
       </c>
-      <c r="G65" s="7" t="n">
+      <c r="E65" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="H65" s="7" t="n">
+      <c r="F65" s="6" t="n">
         <v>4520000</v>
       </c>
-      <c r="I65" s="7" t="n">
+      <c r="G65" s="6" t="n">
         <v>63280000</v>
       </c>
-      <c r="J65" s="6" t="inlineStr"/>
-      <c r="K65" s="6" t="inlineStr"/>
-      <c r="L65" s="7" t="n">
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Thanh ray C (Mã ERP: 2.06.60.032.TPE.00.000).
+• Đơn giá trình thẩm định: 4.520.000 VNĐ (Số lượng: 14 Thanh).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 4.520.000 VNĐ/Thanh từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 8 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [2.06.60.032.TPE.00.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 4.523.000 VNĐ/Thanh theo HĐ Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 (ký ngày 2026-01-23 00:00:00, cách đây 8 tháng - trong hạn 12 tháng).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [Thanh ray C
+Loại: CH2201
+Size: 32x30x1.5mm dài 3m
+Vật liệu: Inox 304
+Hãng: ITS Đài loan] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [CH2201] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 4.975.300 VNĐ/Thanh (Nhà thầu ITS).
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Thanh ray C] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 4.520.000 VNĐ/Thanh.</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr"/>
+      <c r="J65" s="6" t="n">
         <v>4520000</v>
       </c>
-      <c r="M65" s="7" t="n">
+      <c r="K65" s="6" t="n">
         <v>63280000</v>
       </c>
-      <c r="N65" s="7" t="n">
+      <c r="L65" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O65" s="6" t="inlineStr"/>
-      <c r="P65" s="6" t="inlineStr">
-        <is>
-          <t>2.06.60.032.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="M65" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -4456,56 +4420,63 @@
           <t>2.06.60.038.TPE.00.000</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>Nối ray C
 Loại: CH2230
-Size: 40x38x3mm, dài 100mm</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>Nối ray C
+Size: 40x38x3mm, dài 100mm - Nối ray C
 Loại: CH2230
 Size: 40x38x3mm, dài 100mm
 Vật liệu: Inox 304
 Hãng: ITS Đài loan</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>ITS/ Đài Loan</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G66" s="7" t="n">
+      <c r="E66" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="H66" s="7" t="n">
+      <c r="F66" s="6" t="n">
         <v>1120000</v>
       </c>
-      <c r="I66" s="7" t="n">
+      <c r="G66" s="6" t="n">
         <v>13440000</v>
       </c>
-      <c r="J66" s="6" t="inlineStr"/>
-      <c r="K66" s="6" t="inlineStr"/>
-      <c r="L66" s="7" t="n">
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Nối ray C (Mã ERP: 2.06.60.038.TPE.00.000).
+• Đơn giá trình thẩm định: 1.120.000 VNĐ (Số lượng: 12 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 1.120.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 8 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [2.06.60.038.TPE.00.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 1.123.000 VNĐ/Cái theo HĐ Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 (ký ngày 2026-01-23 00:00:00, cách đây 8 tháng - trong hạn 12 tháng).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [Nối ray C
+Loại: CH2230
+Size: 40x38x3mm, dài 100mm
+Vật liệu: Inox 304
+Hãng: ITS Đài loan] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [CH2230] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 1.235.300 VNĐ/Cái (Nhà thầu ITS).
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Nối ray C] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 1.120.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr"/>
+      <c r="J66" s="6" t="n">
         <v>1120000</v>
       </c>
-      <c r="M66" s="7" t="n">
+      <c r="K66" s="6" t="n">
         <v>13440000</v>
       </c>
-      <c r="N66" s="7" t="n">
+      <c r="L66" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O66" s="6" t="inlineStr"/>
-      <c r="P66" s="6" t="inlineStr">
-        <is>
-          <t>2.06.60.038.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="M66" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -4518,56 +4489,55 @@
           <t>2.35.16.032.TPE.00.000</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>Giữ ray
 Loại: CH2240
-Size: 80x25x3mm</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>Giữ ray
+Size: 80x25x3mm - Giữ ray
 Loại: CH2240
 Size: 80x25x3mm
 Vật liệu: Inox 304
 Hãng: ITS Đài loan</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>ITS/ Đài Loan</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G67" s="7" t="n">
+      <c r="E67" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="H67" s="7" t="n">
+      <c r="F67" s="6" t="n">
         <v>905000</v>
       </c>
-      <c r="I67" s="7" t="n">
+      <c r="G67" s="6" t="n">
         <v>46155000</v>
       </c>
-      <c r="J67" s="6" t="inlineStr"/>
-      <c r="K67" s="6" t="inlineStr"/>
-      <c r="L67" s="7" t="n">
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 905.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4 [Giữ ray size: 80x25x3mm. vật liệu: inox 304. loại: CH2240]: 906.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: 45 Cái)
+• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Giữ ray Loại CH2240], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+• Cơ sở 4 (Mua Sắm Công e-GP): e-GP MSC: 106.178 đ/Cái (Kết quả trúng thầu)
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 106.178 đ/Cái.</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr"/>
+      <c r="J67" s="6" t="n">
         <v>905000</v>
       </c>
-      <c r="M67" s="7" t="n">
+      <c r="K67" s="6" t="n">
         <v>46155000</v>
       </c>
-      <c r="N67" s="7" t="n">
+      <c r="L67" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O67" s="6" t="inlineStr"/>
-      <c r="P67" s="6" t="inlineStr">
-        <is>
-          <t>2.35.16.032.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="M67" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -4580,54 +4550,60 @@
           <t>2.06.60.078.TPE.00.000</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>Con lăn dẫn cáp
-Loại: CH2220-1 78x85mm</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>Con lăn dẫn cáp
+Loại: CH2220-1 78x85mm - Con lăn dẫn cáp
 Loại: CH2220-1 78x85mm
 Vật liệu: Inox 304
 Hãng: ITS Đài loan</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>ITS/ Đài Loan</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G68" s="7" t="n">
+      <c r="E68" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="H68" s="7" t="n">
+      <c r="F68" s="6" t="n">
         <v>2710000</v>
       </c>
-      <c r="I68" s="7" t="n">
+      <c r="G68" s="6" t="n">
         <v>86720000</v>
       </c>
-      <c r="J68" s="6" t="inlineStr"/>
-      <c r="K68" s="6" t="inlineStr"/>
-      <c r="L68" s="7" t="n">
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Con lăn dẫn cáp (Mã ERP: 2.06.60.078.TPE.00.000).
+• Đơn giá trình thẩm định: 2.710.000 VNĐ (Số lượng: 32 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 2.710.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 8 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [2.06.60.078.TPE.00.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 2.716.000 VNĐ/Cái theo HĐ Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 (ký ngày 2026-01-23 00:00:00, cách đây 8 tháng - trong hạn 12 tháng).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [Con lăn dẫn cáp
+Loại: CH2220-1 78x85mm
+Vật liệu: Inox 304
+Hãng: ITS Đài loan] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [CH2220] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 2.987.600 VNĐ/Cái (Nhà thầu ITS).
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Con lăn dẫn cáp] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 2.710.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr"/>
+      <c r="J68" s="6" t="n">
         <v>2710000</v>
       </c>
-      <c r="M68" s="7" t="n">
+      <c r="K68" s="6" t="n">
         <v>86720000</v>
       </c>
-      <c r="N68" s="7" t="n">
+      <c r="L68" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O68" s="6" t="inlineStr"/>
-      <c r="P68" s="6" t="inlineStr">
-        <is>
-          <t>2.06.60.078.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="M68" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -4640,54 +4616,57 @@
           <t>2.06.60.085.TPE.00.000</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>Con lăn dẫn đầu
-Loại: CH2250 78x80 mm</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>Con lăn dẫn đầu
+Loại: CH2250 78x80 mm - Con lăn dẫn đầu
 Loại: CH2250 78x80 mm
 Vật liệu: Inox 304
 Hãng: ITS Đài loan</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>ITS/ Đài Loan</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G69" s="7" t="n">
+      <c r="E69" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H69" s="7" t="n">
+      <c r="F69" s="6" t="n">
         <v>980000</v>
       </c>
-      <c r="I69" s="7" t="n">
+      <c r="G69" s="6" t="n">
         <v>1960000</v>
       </c>
-      <c r="J69" s="6" t="inlineStr"/>
-      <c r="K69" s="6" t="inlineStr"/>
-      <c r="L69" s="7" t="n">
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Con lăn dẫn đầu (Mã ERP: 2.06.60.085.TPE.00.000).
+• Đơn giá trình thẩm định: 980.000 VNĐ (Số lượng: 2 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 980.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 8 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [2.06.60.085.TPE.00.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 1.575.000 VNĐ/Cái theo HĐ Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 (ký ngày 2026-01-23 00:00:00, cách đây 8 tháng - trong hạn 12 tháng).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [CH2220] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [CH2250] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 1.732.500 VNĐ/Cái (Nhà thầu ITS).
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Con lăn dẫn đầu] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 980.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr"/>
+      <c r="J69" s="6" t="n">
         <v>980000</v>
       </c>
-      <c r="M69" s="7" t="n">
+      <c r="K69" s="6" t="n">
         <v>1960000</v>
       </c>
-      <c r="N69" s="7" t="n">
+      <c r="L69" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O69" s="6" t="inlineStr"/>
-      <c r="P69" s="6" t="inlineStr">
-        <is>
-          <t>2.06.60.085.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="M69" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -4700,58 +4679,53 @@
           <t>2.06.60.080.TPE.00.000</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>Kẹp cố định đầu ray
 Loại: CH2260
-Size: 80x51x3mm</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>Kẹp cố định đầu ray
+Size: 80x51x3mm - Kẹp cố định đầu ray
 Loại: CH2260
 Size: 80x51x3mm
 Vật liệu: Inox 304
 Hãng: ITS Đài loan</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>ITS/ Đài Loan</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G70" s="7" t="n">
+      <c r="E70" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H70" s="7" t="n">
+      <c r="F70" s="6" t="n">
         <v>2254000</v>
       </c>
-      <c r="I70" s="7" t="n">
+      <c r="G70" s="6" t="n">
         <v>4508000</v>
       </c>
-      <c r="J70" s="6" t="inlineStr"/>
-      <c r="K70" s="6" t="inlineStr"/>
-      <c r="L70" s="7" t="n">
-        <v>2254000</v>
-      </c>
-      <c r="M70" s="7" t="n">
-        <v>4508000</v>
-      </c>
-      <c r="N70" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="6" t="inlineStr"/>
-      <c r="P70" s="6" t="inlineStr">
-        <is>
-          <t>2.06.60.080.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
-        </is>
-      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 2.254.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4 [Kẹp cố định đầu ray. Loại: CH2260. Size: 80x51x3mm. Vật liệu: Inox 304]: 3.574.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: 3 Cái)
+• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [2.06.60.080.TPE.00.000], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+• Cơ sở 4 (Mua Sắm Công e-GP): e-GP MSC: 578.078 đ/Cái (Kết quả trúng thầu)
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 578.078 đ/Cái.</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr"/>
+      <c r="J70" s="6" t="n">
+        <v>578078</v>
+      </c>
+      <c r="K70" s="6" t="n">
+        <v>1156156</v>
+      </c>
+      <c r="L70" s="6" t="n">
+        <v>3351844</v>
+      </c>
+      <c r="M70" s="7" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -4762,56 +4736,51 @@
           <t>4.82.72.013.VIE.00.000</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>Ống nối cáp điện:
-Model: SL16</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>Ống nối cáp điện:
+Model: SL16 - Ống nối cáp điện:
 Model: SL16
 Chất liệu Đồng thau
 Tiết diện cáp sử dụng 16 mm2</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>Kungho/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
+      <c r="D71" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G71" s="7" t="n">
+      <c r="E71" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="H71" s="7" t="n">
+      <c r="F71" s="6" t="n">
         <v>12000</v>
       </c>
-      <c r="I71" s="7" t="n">
+      <c r="G71" s="6" t="n">
         <v>192000</v>
       </c>
-      <c r="J71" s="6" t="inlineStr"/>
-      <c r="K71" s="6" t="inlineStr"/>
-      <c r="L71" s="7" t="n">
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 12.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4 [Ống nối cáp điện; model: SL16. chất liệu đồng thau. tiết diện cáp sử dụng 16 mm2]: 66.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: 16 Cái); Các đợt nhập khác: 52.000 đ, 8.000 đ
+• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [4.82.72.013.VIE.00.000], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+• Cơ sở 4 (Mua Sắm Công e-GP): e-GP MSC: 29.150 đ/Cái (Kết quả trúng thầu)
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 12.000 đ/Cái.</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr"/>
+      <c r="J71" s="6" t="n">
         <v>12000</v>
       </c>
-      <c r="M71" s="7" t="n">
+      <c r="K71" s="6" t="n">
         <v>192000</v>
       </c>
-      <c r="N71" s="7" t="n">
+      <c r="L71" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O71" s="6" t="inlineStr"/>
-      <c r="P71" s="6" t="inlineStr">
-        <is>
-          <t>4.82.72.013.VIE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
-        </is>
-      </c>
+      <c r="M71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -4822,16 +4791,11 @@
           <t>3.15.44.076.CHN.00.000</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>Cáp điện dẹt cho cầu trục
 Quy cách: 16mm2 x 4C
-Ruột mềm</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>Cáp điện dẹt cho cầu trục
+Ruột mềm - Cáp điện dẹt cho cầu trục
 Quy cách: 16mm2 x 4C
 Ruột mềm
 Điện áp: 450/750V
@@ -4839,42 +4803,42 @@
 NSX: Imatek</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>Imatek/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="G72" s="7" t="n">
+      <c r="E72" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="H72" s="7" t="n">
+      <c r="F72" s="6" t="n">
         <v>711000</v>
       </c>
-      <c r="I72" s="7" t="n">
+      <c r="G72" s="6" t="n">
         <v>35550000</v>
       </c>
-      <c r="J72" s="6" t="inlineStr"/>
-      <c r="K72" s="6" t="inlineStr"/>
-      <c r="L72" s="7" t="n">
-        <v>711000</v>
-      </c>
-      <c r="M72" s="7" t="n">
-        <v>35550000</v>
-      </c>
-      <c r="N72" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="6" t="inlineStr"/>
-      <c r="P72" s="6" t="inlineStr">
-        <is>
-          <t>3.15.44.076.CHN.00.000 | Sửa chữa Tời điện 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
-        </is>
-      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 711.000 đ/Mét (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4 [Cáp điện dẹt cho cầu trục. 16mm2 x 4C]: 1.091.000 đ/Mét (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: 99 Mét); Các đợt nhập khác: 730.000 đ, 510.000 đ
+• Cơ sở 3 (EVN IMIS): IMIS EVN: 76.000 đ/Cái (Trung tâm Dịch vụ sửa chữa EVN - Chi nhánh Tập đoàn Điện lực Việt Nam)
+• Cơ sở 4 (Mua Sắm Công e-GP): e-GP MSC: 125.000 đ/Cái (Kết quả trúng thầu)
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 76.000 đ/Mét.</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr"/>
+      <c r="J72" s="6" t="n">
+        <v>76000</v>
+      </c>
+      <c r="K72" s="6" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="L72" s="6" t="n">
+        <v>31750000</v>
+      </c>
+      <c r="M72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -4885,52 +4849,51 @@
           <t>3.20.22.003.TPE.00.000</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>Khóa cáp 
+Dùng cho cáp: 3mm - Khóa cáp 
 Dùng cho cáp: 3mm</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>Khóa cáp 
-Dùng cho cáp: 3mm</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>Kungho/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G73" s="7" t="n">
+      <c r="E73" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="H73" s="7" t="n">
+      <c r="F73" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="I73" s="7" t="n">
+      <c r="G73" s="6" t="n">
         <v>1100000</v>
       </c>
-      <c r="J73" s="6" t="inlineStr"/>
-      <c r="K73" s="6" t="inlineStr"/>
-      <c r="L73" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M73" s="7" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="N73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" s="6" t="inlineStr"/>
-      <c r="P73" s="6" t="inlineStr">
-        <is>
-          <t>3.20.22.003.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 20.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4 [Khóa cáp dùng cho cáp 3mm]: 14.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: 108 Cái); Các đợt nhập khác: 38.000 đ, 14.000 đ
+• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Khóa cáp Dùng cho], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+• Cơ sở 4 (Mua Sắm Công e-GP): e-GP MSC: 5.000 đ/Cái (Kết quả trúng thầu)
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 5.000 đ/Cái.</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr"/>
+      <c r="J73" s="6" t="n">
+        <v>14000</v>
+      </c>
+      <c r="K73" s="6" t="n">
+        <v>770000</v>
+      </c>
+      <c r="L73" s="6" t="n">
+        <v>330000</v>
+      </c>
+      <c r="M73" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -4943,53 +4906,52 @@
           <t>3.34.20.130.CHN.99.000</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>Pendant control station (Tay bấm điều khiển tời điện): 
-- Type: XAC-A6713</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>Pendant control station (Tay bấm điều khiển tời điện): 
+- Type: XAC-A6713 - Pendant control station (Tay bấm điều khiển tời điện): 
 - Type: XAC-A6713
 Control station composition: 06, push buttons + 01 emergency stop</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>Schnerder/ Czech Republic</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G74" s="7" t="n">
+      <c r="E74" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H74" s="7" t="n">
+      <c r="F74" s="6" t="n">
         <v>7406000</v>
       </c>
-      <c r="I74" s="7" t="n">
+      <c r="G74" s="6" t="n">
         <v>7406000</v>
       </c>
-      <c r="J74" s="6" t="inlineStr"/>
-      <c r="K74" s="6" t="inlineStr"/>
-      <c r="L74" s="7" t="n">
-        <v>7406000</v>
-      </c>
-      <c r="M74" s="7" t="n">
-        <v>7406000</v>
-      </c>
-      <c r="N74" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="6" t="inlineStr"/>
-      <c r="P74" s="6" t="inlineStr">
-        <is>
-          <t>3.34.20.130.CHN.99.000 | Sửa chữa Tời điện Tời điện 3 tấn máy nén khí turbine theo BBKT 624/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 7.406.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4 [Pendant control station. Type: XACA6713]: 6.600.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 65/2024) theo hóa đơn số 00000031 ngày 18.09.2024 ngày 2024-10-09. SL: 10 Cái); Các đợt nhập khác: 1.711.000 đ, 5.748.000 đ
+• Cơ sở 3 (EVN IMIS): IMIS EVN: 3.310.185 đ/Cái (Công ty Nhiệt điện Vĩnh Tân)
+• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Pendant control station (Tay bấm điều khiển tời điện):] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 3.310.185 đ/Cái.</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr"/>
+      <c r="J74" s="6" t="n">
+        <v>3310185</v>
+      </c>
+      <c r="K74" s="6" t="n">
+        <v>3310185</v>
+      </c>
+      <c r="L74" s="6" t="n">
+        <v>4095815</v>
+      </c>
+      <c r="M74" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 3: EVN IMIS</t>
         </is>
       </c>
     </row>
@@ -5002,52 +4964,51 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>Lưỡi gà móc cẩu 7 tấn</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>Lưỡi gà móc cẩu 7 tấn:
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 7 tấn - Lưỡi gà móc cẩu 7 tấn:
  + Kích thước: 60 x 175x 3mm
  + Vật liệu: thép</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>Kungho/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G75" s="7" t="n">
+      <c r="E75" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H75" s="7" t="n">
+      <c r="F75" s="6" t="n">
         <v>656000</v>
       </c>
-      <c r="I75" s="7" t="n">
+      <c r="G75" s="6" t="n">
         <v>656000</v>
       </c>
-      <c r="J75" s="6" t="inlineStr"/>
-      <c r="K75" s="6" t="inlineStr"/>
-      <c r="L75" s="7" t="n">
-        <v>656000</v>
-      </c>
-      <c r="M75" s="7" t="n">
-        <v>656000</v>
-      </c>
-      <c r="N75" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="6" t="inlineStr"/>
-      <c r="P75" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã | Sửa chữa tời điên Cầu trục 7 tấn lưới quay rác trạm bơm tuần hoàn theo BBKT 432/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 656.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4 [Lưỡi gà móc cẩu BCD10t. Kích thước (DxR): 120mmx41mm]: 585.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 57/2024) theo hóa đơn số 615 ngày 27.08.2024 ngày 2024-09-06. SL: 1 Cái); Các đợt nhập khác: 2.040.000 đ, 282.000 đ
+• Cơ sở 3 (EVN IMIS): IMIS EVN: 130.000 đ/Cái (Công ty Nhiệt điện Vĩnh Tân)
+• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Lưỡi gà móc cẩu 7 tấn] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 130.000 đ/Cái.</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr"/>
+      <c r="J75" s="6" t="n">
+        <v>585000</v>
+      </c>
+      <c r="K75" s="6" t="n">
+        <v>585000</v>
+      </c>
+      <c r="L75" s="6" t="n">
+        <v>71000</v>
+      </c>
+      <c r="M75" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -5060,52 +5021,37 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>Sơn dầu Jotun chống sét Green 437</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>Sơn dầu Jotun chống sét Green 437</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>Kungho/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Sơn dầu Jotun chống sét Green 437 - Sơn dầu Jotun chống sét Green 437</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>Lít</t>
         </is>
       </c>
-      <c r="G76" s="7" t="n">
+      <c r="E76" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="H76" s="7" t="n">
+      <c r="F76" s="6" t="n">
         <v>625000</v>
       </c>
-      <c r="I76" s="7" t="n">
+      <c r="G76" s="6" t="n">
         <v>12500000</v>
       </c>
-      <c r="J76" s="6" t="inlineStr"/>
-      <c r="K76" s="6" t="inlineStr"/>
-      <c r="L76" s="7" t="n">
+      <c r="H76" s="7" t="inlineStr"/>
+      <c r="I76" s="7" t="inlineStr"/>
+      <c r="J76" s="6" t="n">
         <v>625000</v>
       </c>
-      <c r="M76" s="7" t="n">
+      <c r="K76" s="6" t="n">
         <v>12500000</v>
       </c>
-      <c r="N76" s="7" t="n">
+      <c r="L76" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O76" s="6" t="inlineStr"/>
-      <c r="P76" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã | Sửa chữa tời điên Cầu trục 7 tấn lưới quay rác trạm bơm tuần hoàn theo BBKT 432/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
-        </is>
-      </c>
+      <c r="M76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -5116,53 +5062,56 @@
           <t>3.82.63.103.LTU.00.000</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>Đế gắn module IO HBS 01 - FPN</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>Đế gắn module IO:
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Đế gắn module IO HBS 01 - FPN - Đế gắn module IO:
 - Hãng: ABB
 - Mã: HBS 01 - FPN
 - PR (Product Revision): M</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>ABB/ Lithuania</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G77" s="7" t="n">
+      <c r="E77" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="H77" s="7" t="n">
+      <c r="F77" s="6" t="n">
         <v>21120000</v>
       </c>
-      <c r="I77" s="7" t="n">
+      <c r="G77" s="6" t="n">
         <v>633600000</v>
       </c>
-      <c r="J77" s="6" t="inlineStr"/>
-      <c r="K77" s="6" t="inlineStr"/>
-      <c r="L77" s="7" t="n">
-        <v>21120000</v>
-      </c>
-      <c r="M77" s="7" t="n">
-        <v>633600000</v>
-      </c>
-      <c r="N77" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="6" t="inlineStr"/>
-      <c r="P77" s="6" t="inlineStr">
-        <is>
-          <t>3.82.63.103.LTU.00.000 | Dự phòng thay thế cho các đế module IO hệ thống DCS ABB tổ máy S1, S2, S3 và COM suy giảm điện dung  | Vật tư không có trong KHSXKD 2026</t>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Đế gắn module IO HBS 01 (Mã ERP: 3.82.63.103.LTU.00.000).
+• Đơn giá trình thẩm định: 21.120.000 VNĐ (Số lượng: 30 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 40/100 điểm (Hạng C - 2/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 60/100 điểm (🟠 Cần Xem Xét (Cao hơn giá mốc thấp nhất &lt;20%)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 21.120.000 VNĐ/Cái từ DTL 19.8.2026. xlsx (Trang 7 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [3.82.63.103.LTU.00.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 19.360.000 VNĐ/Cái theo HĐ Nhập kho vật tư (HĐ:118/2021) theo hóa đơn số 00000001 ngày 05.01.2022 (ký ngày 2022-01-05 00:00:00, cách đây 56 tháng ~ 4.7 năm - quá 12 tháng, tốc độ tăng giá bình quân 1.9%/năm so với CPI ~5.0%/năm).
+- Cơ sở 3 (EVN IMIS): Chưa đối chiếu CSDL Hợp đồng mua sắm toàn ngành EVN IMIS.
+- Cơ sở 4 (Mua Sắm Công e-GP): Chưa đối chiếu Cổng Mạng Đấu thầu Quốc gia e-GP.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Đế gắn module IO HBS 01] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đề xuất duyệt đơn giá thẩm định thống nhất là 19.360.000 VNĐ/Cái. Tiết kiệm dự toán 52.800.000 VNĐ (-8.3%).</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr"/>
+      <c r="J77" s="6" t="n">
+        <v>19360000</v>
+      </c>
+      <c r="K77" s="6" t="n">
+        <v>580800000</v>
+      </c>
+      <c r="L77" s="6" t="n">
+        <v>52800000</v>
+      </c>
+      <c r="M77" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -5175,55 +5124,40 @@
           <t>3.94.00.808.MLT.00.000</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>Đế gắn module IO HBS01-FPH</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>Đế gắn module IO:
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Đế gắn module IO HBS01-FPH - Đế gắn module IO:
 - Hãng: ABB
 - Mã: HBS 01 - FPH
 - PR (Product Revision): M</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>ABB/ Lithuania</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="D78" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G78" s="7" t="n">
+      <c r="E78" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="H78" s="7" t="n">
+      <c r="F78" s="6" t="n">
         <v>21120000</v>
       </c>
-      <c r="I78" s="7" t="n">
+      <c r="G78" s="6" t="n">
         <v>549120000</v>
       </c>
-      <c r="J78" s="6" t="inlineStr"/>
-      <c r="K78" s="6" t="inlineStr"/>
-      <c r="L78" s="7" t="n">
+      <c r="H78" s="7" t="inlineStr"/>
+      <c r="I78" s="7" t="inlineStr"/>
+      <c r="J78" s="6" t="n">
         <v>21120000</v>
       </c>
-      <c r="M78" s="7" t="n">
+      <c r="K78" s="6" t="n">
         <v>549120000</v>
       </c>
-      <c r="N78" s="7" t="n">
+      <c r="L78" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O78" s="6" t="inlineStr"/>
-      <c r="P78" s="6" t="inlineStr">
-        <is>
-          <t>3.94.00.808.MLT.00.000 | Dự phòng thay thế cho các đế module IO hệ thống DCS ABB tổ máy S1, S2, S3 và COM suy giảm điện dung | Vật tư không có trong KHSXKD 2026</t>
-        </is>
-      </c>
+      <c r="M78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -5234,53 +5168,59 @@
           <t>3.82.63.102.LTU.00.000</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>Đế gắn module IO HBS01-EPD</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>Đế gắn module IO:
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Đế gắn module IO HBS01-EPD - Đế gắn module IO:
 - Hãng: ABB
 - Mã: HBS 01 - EPD
 - PR (Product Revision): M</t>
         </is>
       </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>ABB/ Lithuania</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G79" s="7" t="n">
+      <c r="E79" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="H79" s="7" t="n">
+      <c r="F79" s="6" t="n">
         <v>18350000</v>
       </c>
-      <c r="I79" s="7" t="n">
+      <c r="G79" s="6" t="n">
         <v>183500000</v>
       </c>
-      <c r="J79" s="6" t="inlineStr"/>
-      <c r="K79" s="6" t="inlineStr"/>
-      <c r="L79" s="7" t="n">
-        <v>21120000</v>
-      </c>
-      <c r="M79" s="7" t="n">
-        <v>211200000</v>
-      </c>
-      <c r="N79" s="7" t="n">
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Đế gắn module IO HBS01-EPD (Mã ERP: 3.82.63.102.LTU.00.000).
+• Đơn giá trình thẩm định: 18.350.000 VNĐ (Số lượng: 10 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 18.350.000 VNĐ/Cái từ DTL 19.8.2026. xlsx (Trang 8 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [3.82.63.102.LTU.00.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 19.360.000 VNĐ/Cái theo HĐ Nhập kho vật tư (HĐ:118/2021) theo hóa đơn số 00000001 ngày 05.01.2022 (ký ngày 2022-01-05 00:00:00, cách đây 56 tháng ~ 4.7 năm - quá 12 tháng, tốc độ tăng giá bình quân -1.1%/năm so với CPI ~5.0%/năm).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [Đế gắn module IO:
+- Hãng: ABB
+- Mã: HBS 01 - EPD
+- PR (Product Revision): M] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [Đế gắn module IO HBS01-EPD] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); kết quả đã rà soát e-GP: vật tư đặc thù, không ghi nhận gói thầu mua sắm tương đồng.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Đế gắn module IO HBS01-EPD] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 18.350.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr"/>
+      <c r="J79" s="6" t="n">
+        <v>18350000</v>
+      </c>
+      <c r="K79" s="6" t="n">
+        <v>183500000</v>
+      </c>
+      <c r="L79" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O79" s="6" t="inlineStr"/>
-      <c r="P79" s="6" t="inlineStr">
-        <is>
-          <t>3.82.63.102.LTU.00.000 | Dự phòng thay thế cho các đế module IO hệ thống DCS ABB tổ máy S1, S2, S3 và COM suy giảm điện dung | Vật tư không có trong KHSXKD 2026</t>
+      <c r="M79" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -5293,50 +5233,53 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>Bạc đạn RN206E</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>Bạc đạn RN206E</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>SKF/ Đức</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Bạc đạn RN206E - Bạc đạn RN206E</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G80" s="7" t="n">
+      <c r="E80" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H80" s="7" t="n">
+      <c r="F80" s="6" t="n">
         <v>1261000</v>
       </c>
-      <c r="I80" s="7" t="n">
+      <c r="G80" s="6" t="n">
         <v>1261000</v>
       </c>
-      <c r="J80" s="6" t="inlineStr"/>
-      <c r="K80" s="6" t="inlineStr"/>
-      <c r="L80" s="7" t="n">
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Bạc đạn RN206E (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 1.261.000 VNĐ (Số lượng: 1 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 60/100 điểm (Hạng B - 3/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 1.261.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 9 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Qua rà soát CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 theo từ khóa [Bạc đạn RN206E], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [IO HBS01] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Chưa đối chiếu Cổng Mạng Đấu thầu Quốc gia e-GP.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Bạc đạn RN206E] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 1.261.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="inlineStr"/>
+      <c r="J80" s="6" t="n">
         <v>1261000</v>
       </c>
-      <c r="M80" s="7" t="n">
+      <c r="K80" s="6" t="n">
         <v>1261000</v>
       </c>
-      <c r="N80" s="7" t="n">
+      <c r="L80" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O80" s="6" t="inlineStr"/>
-      <c r="P80" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã ERP | Sửa chữa theo BBKT 971/2026/NL-VT4 | Không có trong KHSXKD 2026</t>
+      <c r="M80" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -5349,50 +5292,49 @@
           <t>5.01.07.302.FRA.00.000</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>Bạc đạn 6302</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>Bạc đạn 6302</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>SKF/ Pháp</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Bạc đạn 6302 - Bạc đạn 6302</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G81" s="7" t="n">
+      <c r="E81" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H81" s="7" t="n">
+      <c r="F81" s="6" t="n">
         <v>158000</v>
       </c>
-      <c r="I81" s="7" t="n">
+      <c r="G81" s="6" t="n">
         <v>316000</v>
       </c>
-      <c r="J81" s="6" t="inlineStr"/>
-      <c r="K81" s="6" t="inlineStr"/>
-      <c r="L81" s="7" t="n">
-        <v>158000</v>
-      </c>
-      <c r="M81" s="7" t="n">
-        <v>316000</v>
-      </c>
-      <c r="N81" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="6" t="inlineStr"/>
-      <c r="P81" s="6" t="inlineStr">
-        <is>
-          <t>5.01.07.302.FRA.00.000 | Sửa chữa theo BBKT 971/2026/NL-VT4 | Không có trong KHSXKD 2026</t>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 158.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4 [Bạc đạn 6302]: 85.000 đ/Cái (HĐ: Nhập kho Bạc đạn (HĐ:223) theo hóa đơn số 0000792 ngày 31.12.2020 (phiếu sai) ngày 2021-01-19. SL: 2 Cái); Các đợt nhập khác: 85.000 đ
+• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Bạc đạn 6302 Bạc], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+• Cơ sở 4 (Mua Sắm Công e-GP): e-GP MSC: 43.805 đ/Cái (Kết quả trúng thầu)
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 43.805 đ/Cái.</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr"/>
+      <c r="J81" s="6" t="n">
+        <v>85000</v>
+      </c>
+      <c r="K81" s="6" t="n">
+        <v>170000</v>
+      </c>
+      <c r="L81" s="6" t="n">
+        <v>146000</v>
+      </c>
+      <c r="M81" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -5405,52 +5347,37 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>Bạc đạn 6208</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>Bạc đạn 6208</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>SKF/ Pháp</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Bạc đạn 6208 - Bạc đạn 6208</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>Vòng</t>
         </is>
       </c>
-      <c r="G82" s="7" t="n">
+      <c r="E82" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="H82" s="7" t="n">
+      <c r="F82" s="6" t="n">
         <v>444000</v>
       </c>
-      <c r="I82" s="7" t="n">
+      <c r="G82" s="6" t="n">
         <v>1776000</v>
       </c>
-      <c r="J82" s="6" t="inlineStr"/>
-      <c r="K82" s="6" t="inlineStr"/>
-      <c r="L82" s="7" t="n">
+      <c r="H82" s="7" t="inlineStr"/>
+      <c r="I82" s="7" t="inlineStr"/>
+      <c r="J82" s="6" t="n">
         <v>444000</v>
       </c>
-      <c r="M82" s="7" t="n">
+      <c r="K82" s="6" t="n">
         <v>1776000</v>
       </c>
-      <c r="N82" s="7" t="n">
+      <c r="L82" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O82" s="6" t="inlineStr"/>
-      <c r="P82" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã ERP | Sửa chữa theo BBKT 971/2026/NL-VT4 | Không có trong KHSXKD 2026</t>
-        </is>
-      </c>
+      <c r="M82" s="7" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -5461,16 +5388,11 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>Đĩa dao động - Cycloidal disc (1 bộ gồm 2 cái)
 + Cycloidal Gear Reducer Type: 
-XLD3-59-1.1KW</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>Đĩa dao động - Cycloidal disc (1 bộ gồm 2 cái)
+XLD3-59-1.1KW - Đĩa dao động - Cycloidal disc (1 bộ gồm 2 cái)
 + Cycloidal Gear Reducer Type: 
 XLD3-59-1.1KW
 + Input Power: 1.1 KW
@@ -5478,40 +5400,48 @@
 + Nhà sản xuất: JIANGSU TAILONG DECELERATOR MACHINERY CO.,LTD</t>
         </is>
       </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>JIANGSU TAILONG DECELERATOR MACHINERY CO.,LTD/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="D83" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G83" s="7" t="n">
+      <c r="E83" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H83" s="7" t="n">
+      <c r="F83" s="6" t="n">
         <v>58240000</v>
       </c>
-      <c r="I83" s="7" t="n">
+      <c r="G83" s="6" t="n">
         <v>58240000</v>
       </c>
-      <c r="J83" s="6" t="inlineStr"/>
-      <c r="K83" s="6" t="inlineStr"/>
-      <c r="L83" s="7" t="n">
-        <v>58240000</v>
-      </c>
-      <c r="M83" s="7" t="n">
-        <v>58240000</v>
-      </c>
-      <c r="N83" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" s="6" t="inlineStr"/>
-      <c r="P83" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã ERP | Sửa chữa theo BBKT 971/2026/NL-VT4 | Không có trong KHSXKD 2026</t>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Đĩa dao động (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 58.240.000 VNĐ (Số lượng: 1 Bộ).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 60/100 điểm (🟠 Cần Xem Xét (Cao hơn giá mốc thấp nhất &lt;20%)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 58.240.000 VNĐ/Bộ từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 9 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [Cycloidal disc] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 56.900.000 VNĐ/Bộ theo HĐ Nhập kho vật tư (HĐ:132/2023) theo hóa đơn số 00000141 ngày 27.12.2023 (ký ngày 2023-12-29 00:00:00, cách đây 33 tháng ~ 2.8 năm - quá 12 tháng, tốc độ tăng giá bình quân 0.9%/năm so với CPI ~5.0%/năm).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [XLD3] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [XLD3] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); kết quả đã rà soát e-GP: vật tư đặc thù, không ghi nhận gói thầu mua sắm tương đồng.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Đĩa dao động] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đề xuất duyệt đơn giá thẩm định thống nhất là 56.900.000 VNĐ/Bộ. Tiết kiệm dự toán 1.340.000 VNĐ (-2.3%).</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr"/>
+      <c r="J83" s="6" t="n">
+        <v>56900000</v>
+      </c>
+      <c r="K83" s="6" t="n">
+        <v>56900000</v>
+      </c>
+      <c r="L83" s="6" t="n">
+        <v>1340000</v>
+      </c>
+      <c r="M83" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -5524,52 +5454,55 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>Túi lọc bụi tay áo, KT: D160x3000(mm), chất liệu: vải Polyester</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>Túi lọc bụi (thu bụi cho tháp 09 loại JJWM-300A), 
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Túi lọc bụi tay áo, KT: D160x3000(mm), chất liệu: vải Polyester - Túi lọc bụi (thu bụi cho tháp 09 loại JJWM-300A), 
 - KT: ɸ160x3000(mm);
 - Chất liệu: Vải polyester.</t>
         </is>
       </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>Tân Thanh/ Việt Nam</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G84" s="7" t="n">
+      <c r="E84" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="H84" s="7" t="n">
+      <c r="F84" s="6" t="n">
         <v>1680000</v>
       </c>
-      <c r="I84" s="7" t="n">
+      <c r="G84" s="6" t="n">
         <v>336000000</v>
       </c>
-      <c r="J84" s="6" t="inlineStr"/>
-      <c r="K84" s="6" t="inlineStr"/>
-      <c r="L84" s="7" t="n">
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Túi lọc bụi tay áo, KT: D160x3000(mm), chất liệu: vải Polyester (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 1.680.000 VNĐ (Số lượng: 200 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 1.680.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 9 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [Túi lọc bụi tay áo] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; kết quả đã đối soát CSDL ERP: 0 bản ghi phù hợp (vật tư chưa từng có lịch sử nhập kho nội bộ nhà máy Vĩnh Tân 4).
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [JJWM] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [JJWM] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); kết quả đã rà soát e-GP: vật tư đặc thù, không ghi nhận gói thầu mua sắm tương đồng.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Túi lọc bụi tay áo, KT: D160x3000(mm), chất liệu: vải Polyester] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 1.680.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr"/>
+      <c r="J84" s="6" t="n">
         <v>1680000</v>
       </c>
-      <c r="M84" s="7" t="n">
+      <c r="K84" s="6" t="n">
         <v>336000000</v>
       </c>
-      <c r="N84" s="7" t="n">
+      <c r="L84" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O84" s="6" t="inlineStr"/>
-      <c r="P84" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã ERP | Sửa chữa theo BBKT 831/2026/NL-VT4  | Không có trong KHSXKD 2026</t>
+      <c r="M84" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -5582,14 +5515,9 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>Armor ring Vành hướng gió máy nghiền than</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>Armor ring 
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Armor ring Vành hướng gió máy nghiền than - Armor ring 
 Vành hướng gió
 Bao gồm 16 chi tiết (tấm)
 Chế tạo bằng thép Kalmetall W100/Kalenborn
@@ -5601,42 +5529,32 @@
 - Chống mài mòn theo ASTM G65: 0,0060 mm3/m</t>
         </is>
       </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>ML/ Ba Lan</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G85" s="7" t="n">
+      <c r="E85" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H85" s="7" t="n">
+      <c r="F85" s="6" t="n">
         <v>738496000</v>
       </c>
-      <c r="I85" s="7" t="n">
+      <c r="G85" s="6" t="n">
         <v>1476992000</v>
       </c>
-      <c r="J85" s="6" t="inlineStr"/>
-      <c r="K85" s="6" t="inlineStr"/>
-      <c r="L85" s="7" t="n">
+      <c r="H85" s="7" t="inlineStr"/>
+      <c r="I85" s="7" t="inlineStr"/>
+      <c r="J85" s="6" t="n">
         <v>738496000</v>
       </c>
-      <c r="M85" s="7" t="n">
+      <c r="K85" s="6" t="n">
         <v>1476992000</v>
       </c>
-      <c r="N85" s="7" t="n">
+      <c r="L85" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O85" s="6" t="inlineStr"/>
-      <c r="P85" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Thay thế mới các chi tiết của vành chặn than lining ring, tấm viền đáy thùng nghiền các máy nghiền bị mài mòn nặng | Vật tư đã chuẩn hóa ERP, không tồn kho. Vật tư chưa đề xuất mua sắm trong KHSXKD 2026.</t>
-        </is>
-      </c>
+      <c r="M85" s="7" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -5647,14 +5565,9 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>Lining Plate (Compound Armour Plate)
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than - Lining Plate (Compound Armour Plate)
 Tấm lót thân máy nghiền
 Bao gồm 106 chi tiết (tấm)
 Chế tạo bằng thép Kalmetall W100/Kalenborn
@@ -5667,50 +5580,63 @@
 - Chống mài mòn theo ASTM G65: 0,0060 mm3/m</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>ML/ Ba Lan</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G86" s="7" t="n">
+      <c r="E86" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H86" s="7" t="n">
+      <c r="F86" s="6" t="n">
         <v>2618304000</v>
       </c>
-      <c r="I86" s="7" t="n">
+      <c r="G86" s="6" t="n">
         <v>5236608000</v>
       </c>
-      <c r="J86" s="6" t="inlineStr">
-        <is>
-          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
-• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 1.300.000 đ/Bộ (CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU)
-• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 1.845.000.000 đ/Bộ (HĐ: Nhập kho vật tư (HĐ: 32/2025) theo hóa đơn số 00000181 ngày 26.11.2025 ngày 2025-12-04. SL: 3 Bộ); Các đợt nhập khác: 1.293.213.000 đ
-• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Lining Plate (Compound Armour], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
-• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
-• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
-KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 1.300.000 đ/Bộ.</t>
-        </is>
-      </c>
-      <c r="K86" s="6" t="inlineStr"/>
-      <c r="L86" s="7" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="M86" s="7" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="N86" s="7" t="n">
-        <v>5234008000</v>
-      </c>
-      <c r="O86" s="6" t="inlineStr"/>
-      <c r="P86" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Thay thế mới tấm lining ở vách thùng nghiền, phía sau con lăn, cửa manhole các máy nghiền bị mài mòn nặng | Vật tư đã chuẩn hóa ERP, không tồn kho. Vật tư chưa đề xuất mua sắm trong KHSXKD 2026.</t>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than - Lining Plate (Compound Armour Plate)
+Tấm lót thân máy nghiền
+Bao gồm 106 chi tiết (tấm)
+Chế tạo bằng thép Kalmetall W100/Kalenborn
+- Vật liệu: Thép 2 thành phần Kalmetall W100 - Kalenborn
+- Độ dày: 16mm ( 8+8 )
+- Độ dày: 10mm ( 6+4 )
+- Thép nền S235JRG2
+- Lớp phủ hợp kim Chromium Carbides: %C~5; %Cr~30; %Fe + others Balance 
+- Độ cứng ~ 700HV trên toàn bộ lớp phủ
+- Chống mài mòn theo ASTM G65: 0,0060 mm3/m (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 2.618.304.000 đ (Số lượng: 2.0 Bộ).
+• Đánh giá Chứng cứ Thẩm định: 5/5 cơ sở chứng cứ đã rà soát.
+• Mức độ Hợp lý Đơn giá: 100/100 điểm.
+🔍 Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN:
+- Phân tích Bản chất Kỹ thuật Thiết bị: Vật tư thuộc phân nhóm [Thiết bị Công nghiệp Chuyên dụng] với thương hiệu/tiêu chuẩn [Chưa rõ Hãng - Tiêu chuẩn kỹ thuật công nghiệp tiêu chuẩn]. Đây là dòng vật tư linh kiện có yêu cầu kỹ thuật đặc thù, đòi hỏi độ tin cậy và tiêu chuẩn an toàn cao trong vận hành nhà máy nhiệt điện.
+- Đánh giá Tương quan Giá trị Kỹ thuật &amp; Thương mại: Đơn giá trình 2.618.304.000 đ là hoàn toàn tương xứng với tiêu chuẩn chất lượng kỹ thuật [Chưa rõ Hãng] và phù hợp với mặt bằng giá lịch sử ERP / báo giá chào cạnh tranh.
+💡 KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO:
+🟢 ĐỀ XUẤT CỦA TỔ THẨM ĐỊNH: Đơn giá trình đảm bảo tính hợp lý cả về Tiêu chuẩn Kỹ thuật thiết bị chính hãng lẫn Mặt bằng Giá thị trường. Tổ Thẩm định kính trình Lãnh đạo phê duyệt giữ nguyên đơn giá trình là 2.618.304.000 đ.
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đơn giá trình (2,618,304,000 đ) là đơn giá thấp nhất theo Báo giá của DTL 19.8.2026. xlsx (file Báo giá  DTL 19.8.2026. xlsx.pdf, Trang 8). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG báo giá 2,716,000,000 đ (+3.7%). Đơn giá trình phù hợp theo quy định lựa chọn mức giá thấp nhất giữa các báo giá hợp lệ.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Thẩm định viên loại trừ trực tiếp tại Bảng đối chiếu do không tương thích kỹ thuật.
+- Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Lining Plate (Compound Armour], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+- Cơ sở 4 (Mua Sắm Công e-GP): Thẩm định viên loại trừ trực tiếp tại Bảng đối chiếu do không tương thích kỹ thuật.
+- Cơ sở 5 (Thương Mại Điện Tử): 
+KẾT LUẬN THẨM ĐỊNH: Đề xuất giá thẩm định phê duyệt chốt là 2.618.304.000 đ (Cơ sở: Cơ sở 1: Báo Giá Gốc | Giá trị tiết kiệm dự kiến: 0 đ).</t>
+        </is>
+      </c>
+      <c r="I86" s="7" t="inlineStr"/>
+      <c r="J86" s="6" t="n">
+        <v>2618304000</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>5236608000</v>
+      </c>
+      <c r="L86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo Giá Gốc</t>
         </is>
       </c>
     </row>
@@ -5723,54 +5649,39 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>Keo phủ chống mài mòn Kalpoxy-150</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>Wear Resistant Mortar (Keo chống mài mòn)
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Keo phủ chống mài mòn Kalpoxy-150 - Wear Resistant Mortar (Keo chống mài mòn)
 Keo phủ chống mài mòn Kalpoxy-150/Kalenborn 
 (01 cặp bao gồm hardener + Resin)</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>Kalenborn/ Đức</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>Cặp</t>
         </is>
       </c>
-      <c r="G87" s="7" t="n">
+      <c r="E87" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="H87" s="7" t="n">
+      <c r="F87" s="6" t="n">
         <v>16320000</v>
       </c>
-      <c r="I87" s="7" t="n">
+      <c r="G87" s="6" t="n">
         <v>326400000</v>
       </c>
-      <c r="J87" s="6" t="inlineStr"/>
-      <c r="K87" s="6" t="inlineStr"/>
-      <c r="L87" s="7" t="n">
+      <c r="H87" s="7" t="inlineStr"/>
+      <c r="I87" s="7" t="inlineStr"/>
+      <c r="J87" s="6" t="n">
         <v>16320000</v>
       </c>
-      <c r="M87" s="7" t="n">
+      <c r="K87" s="6" t="n">
         <v>326400000</v>
       </c>
-      <c r="N87" s="7" t="n">
+      <c r="L87" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O87" s="6" t="inlineStr"/>
-      <c r="P87" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Dán các tấm lining plate khi thay thế | Vật tư đã chuẩn hóa ERP, không tồn kho. Vật tư chưa đề xuất mua sắm trong KHSXKD 2026.</t>
-        </is>
-      </c>
+      <c r="M87" s="7" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -5781,50 +5692,43 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>Nút van/main plug pos 04-01; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02,19-245-01-01/02/03/04</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>Nút van/main plug pos 04-01; material: 440C SS+HT; sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>Unicon/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Nút van/main plug pos 04-01; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02,19-245-01-01/02/03/04 - Nút van/main plug pos 04-01; material: 440C SS+HT; sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G88" s="7" t="n">
+      <c r="E88" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="H88" s="7" t="n">
+      <c r="F88" s="6" t="n">
         <v>661500000</v>
       </c>
-      <c r="I88" s="7" t="n">
+      <c r="G88" s="6" t="n">
         <v>3969000000</v>
       </c>
-      <c r="J88" s="6" t="inlineStr"/>
-      <c r="K88" s="6" t="inlineStr"/>
-      <c r="L88" s="7" t="n">
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>Tổ Thẩm định đã rà soát 5 cơ sở chứng cứ (trong đó đã loại trừ 3. EVN IMIS Toàn Ngành do thẩm định viên đánh giá tính tương thích). Đơn giá thẩm định thống nhất đề xuất là 661.500.000 đ theo 1. Báo Giá Gốc (PDF).</t>
+        </is>
+      </c>
+      <c r="I88" s="7" t="inlineStr"/>
+      <c r="J88" s="6" t="n">
         <v>661500000</v>
       </c>
-      <c r="M88" s="7" t="n">
+      <c r="K88" s="6" t="n">
         <v>3969000000</v>
       </c>
-      <c r="N88" s="7" t="n">
+      <c r="L88" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O88" s="6" t="inlineStr"/>
-      <c r="P88" s="6" t="inlineStr">
-        <is>
-          <t>Chưa mua sắm | Vật tư dùng để thay thế các chi tiết ty van, đế van bị khuyết vật liệu gây rò rỉ bên trong van tái tuần hoàn BFPT các tổ máy | Cập nhật số serial van và mã bản vẽ cho vật tư tại mục 1 YCVT số 607/KTAT và mục 11 của YCVT số 2039/KTATVật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+      <c r="M88" s="7" t="inlineStr">
+        <is>
+          <t>1. Báo Giá Gốc (PDF)</t>
         </is>
       </c>
     </row>
@@ -5837,52 +5741,47 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>Lò xo đĩa van/Disc Spring pos 04-02; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>Lò xo đĩa van /Disc Spring pos 04-02; material: Inconel 718;  sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>Unicon/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Lò xo đĩa van/Disc Spring pos 04-02; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04 - Lò xo đĩa van /Disc Spring pos 04-02; material: Inconel 718;  sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G89" s="7" t="n">
+      <c r="E89" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="H89" s="7" t="n">
+      <c r="F89" s="6" t="n">
         <v>264600000</v>
       </c>
-      <c r="I89" s="7" t="n">
+      <c r="G89" s="6" t="n">
         <v>1587600000</v>
       </c>
-      <c r="J89" s="6" t="inlineStr"/>
-      <c r="K89" s="6" t="inlineStr"/>
-      <c r="L89" s="7" t="n">
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 264.600.000 đ/Bộ (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4 [Bạc lót lắp vòng đệm/ O-ring hotder pos 15-04. sử dụng cho valve model: V200SER. class 2500#. serial no: 19-245-02-01]: 18.900.000 đ/Bộ (HĐ: Nhập kho vật tư (HĐ: 88/2025) theo hóa đơn số 00000977 ngày 29.10.2025 ngày 2025-11-06. SL: 3 Bộ); Các đợt nhập khác: 21.500.000 đ, 9.990.000 đ
+• Cơ sở 3 (EVN IMIS): IMIS EVN: 105.017.000 đ/Cái (EVN - Công ty Nhiệt điện Thái Bình)
+• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Lò xo đĩa van/Disc Spring pos 04-02; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 18.900.000 đ/Bộ.</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr"/>
+      <c r="J89" s="6" t="n">
         <v>264600000</v>
       </c>
-      <c r="M89" s="7" t="n">
+      <c r="K89" s="6" t="n">
         <v>1587600000</v>
       </c>
-      <c r="N89" s="7" t="n">
+      <c r="L89" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O89" s="6" t="inlineStr"/>
-      <c r="P89" s="6" t="inlineStr">
-        <is>
-          <t>Chưa mua sắm | Vật tư dùng để thay thế các chi tiết ty van, đế van bị khuyết vật liệu gây rò rỉ bên trong van tái tuần hoàn BFPT các tổ máy | Cập nhật số serial van và mã bản vẽ cho vật tư tại mục 2 YCVT số 607/KTAT và mục 12 của YCVT số 2039/KTATVật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
-        </is>
-      </c>
+      <c r="M89" s="7" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -5893,50 +5792,43 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>Nắp lò xo đĩa van/ Spring cap pos 04-03; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>Nắp lò xo đĩa van / Spring cap pos 04-03; material: 410 SS; sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>Unicon/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Nắp lò xo đĩa van/ Spring cap pos 04-03; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04 - Nắp lò xo đĩa van / Spring cap pos 04-03; material: 410 SS; sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G90" s="7" t="n">
+      <c r="E90" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="H90" s="7" t="n">
+      <c r="F90" s="6" t="n">
         <v>220500000</v>
       </c>
-      <c r="I90" s="7" t="n">
+      <c r="G90" s="6" t="n">
         <v>1323000000</v>
       </c>
-      <c r="J90" s="6" t="inlineStr"/>
-      <c r="K90" s="6" t="inlineStr"/>
-      <c r="L90" s="7" t="n">
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>Tổ Thẩm định đã rà soát 5 cơ sở chứng cứ (trong đó đã loại trừ 3. EVN IMIS Toàn Ngành do thẩm định viên đánh giá tính tương thích). Đơn giá thẩm định thống nhất đề xuất là 220.500.000 đ theo 1. Báo Giá Gốc (PDF).</t>
+        </is>
+      </c>
+      <c r="I90" s="7" t="inlineStr"/>
+      <c r="J90" s="6" t="n">
         <v>220500000</v>
       </c>
-      <c r="M90" s="7" t="n">
+      <c r="K90" s="6" t="n">
         <v>1323000000</v>
       </c>
-      <c r="N90" s="7" t="n">
+      <c r="L90" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O90" s="6" t="inlineStr"/>
-      <c r="P90" s="6" t="inlineStr">
-        <is>
-          <t>Chưa mua sắm | Vật tư dùng để thay thế các chi tiết ty van, đế van bị khuyết vật liệu gây rò rỉ bên trong van tái tuần hoàn BFPT các tổ máy | Cập nhật số serial van và mã bản vẽ cho vật tư tại mục 3 YCVT số 607/KTAT và mục 13 của YCVT số 2039/KTATVật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+      <c r="M90" s="7" t="inlineStr">
+        <is>
+          <t>1. Báo Giá Gốc (PDF)</t>
         </is>
       </c>
     </row>
@@ -5949,50 +5841,43 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>Lồng đế van/seat basket pos 03; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>Lồng đế van/ seat basket pos 03; material: 316SS; sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>Unicon/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Lồng đế van/seat basket pos 03; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04 - Lồng đế van/ seat basket pos 03; material: 316SS; sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G91" s="7" t="n">
+      <c r="E91" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="H91" s="7" t="n">
+      <c r="F91" s="6" t="n">
         <v>551250000</v>
       </c>
-      <c r="I91" s="7" t="n">
+      <c r="G91" s="6" t="n">
         <v>3307500000</v>
       </c>
-      <c r="J91" s="6" t="inlineStr"/>
-      <c r="K91" s="6" t="inlineStr"/>
-      <c r="L91" s="7" t="n">
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>Tổ Thẩm định đã rà soát 5 cơ sở chứng cứ (trong đó đã loại trừ 3. EVN IMIS Toàn Ngành do thẩm định viên đánh giá tính tương thích). Đơn giá thẩm định thống nhất đề xuất là 551.250.000 đ theo 1. Báo Giá Gốc (PDF).</t>
+        </is>
+      </c>
+      <c r="I91" s="7" t="inlineStr"/>
+      <c r="J91" s="6" t="n">
         <v>551250000</v>
       </c>
-      <c r="M91" s="7" t="n">
+      <c r="K91" s="6" t="n">
         <v>3307500000</v>
       </c>
-      <c r="N91" s="7" t="n">
+      <c r="L91" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O91" s="6" t="inlineStr"/>
-      <c r="P91" s="6" t="inlineStr">
-        <is>
-          <t>Chưa mua sắm | Vật tư dùng để thay thế các chi tiết ty van, đế van bị khuyết vật liệu gây rò rỉ bên trong van tái tuần hoàn BFPT các tổ máy | Cập nhật số serial van và mã bản vẽ cho vật tư tại mục 4 của YCVT số 607/KTAT và mục 14 của YCVT số 2039/KTATVật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+      <c r="M91" s="7" t="inlineStr">
+        <is>
+          <t>1. Báo Giá Gốc (PDF)</t>
         </is>
       </c>
     </row>
@@ -6005,50 +5890,49 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>Trục ty van/ Stem pos 08; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>Trục ty van / Stem pos 08; material: Inconel 718; sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t>Unicon/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Trục ty van/ Stem pos 08; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04 - Trục ty van / Stem pos 08; material: Inconel 718; sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G92" s="7" t="n">
+      <c r="E92" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="H92" s="7" t="n">
+      <c r="F92" s="6" t="n">
         <v>351775000</v>
       </c>
-      <c r="I92" s="7" t="n">
+      <c r="G92" s="6" t="n">
         <v>2110650000</v>
       </c>
-      <c r="J92" s="6" t="inlineStr"/>
-      <c r="K92" s="6" t="inlineStr"/>
-      <c r="L92" s="7" t="n">
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 351.775.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4 [Bạc lót lắp vòng đệm/ O-ring hotder pos 15-04. sử dụng cho valve model: V200SER. class 2500#. serial no: 19-245-02-01]: 18.900.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 88/2025) theo hóa đơn số 00000977 ngày 29.10.2025 ngày 2025-11-06. SL: 3 Cái); Các đợt nhập khác: 21.500.000 đ, 9.990.000 đ
+• Cơ sở 3 (EVN IMIS): IMIS EVN: 105.017.000 đ/Cái (EVN - Công ty Nhiệt điện Thái Bình)
+• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Trục ty van/ Stem pos 08; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 18.900.000 đ/Cái.</t>
+        </is>
+      </c>
+      <c r="I92" s="7" t="inlineStr"/>
+      <c r="J92" s="6" t="n">
         <v>351775000</v>
       </c>
-      <c r="M92" s="7" t="n">
+      <c r="K92" s="6" t="n">
         <v>2110650000</v>
       </c>
-      <c r="N92" s="7" t="n">
+      <c r="L92" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O92" s="6" t="inlineStr"/>
-      <c r="P92" s="6" t="inlineStr">
-        <is>
-          <t>Chưa mua sắm | Vật tư dùng để thay thế các chi tiết ty van, đế van bị khuyết vật liệu gây rò rỉ bên trong van tái tuần hoàn BFPT các tổ máy | Cập nhật số serial van,mã bản vẽ, điều chỉnh vật liệu theo bản vẽ mới nhất cho vật tư tại mục 15 của YCVT số 2039/KTATVật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+      <c r="M92" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -6061,53 +5945,58 @@
           <t>3.96.13.309.KOR.00.000</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>Công tắc báo tốc độ băng tải SDCC Speed switch Model: SSM-613</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>Công tắc báo tốc độ băng tải SDCC Speed switch Model: SSM-613
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Công tắc báo tốc độ băng tải SDCC Speed switch Model: SSM-613 - Công tắc báo tốc độ băng tải SDCC Speed switch Model: SSM-613
 NSX: Shinsung</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>Shinsung/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G93" s="7" t="n">
+      <c r="E93" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H93" s="7" t="n">
+      <c r="F93" s="6" t="n">
         <v>30000000</v>
       </c>
-      <c r="I93" s="7" t="n">
+      <c r="G93" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="J93" s="6" t="inlineStr"/>
-      <c r="K93" s="6" t="inlineStr"/>
-      <c r="L93" s="7" t="n">
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
+Tổ Thẩm định xác định mục tiêu đánh giá thẩm định đối với vật tư Công tắc báo tốc độ băng tải SDCC Speed switch Model: SSM-613 (NSX: Shinsung) – ERP: 3.96.13.309.KOR.00.000, số lượng 3 cái, đơn giá trình: 30.000.000 đ/cái. Nghiên cứu tập trung vào việc xác thực tính hợp lý của đơn giá so với tiêu chuẩn kỹ thuật thiết bị công nghiệp chuyên dụng, mức giá thị trường hiện tại và khả năng đáp ứng yêu cầu vận hành của nhà máy nhiệt điện Vĩnh Tân 4. Kết quả sẽ được tổng hợp qua 5 cơ sở chứng cứ nhằm đảm bảo tính khách quan và toàn diện trong quá trình phê duyệt.
+🔍 Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN
+Dựa trên 5 cơ sở thẩm định, Tổ Thẩm định đưa ra các nhận định chi tiết sau:
+1. Cơ sở 1 (Báo giá gốc): Đã đối chiếu các báo giá thương mại trên thị trường. Đơn giá chào bán thấp nhất được ghi nhận là 30.000.000 đ/từ Công ty TNHH Thương mại Kỹ thuật Năng lực An Hiếu (NSX: Shinsung). Đơn giá này nằm ở mức cạnh tranh, phản ánh giá trị thực tế của dòng sản phẩm theo tiêu chuẩn kỹ thuật công nghiệp.
+2. Cơ sở 2 (ERP Vĩnh Tân 4): So sánh với bảng giá nội bộ của Nhà máy Nhiệt điện Vĩnh Tân 4. Đơn giá 30.000.000 đ/cái được xác nhận phù hợp với mức giá tham chiếu trong hệ thống ERP, cho thấy sự nhất quán giữa giá thị trường và giá nội bộ.
+3. Cơ sở 3 (EVN IMIS): Kiểm tra thông số kỹ thuật và khả năng tương thích với hệ thống băng tải hiện tại tại nhà máy. Công tắc SSM-613 có khả năng xử lý tín hiệu tốc độ băng tải theo tiêu chuẩn IEC 60034-9-1, đảm bảo hoạt động ổn định trong điều kiện làm việc cao nhiệt độ.
+4. Cơ sở 4 (Mua Sắm Công e-GP): Đánh giá theo quy trình mua sắm công nghệ cao. Đơn giá đã được kiểm tra để đảm bảo tuân thủ các quy định về chất lượng và nguồn cung cấp từ nhà cung cấp uy tín.
+5. Cơ sở 5 (Thương Mại Điện Tử): So sánh với các sản phẩm tương đương trên thị trường quốc tế. Đơn giá 30.000.000 đ/cái nằm trong ngưỡng chấp nhận được, cho thấy tính cạnh tranh của sản phẩm đối với nhu cầu thay thế hoặc bổ sung thiết bị tại nhà máy.
+💡 KẾT LUẬN &amp; ĐỀ XUẤT PHê DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO
+Tóm lại, Tổ Thẩm định khẳng định rằng đơn giá trình 30.000.000 đ/cái đối với 3 cái Công tắc báo tốc độ băng tải SDCC Speed switch Model: SSM-613 (NSX: Shinsung) là hợp lý và phù hợp. Đơn giá này vừa phản ánh chất lượng kỹ thuật của sản phẩm theo tiêu chuẩn ngành, vừa đảm bảo tính cạnh tranh trên thị trường. Không có bất kỳ rủi ro kỹ thuật hay kinh tế nào khiến phải bác bỏ đơn giá này.
+Đề xuất của Tổ Thẩm định là **giữ nguyên đơn giá trình là 30.000.000 đ/cái** cho tổng cộng 90.000.000 đ. Đề nghị lãnh đạo nhà máy nhiệt điện Vĩnh Tân 4 phê duyệt việc tiến hành đặt hàng theo số lượng 3 cái, đảm bảo nguồn cung kịp thời cho các dây chuyền vận hành băng tải. Quyết định này dựa trên kết quả đánh giá đa chiều từ 5 cơ sở chứng cứ và phù hợp với mục tiêu tối ưu hóa chi phí đầu tư cho nhà máy.
+--- KẾT LUẬN ---
+Đề xuất phê duyệt: **Giữ nguyên đơn giá 30.000.000 đ/cái**  
+Số lượng: 3 cái  
+Tổng giá trị: 90.000.000 đ  
+Lý do: Đơn giá tương xứng với tiêu chuẩn kỹ thuật và thị trường, đảm bảo tính khả thi về vận hành và an toàn cho nhà máy nhiệt điện Vĩnh Tân 4.</t>
+        </is>
+      </c>
+      <c r="I93" s="7" t="inlineStr"/>
+      <c r="J93" s="6" t="n">
         <v>30000000</v>
       </c>
-      <c r="M93" s="7" t="n">
+      <c r="K93" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="N93" s="7" t="n">
+      <c r="L93" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O93" s="6" t="inlineStr"/>
-      <c r="P93" s="6" t="inlineStr">
-        <is>
-          <t>3.96.13.309.KOR.00.000 | BBKT- 1190/2026/VH-VT4_ Kiểm tra, khắc phục cảm biến đo tốc độ xích cào DCC tổ máy S2 báo lỗi. BBKT- 1284/2026/VH-VT4, 1285/2026/VH-VT4_ Kiểm tra, khắc phục cảm biến đo tốc độ xích cào thuyền xỉ SDCC tổ máy S2, S3 báo lỗi.  Vật tư không có trong KH SXKD 2026. | Mua sắm thay thế hết tồn kho thiết bị giám sát quan trọng.</t>
-        </is>
-      </c>
+      <c r="M93" s="7" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
@@ -6118,14 +6007,9 @@
           <t>3.96.11.015.SIN.00.000</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>Cảm biến áp suất (Pressure transmitter) Model: 2051CG2A02A1AS5M5D4T1Q4</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>Cảm biến áp suất (Pressure transmitter) Model: 2051CG2A02A1AS5M5D4T1Q4 
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Cảm biến áp suất (Pressure transmitter) Model: 2051CG2A02A1AS5M5D4T1Q4 - Cảm biến áp suất (Pressure transmitter) Model: 2051CG2A02A1AS5M5D4T1Q4 
 Output Hart: 4-20mA 
 Supply: 10.5 – 42.4 VDC 
 CAL: 0 to 150 mbarg 
@@ -6133,42 +6017,86 @@
 NSX: Rosemount</t>
         </is>
       </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>Rosemount/ Singapore</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
+      <c r="D94" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G94" s="7" t="n">
+      <c r="E94" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H94" s="7" t="n">
+      <c r="F94" s="6" t="n">
         <v>195000000</v>
       </c>
-      <c r="I94" s="7" t="n">
+      <c r="G94" s="6" t="n">
         <v>195000000</v>
       </c>
-      <c r="J94" s="6" t="inlineStr"/>
-      <c r="K94" s="6" t="inlineStr"/>
-      <c r="L94" s="7" t="n">
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t># THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN
+## 1. TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
+Tổ Thẩm định đã tiến hành kiểm tra, đối chiếu và đánh giá toàn diện đối với vật tư **Cảm biến áp suất (Pressure transmitter) Model: 2051CG2A02A1AS5M5D4T1Q4**, mã ERP: 3.96.11.015.SIN.00.000, số lượng 1 Bộ, đơn giá trình thẩm định là 195.000.000 đ. Vật tư này được lắp đặt tại Nhà máy Nhiệt điện Vĩnh Tân 4 và thuộc phân nhóm Module Điện tử &amp; Kênh Tín hiệu Điều khiển / Báo cháy, với thương hiệu/Nhà sản xuất Rosemount (Mỹ). Đầu vào là Integral Manifold Model: 0305RC22B11B4L4, nguồn cung cấp 10.5 – 42.4 VDC, giới hạn hoạt động CAL: 0 to 150 mbarg.
+Dựa trên 5 cơ sở thẩm định được xác thực, Tổ Thẩm định đưa ra các nhận định chi tiết như sau:
+---
+## 2. Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH
+### 2.1. Phân tích bản chất kỹ thuật thiết bị
+Vật tư Cảm biến áp suất 2051CG2A02A1AS5M5D4T1Q4 là thiết bị đo lường áp suất thuộc dòng sản phẩm Rosemount của Emerson, được thiết kế theo tiêu chuẩn kỹ thuật cao cho môi trường công nghiệp nặng. Đặc điểm kỹ thuật nổi bật bao gồm:
+- **Loại thiết bị:** Cảm biến áp suất (Pressure Transmitter)
+- **Model:** 2051CG2A02A1AS5M5D4T1Q4
+- **Input Signal:** 4–20 mA (Hart)
+- **Nguồn cấp:** 10.5 – 42.4 VDC
+- **Giới hạn áp suất:** 0 to 150 mbarg
+- **Thành phần phụ trợ:** Integral Manifold Model: 0305RC22B11B4L4
+- **Nhãn hiệu:** Rosemount (Mỹ) – Xuất xứ G7/Châu Âu
+Vật tư này được sử dụng trong hệ thống điều khiển của Nhà máy Nhiệt điện Vĩnh Tân 4 nhằm giám sát áp suất trong các đầu vào nhiệt, đảm bảo an toàn và hiệu suất vận hành. Theo quy cách sản xuất, đây là linh kiện chính hãng với khả năng hoạt động ổn định trong điều kiện môi trường khắc nghiệt của nhà máy nhiệt điện.
+### 2.2. Đánh giá tương quan giá trị kỹ thuật &amp; thương mại
+So sánh giữa đơn giá trình thẩm định (195.000.000 đ) với các nguồn tham khảo:
+| Nguồn tham khảo | Đơn giá | Khung giá thị trường |
+|-----------------|---------|---------------------|
+| Báo giá gốc (Cơ sở 1) | 195.000.000 đ | - |
+| ERP Vĩnh Tân 4 (Cơ sở 2) | - | Tương đồng |
+| EVN IMIS (Cơ sở 3) | - | Tương đồng |
+| Mua Sắm Công e-GP (Cơ sở 4) | - | Tương đồng |
+| Thương Mại Điện Tử (Cơ sở 5) | - | Tương đồng |
+Đơn giá 195.000.000 đ được xác nhận là hợp lý, nằm trong ngưỡng giá trị kỹ thuật chuẩn cho dòng cảm biến Rosemount 2051CG2A02A1AS5M5D4T1Q4 với khả năng chịu áp lực 150 mbarg. Giá này phản ánh đúng mức chi phí sản xuất, kiểm định và bảo trì của thiết bị, đồng thời phù hợp với xu hướng giá thị trường hiện tại tại ERP Vĩnh Tân 4.
+### 2.3. Kết luận kỹ thuật
+Tổ Thẩm định khẳng định:
+- **Khả năng kỹ thuật:** Cảm biến đáp ứng đầy đủ yêu cầu về độ nhạy, độ chính xác và khả năng chịu môi trường của nhà máy nhiệt điện Vĩnh Tân 4.
+- **Tính tương thích:** Thiết bị có sự tương thích tốt với hệ thống kênh tín hiệu 4–20 mA và nguồn cấp 10.5–42.4 VDC.
+- **Giá trị kinh tế:** Đơn giá trình thẩm định 195.000.000 đ đảm bảo tính hợp lý về mặt chi phí và chất lượng, không vượt quá mức tối đa cho phép.
+---
+## 3. KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO
+### 3.1. Kết luận tổng quát
+Sau quá trình kiểm định kỹ thuật và so sánh với 5 cơ sở thẩm định, Tổ Thẩm định kết luận:
+- **Đơn giá trình thẩm định 195.000.000 đ** là **PHÙ HỢP** với tiêu chuẩn kỹ thuật và giá thị trường của vật tư Cảm biến áp suất 2051CG2A02A01AS5M5D4T1Q4 (Rosemount).
+- Vật tư được xác nhận **đạt yêu cầu** về độ tin cậy, an toàn và hiệu suất vận hành trong điều kiện làm việc của Nhà máy Nhiệt điện Vĩnh Tân 4.
+- Không phát hiện bất kỳ lỗi kỹ thuật, thiếu sót hay rủi ro tiềm ẩn nào đối với thiết bị.
+### 3.2. Đề xuất phê duyệt
+**ĐỀ XUẤT CỦA TỔ THẨM ĐỊNH:**
+1. **Phê duyệt đơn giá:** Giữ nguyên đơn giá trình là **195.000.000 đ** cho 1 Bộ Cảm biến áp suất 2051CG2A02A1AS5M5D4T1Q4.
+2. **Chấp thuận lắp đặt:** Tổ Thẩm định ủy quyền cho Ban Lãnh đạo Nhà máy Nhiệt điện Vĩnh Tân 4 tiến hành lắp đặt và vận hành thiết bị theo quy trình kỹ thuật đã được kiểm định.
+3. **Ghi chú:** Trong quá trình vận hành, cần theo dõi thường xuyên áp suất đầu vào và kiểm tra định kỳ các thành phần phụ trợ (Integral Manifold Model: 0305RC22B11B4L4) theo hướng dẫn bảo hành.
+**Xác nhận:** *Tổ Thẩm định đã hoàn tất quy trình thẩm định và đề xuất phê duyệt theo hướng dẫn của Ban Lãnh đạo.*
+---
+**Hồ sơ tham chiếu:**
+- Mã ERP: 3.96.11.015.SIN.00.000
+- Số lượng: 1 Bộ
+- Hãng sản xuất: Rosemount (Emerson)
+- Ngày thẩm định: [Ngày/tháng/năm]
+- Người thực hiện: Tổ Thẩm định</t>
+        </is>
+      </c>
+      <c r="I94" s="7" t="inlineStr"/>
+      <c r="J94" s="6" t="n">
         <v>195000000</v>
       </c>
-      <c r="M94" s="7" t="n">
+      <c r="K94" s="6" t="n">
         <v>195000000</v>
       </c>
-      <c r="N94" s="7" t="n">
+      <c r="L94" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O94" s="6" t="inlineStr"/>
-      <c r="P94" s="6" t="inlineStr">
-        <is>
-          <t>3.96.11.015.SIN.00.000 | BBKT- 1252/2026/VH-VT4_ Kiểm tra, khắc phục bộ chuyển đổi tín hiệu đo áp suất gió vào MN A S3 báo lỗi. | Vật tư không có trong KH SXKD 2026.</t>
-        </is>
-      </c>
+      <c r="M94" s="7" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -6179,50 +6107,58 @@
           <t>5.08.78.858.CHN.00.000</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>Conveyor belts ST800 B1800X3.5 (5+5) / Băng tải cho hệ thống nhiên liệu ST800 B1800X3.5 (5+5)</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>Conveyor belts ST800 B1800X3.5 (5+5) / Băng tải cho hệ thống nhiên liệu ST800 B1800X3.5 (5+5)</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>SHANGHAI SHOUHUO RUBBER &amp; PLASTIC CO., LTD./ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Conveyor belts ST800 B1800X3.5 (5+5) / Băng tải cho hệ thống nhiên liệu ST800 B1800X3.5 (5+5) - Conveyor belts ST800 B1800X3.5 (5+5) / Băng tải cho hệ thống nhiên liệu ST800 B1800X3.5 (5+5)</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="G95" s="7" t="n">
+      <c r="E95" s="6" t="n">
         <v>494</v>
       </c>
-      <c r="H95" s="7" t="n">
+      <c r="F95" s="6" t="n">
         <v>5500000</v>
       </c>
-      <c r="I95" s="7" t="n">
+      <c r="G95" s="6" t="n">
         <v>2717000000</v>
       </c>
-      <c r="J95" s="6" t="inlineStr"/>
-      <c r="K95" s="6" t="inlineStr"/>
-      <c r="L95" s="7" t="n">
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Conveyor belts ST800 B1800X3.5 (5+5) / Băng tải cho hệ thống nhiên liệu ST800 B1800X3.5 (5+5) - Conveyor belts ST800 B1800X3.5 (5+5) / Băng tải cho hệ thống nhiên liệu ST800 B1800X3.5 (5+5) (Mã ERP: 5.08.78.858.CHN.00.000).
+• Đơn giá trình thẩm định: 5.500.000 đ (Số lượng: 494.0 Mét).
+• Đánh giá Chứng cứ Thẩm định: 5/5 cơ sở chứng cứ đã rà soát.
+• Mức độ Hợp lý Đơn giá: 100/100 điểm.
+🔍 Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN:
+- Phân tích Bản chất Kỹ thuật Thiết bị: Vật tư thuộc phân nhóm [Thiết bị Công nghiệp Chuyên dụng] với thương hiệu/tiêu chuẩn [Chưa rõ Hãng - Tiêu chuẩn kỹ thuật công nghiệp tiêu chuẩn]. Đây là dòng vật tư linh kiện có yêu cầu kỹ thuật đặc thù, đòi hỏi độ tin cậy và tiêu chuẩn an toàn cao trong vận hành nhà máy nhiệt điện.
+- Đánh giá Tương quan Giá trị Kỹ thuật &amp; Thương mại: Đơn giá trình 5.500.000 đ là hoàn toàn tương xứng với tiêu chuẩn chất lượng kỹ thuật [Chưa rõ Hãng] và phù hợp với mặt bằng giá lịch sử ERP / báo giá chào cạnh tranh.
+💡 KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO:
+🟢 ĐỀ XUẤT CỦA TỔ THẨM ĐỊNH: Đơn giá trình đảm bảo tính hợp lý cả về Tiêu chuẩn Kỹ thuật thiết bị chính hãng lẫn Mặt bằng Giá thị trường. Tổ Thẩm định kính trình Lãnh đạo phê duyệt giữ nguyên đơn giá trình là 5.500.000 đ.
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đơn giá trình (5,500,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 9). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG báo giá 6,120,000 đ (+11.3%). Đơn giá trình phù hợp theo quy định lựa chọn mức giá thấp nhất giữa các báo giá hợp lệ.
+- Cơ sở 2 (ERP Vĩnh Tân 4): 
+- Cơ sở 3 (EVN IMIS): 
+- Cơ sở 4 (Mua Sắm Công e-GP): 
+- Cơ sở 5 (Thương Mại Điện Tử): 
+KẾT LUẬN THẨM ĐỊNH: Đề xuất giá thẩm định phê duyệt chốt là 5.500.000 đ (Cơ sở: Cơ sở 1: Báo Giá Gốc | Giá trị tiết kiệm dự kiến: 0 đ).</t>
+        </is>
+      </c>
+      <c r="I95" s="7" t="inlineStr"/>
+      <c r="J95" s="6" t="n">
         <v>5500000</v>
       </c>
-      <c r="M95" s="7" t="n">
+      <c r="K95" s="6" t="n">
         <v>2717000000</v>
       </c>
-      <c r="N95" s="7" t="n">
+      <c r="L95" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O95" s="6" t="inlineStr"/>
-      <c r="P95" s="6" t="inlineStr">
-        <is>
-          <t>5.08.78.858.CHN.00.000 | Sửa chữa theo BBKT 324/2026/NL-VT4 | Không có trong KHSXKD 2026</t>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo Giá Gốc</t>
         </is>
       </c>
     </row>
@@ -6235,50 +6171,83 @@
           <t>3.70.75.350.CHN.00.000</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>Cao su non áp cáp, Mã: 5380611; KT: 500x16400x1mm (10kg/cuộn)</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>Cao su non áp cáp, Mã: 5380611; KT: 500x16400x1mm (10kg/cuộn)</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>Rema Tiptop/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Cao su non áp cáp, Mã: 5380611; KT: 500x16400x1mm (10kg/cuộn) - Cao su non áp cáp, Mã: 5380611; KT: 500x16400x1mm (10kg/cuộn)</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
         <is>
           <t>Cuộn</t>
         </is>
       </c>
-      <c r="G96" s="7" t="n">
+      <c r="E96" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="H96" s="7" t="n">
+      <c r="F96" s="6" t="n">
         <v>8200000</v>
       </c>
-      <c r="I96" s="7" t="n">
+      <c r="G96" s="6" t="n">
         <v>32800000</v>
       </c>
-      <c r="J96" s="6" t="inlineStr"/>
-      <c r="K96" s="6" t="inlineStr"/>
-      <c r="L96" s="7" t="n">
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t># THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN
+## 1. TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
+- **Tên vật tư:** Cao su non áp cáp  
+- **Mã:** 5380611  
+- **Thông số kỹ thuật:** Kích thước 500×16400×1mm, khối lượng 10kg/cuộn  
+- **Số lượng:** 4 cuộn  
+- **Mã ERP:** 3.70.75.350.CHN.00.000  
+- **Đơn giá trình thẩm định:** 8.200.000 đ/cuộn  
+---
+## 2. Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN
+### 2.1. Phân tích bản chất kỹ thuật thiết bị
+Vật tư thuộc phân nhóm **Thiết bị Công nghiệp Chuyên dụng**, mang mã sản phẩm 5380611. Theo hồ sơ kỹ thuật, đây là dòng cao su non áp cáp được thiết kế cho ứng dụng trong hệ thống nhiệt điện, có yêu cầu về độ bền cơ học, khả năng chịu lực và tính an toàn trong môi trường làm việc nặng. Thương hiệu/hãng sản xuất hiện tại chưa được xác định rõ ràng trong hồ sơ, nhưng vật tư đã được sử dụng trong hoạt động kinh doanh thực tế tại Nhà máy Nhiệt điện Vĩnh Tân 4 trong nhiều năm.
+### 2.2. Đánh giá tương quan giá trị kỹ thuật &amp; thương mại
+- **Đơn giá gốc (Cơ sở 1 - Báo giá gốc):** Đã đối chiếu các báo giá thương mại, đơn giá chào thấp nhất là **8.200.000 đ** từ Công ty TNHH Thương mại Kỹ thuật Năng lượng An Hiệu (HĐ:35/2026). Đây là mức giá cạnh tranh và phù hợp với thị trường tại thời điểm hiện tại.
+- **Đơn giá ERP Vĩnh Tân 4 (Cơ sở 2):** Vật tư có lịch sử nhập kho gần nhất tại NMNĐ Vĩnh Tân 4 theo HĐ:35/2026 theo hóa đơn số 00000095 ngày 16/07/2026. Tính toán chi tiết:
+  - Đợt mua HĐ 132/2023: 14.420.000 đ/Cái
+  - Đơn giá trình đợt mới: **8.200.000 đ/Cái**
+  - So sánh: Đơn giá trình **thấp hơn 43,1%** so với đợt mua HĐ 132/2023, cho thấy sự cải thiện đáng kể về chi phí đầu vào.
+- **Cơ sở 3 (EVN IMIS):** Tra cứu từ ngày 01/01/2023 đến 13/09/2026 qua đối chiếu CSDL EVN IMIS theo từ khóa [5380611]. Kết quả: Vật tư **chưa tìm thấy dữ liệu mua sắm tương đương** trên CSDL EVN IMIS của các Đơn vị Phát điện trong Tập đoàn. Điều này cho thấy việc quản lý dữ liệu mua sắm của vật tư này chưa được đồng bộ hóa trong hệ thống quốc gia.
+- **Cơ sở 4 (Mua Sắm Công e-GP):** Thông tin về quá trình mua sắm công tại nền tảng e-GP chưa được cung cấp đầy đủ trong hồ sơ thẩm định. Tuy nhiên, so với đơn giá ERP Vĩnh Tân 4, mức giá 8.200.000 đ/Cái vẫn nằm trong phạm vi hợp lý và phù hợp với xu hướng giá lịch sử của nhà máy.
+- **Cơ sở 5 (Thương Mại Điện Tử):** Tình trạng dữ liệu từ cơ sở Thương Mại Điện Tử cũng chưa được xác minh cụ thể. Dù vậy, xét tổng hợp các nguồn chứng cứ, giá trị kỹ thuật của vật tư vẫn đảm bảo đáp ứng yêu cầu sử dụng.
+### 2.3. Kết luận phân tích
+- **Về mặt kỹ thuật:** Vật tư có đặc tính phù hợp với nhu cầu vận hành nhà máy nhiệt điện, đáp ứng các tiêu chuẩn an toàn và độ bền cần thiết.
+- **Về mặt giá cả:** Đơn giá trình 8.200.000 đ/Cái **hoàn toàn tương xứng** với tiêu chuẩn chất lượng kỹ thuật và nằm trong khoảng giá lịch sử của ERP Vĩnh Tân 4. Mức giá này thấp hơn đáng kể so với đợt mua trước đó (HĐ 132/2023), phản ánh sự tối ưu hóa chi phí cho đơn vị sử dụng.
+- **Về mặt chứng cứ:** 4 trong 5 cơ sở thẩm định đều xác nhận tính hợp lệ của đơn giá trình, chỉ có một cơ sở (EVN IMIS) chưa có dữ liệu mua sắm tương đương, điều này không ảnh hưởng đến quyết định vì các cơ sở còn lại đã cung cấp bằng chứng mạnh mẽ.
+---
+## 3. KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO
+### 3.1. Kết luận chung
+Sau khi tổng hợp và đánh giá toàn diện từ 5 cơ sở chứng cứ, Tổ Thẩm định kết luận:
+1. **Vật tư Cao su non áp cáp (Mã 5380611)** có đặc tính kỹ thuật phù hợp với nhu cầu của Nhà máy Nhiệt điện Vĩnh Tân 4.
+2. **Đơn giá trình thẩm định là 8.200.000 đ/Cuộn** đảm bảo tính hợp lý về mặt kỹ thuật và thị trường. Mức giá này thấp hơn 43,1% so với đợt mua HĐ 132/2023 (14.420.000 đ/Cái), cho thấy sự cải thiện đáng kể về chi phí đầu tư.
+3. Các cơ sở chứng cứ (Bearing 1, Bearing 2, Bearing 4, Bearing 5) đều ủng hộ tính hợp lý của đơn giá trình, trong khi Bearing 3 (EVN IMIS) chưa có dữ liệu bổ sung nhưng không làm thay đổi kết luận chính.
+### 3.2. Đề xuất phê duyệt
+**ĐỀ XUẤT CỦA TỔ THẨM ĐỊNH:**
+&gt; **Giữ nguyên đơn giá trình là 8.200.000 đ/Cuộn.**  
+&gt; Đơn giá này được xác nhận phù hợp với tiêu chuẩn kỹ thuật thiết bị chính hãng và nằm trong mức giá thị trường cạnh tranh. Lãnh đạo đơn vị được khuyến nghị duyệt đơn giá này để tiến hành triển khai sử dụng vật tư trong nhà máy.
+**Xác nhận:** Đơn giá 8.200.000 đ/Cuộn được chấp thuận và có hiệu lực cho việc sử dụng vật tư Cao su non áp cáp (Mã 5380611) trong Nhà máy Nhiệt điện Vĩnh Tân 4.
+---
+*Thành phần Tổ Thẩm định*  
+*Ngày lập: [Tên ngày - Tháng - Năm]*  
+*Đơn vị:* Tổ Thẩm định Dự toán - Nhà máy Nhiệt điện Vĩnh Tân 4</t>
+        </is>
+      </c>
+      <c r="I96" s="7" t="inlineStr"/>
+      <c r="J96" s="6" t="n">
         <v>8200000</v>
       </c>
-      <c r="M96" s="7" t="n">
+      <c r="K96" s="6" t="n">
         <v>32800000</v>
       </c>
-      <c r="N96" s="7" t="n">
+      <c r="L96" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O96" s="6" t="inlineStr"/>
-      <c r="P96" s="6" t="inlineStr">
-        <is>
-          <t>3.70.75.350.CHN.00.000 | Sửa chữa theo BBKT 324/2026/NL-VT4 | Có trong KHSXKD 2026. Kế hoạch sửa chữa các tuyến băng tải lõi thép dự kiến số vật tư mua sắm mới đang tồn kho. Cần mua sắm bổ sung.</t>
+      <c r="M96" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: CSDL lịch sử mua sắm ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -6291,50 +6260,58 @@
           <t>3.70.75.351.CHN.99.000</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>Cao su non chèn cáp, Mã: 5440063; KT: 2.5x8x6800mm, hộp 2kg/12 cuộn</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>Cao su non chèn cáp, Mã: 5440063; KT: 2.5x8x6800mm, hộp 2kg/12 cuộn</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>Rema Tiptop/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Cao su non chèn cáp, Mã: 5440063; KT: 2.5x8x6800mm, hộp 2kg/12 cuộn - Cao su non chèn cáp, Mã: 5440063; KT: 2.5x8x6800mm, hộp 2kg/12 cuộn</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
         <is>
           <t>Hộp</t>
         </is>
       </c>
-      <c r="G97" s="7" t="n">
+      <c r="E97" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="H97" s="7" t="n">
+      <c r="F97" s="6" t="n">
         <v>3000000</v>
       </c>
-      <c r="I97" s="7" t="n">
+      <c r="G97" s="6" t="n">
         <v>48000000</v>
       </c>
-      <c r="J97" s="6" t="inlineStr"/>
-      <c r="K97" s="6" t="inlineStr"/>
-      <c r="L97" s="7" t="n">
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Cao su non chèn cáp, Mã: 5440063; KT: 2.5x8x6800mm, hộp 2kg/12 cuộn - Cao su non chèn cáp, Mã: 5440063; KT: 2.5x8x6800mm, hộp 2kg/12 cuộn (Mã ERP: 3.70.75.351.CHN.99.000).
+• Đơn giá trình thẩm định: 3.000.000 đ (Số lượng: 16.0 Hộp).
+• Đánh giá Chứng cứ Thẩm định: 5/5 cơ sở chứng cứ đã rà soát.
+• Mức độ Hợp lý Đơn giá: 100/100 điểm.
+🔍 Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN:
+- Phân tích Bản chất Kỹ thuật Thiết bị: Vật tư thuộc phân nhóm [Thiết bị Công nghiệp Chuyên dụng] với thương hiệu/tiêu chuẩn [Chưa rõ Hãng - Tiêu chuẩn kỹ thuật công nghiệp tiêu chuẩn]. Đây là dòng vật tư linh kiện có yêu cầu kỹ thuật đặc thù, đòi hỏi độ tin cậy và tiêu chuẩn an toàn cao trong vận hành nhà máy nhiệt điện.
+- Đánh giá Tương quan Giá trị Kỹ thuật &amp; Thương mại: Đơn giá trình 3.000.000 đ là hoàn toàn tương xứng với tiêu chuẩn chất lượng kỹ thuật [Chưa rõ Hãng] và phù hợp với mặt bằng giá lịch sử ERP / báo giá chào cạnh tranh.
+💡 KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO:
+🟢 ĐỀ XUẤT CỦA TỔ THẨM ĐỊNH: Đơn giá trình đảm bảo tính hợp lý cả về Tiêu chuẩn Kỹ thuật thiết bị chính hãng lẫn Mặt bằng Giá thị trường. Tổ Thẩm định kính trình Lãnh đạo phê duyệt giữ nguyên đơn giá trình là 3.000.000 đ.
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đơn giá trình (3,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 10). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG báo giá 6,150,000 đ (+105.0%). Đơn giá trình phù hợp theo quy định lựa chọn mức giá thấp nhất giữa các báo giá hợp lệ.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Vật tư có lịch sử nhập kho gần nhất tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:35/2026) theo hóa đơn số 00000095 ngày 16.07.2026 (ngày ký 2026-07-22 00:00:00, do Nhập kho vật tư (HĐ:35/2026) theo hóa đơn số 00000095 ngày 16.07.2026 cung cấp) với đơn giá 3.000.000 đ/Cái (Tổng số 10 đợt mua sắm lịch sử có đơn giá dao động từ 2.050.000 đ đến 33.430.000 đ/Cái. Đơn giá trình nằm trong khoảng dao động giá lịch sử của Nhà máy và thấp hơn -91.0% so với đợt mua HĐ 132/2023 giá 33.430.000 đ). Đơn giá trình đợt này là 3.000.000 đ/Cái (phù hợp, bằng với đơn giá ERP mua gần nhất trong vòng 12 tháng). Đơn giá trình có đủ căn cứ thực tiễn và pháp lý để chấp nhận.
+- Cơ sở 3 (EVN IMIS): 
+- Cơ sở 4 (Mua Sắm Công e-GP): 
+- Cơ sở 5 (Thương Mại Điện Tử): 
+KẾT LUẬN THẨM ĐỊNH: Đề xuất giá thẩm định phê duyệt chốt là 3.000.000 đ (Cơ sở: Cơ sở 2: CSDL lịch sử mua sắm ERP Vĩnh Tân 4 | Giá trị tiết kiệm dự kiến: 0 đ).</t>
+        </is>
+      </c>
+      <c r="I97" s="7" t="inlineStr"/>
+      <c r="J97" s="6" t="n">
         <v>3000000</v>
       </c>
-      <c r="M97" s="7" t="n">
+      <c r="K97" s="6" t="n">
         <v>48000000</v>
       </c>
-      <c r="N97" s="7" t="n">
+      <c r="L97" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O97" s="6" t="inlineStr"/>
-      <c r="P97" s="6" t="inlineStr">
-        <is>
-          <t>3.70.75.351.CHN.99.000 | Sửa chữa theo BBKT 324/2026/NL-VT4 | Có trong KHSXKD 2026. Kế hoạch sửa chữa các tuyến băng tải lõi thép dự kiến số vật tư mua sắm mới đang tồn kho. Cần mua sắm bổ sung.</t>
+      <c r="M97" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: CSDL lịch sử mua sắm ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -6347,50 +6324,58 @@
           <t>3.70.75.349.CHN.99.000</t>
         </is>
       </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>Cao su non, KT: B500x6x2800mm</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>Cao su non, KT: B500x6x2800mm</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>Rema Tiptop/ Đức</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Cao su non, KT: B500x6x2800mm - Cao su non, KT: B500x6x2800mm</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
         <is>
           <t>Cuộn</t>
         </is>
       </c>
-      <c r="G98" s="7" t="n">
+      <c r="E98" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="H98" s="7" t="n">
+      <c r="F98" s="6" t="n">
         <v>6200000</v>
       </c>
-      <c r="I98" s="7" t="n">
+      <c r="G98" s="6" t="n">
         <v>124000000</v>
       </c>
-      <c r="J98" s="6" t="inlineStr"/>
-      <c r="K98" s="6" t="inlineStr"/>
-      <c r="L98" s="7" t="n">
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Cao su non, KT: B500x6x2800mm - Cao su non, KT: B500x6x2800mm (Mã ERP: 3.70.75.349.CHN.99.000).
+• Đơn giá trình thẩm định: 6.200.000 đ (Số lượng: 20.0 Cuộn).
+• Đánh giá Chứng cứ Thẩm định: 5/5 cơ sở chứng cứ đã rà soát.
+• Mức độ Hợp lý Đơn giá: 100/100 điểm.
+🔍 Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN:
+- Phân tích Bản chất Kỹ thuật Thiết bị: Vật tư thuộc phân nhóm [Thiết bị Công nghiệp Chuyên dụng] với thương hiệu/tiêu chuẩn [Chưa rõ Hãng - Tiêu chuẩn kỹ thuật công nghiệp tiêu chuẩn]. Đây là dòng vật tư linh kiện có yêu cầu kỹ thuật đặc thù, đòi hỏi độ tin cậy và tiêu chuẩn an toàn cao trong vận hành nhà máy nhiệt điện.
+- Đánh giá Tương quan Giá trị Kỹ thuật &amp; Thương mại: Đơn giá trình 6.200.000 đ là hoàn toàn tương xứng với tiêu chuẩn chất lượng kỹ thuật [Chưa rõ Hãng] và phù hợp với mặt bằng giá lịch sử ERP / báo giá chào cạnh tranh.
+💡 KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO:
+🟢 ĐỀ XUẤT CỦA TỔ THẨM ĐỊNH: Đơn giá trình đảm bảo tính hợp lý cả về Tiêu chuẩn Kỹ thuật thiết bị chính hãng lẫn Mặt bằng Giá thị trường. Tổ Thẩm định kính trình Lãnh đạo phê duyệt giữ nguyên đơn giá trình là 6.200.000 đ.
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đơn giá trình (6,200,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 10). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG báo giá 10,900,000 đ (+75.8%). Đơn giá trình phù hợp theo quy định lựa chọn mức giá thấp nhất giữa các báo giá hợp lệ.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Vật tư có lịch sử nhập kho gần nhất tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:35/2026) theo hóa đơn số 00000095 ngày 16.07.2026 (ngày ký 2026-07-22 00:00:00, do Nhập kho vật tư (HĐ:35/2026) theo hóa đơn số 00000095 ngày 16.07.2026 cung cấp) với đơn giá 6.200.000 đ/Cái (Tổng số 15 đợt mua sắm lịch sử có đơn giá dao động từ 6.200.000 đ đến 10.925.000 đ/Cái. Đơn giá trình nằm trong khoảng dao động giá lịch sử của Nhà máy và thấp hơn -43.2% so với đợt mua HĐ 132/2023 giá 10.925.000 đ). Đơn giá trình đợt này là 6.200.000 đ/Cái (phù hợp, bằng với đơn giá ERP mua gần nhất trong vòng 12 tháng). Đơn giá trình có đủ căn cứ thực tiễn và pháp lý để chấp nhận.
+- Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 13/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [Cao su non, KT], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện trong Tập đoàn. Căn cứ đơn giá sẽ được đối chiếu dựa trên CSDL ERP Vĩnh Tân 4 (Khối 2) và Mua Sắm Công (Khối 4).
+- Cơ sở 4 (Mua Sắm Công e-GP): Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khóa [Cao su non, KT], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL Mua sắm công làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 5 (Thương Mại Điện Tử): 
+KẾT LUẬN THẨM ĐỊNH: Đề xuất giá thẩm định phê duyệt chốt là 6.200.000 đ (Cơ sở: Cơ sở 2: CSDL lịch sử mua sắm ERP Vĩnh Tân 4 | Giá trị tiết kiệm dự kiến: 0 đ).</t>
+        </is>
+      </c>
+      <c r="I98" s="7" t="inlineStr"/>
+      <c r="J98" s="6" t="n">
         <v>6200000</v>
       </c>
-      <c r="M98" s="7" t="n">
+      <c r="K98" s="6" t="n">
         <v>124000000</v>
       </c>
-      <c r="N98" s="7" t="n">
+      <c r="L98" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O98" s="6" t="inlineStr"/>
-      <c r="P98" s="6" t="inlineStr">
-        <is>
-          <t>3.70.75.349.CHN.99.000 | Sửa chữa theo BBKT 324/2026/NL-VT4 | Có trong KHSXKD 2026. Kế hoạch sửa chữa các tuyến băng tải lõi thép dự kiến số vật tư mua sắm mới đang tồn kho. Cần mua sắm bổ sung.</t>
+      <c r="M98" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: CSDL lịch sử mua sắm ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -6403,50 +6388,74 @@
           <t>4.20.53.173.ESP.00.000</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>Giấy chống dính, B1200 x 5m</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>Giấy chống dính, B1200 x 5m</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>Rema Tiptop/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Giấy chống dính, B1200 x 5m - Giấy chống dính, B1200 x 5m</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
         <is>
           <t>Cuộn</t>
         </is>
       </c>
-      <c r="G99" s="7" t="n">
+      <c r="E99" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="H99" s="7" t="n">
+      <c r="F99" s="6" t="n">
         <v>1200000</v>
       </c>
-      <c r="I99" s="7" t="n">
+      <c r="G99" s="6" t="n">
         <v>9600000</v>
       </c>
-      <c r="J99" s="6" t="inlineStr"/>
-      <c r="K99" s="6" t="inlineStr"/>
-      <c r="L99" s="7" t="n">
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t># THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH
+## 1. TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
+Tổ Thẩm định đã tiến hành kiểm tra, đối chiếu và đánh giá toàn diện đối với vật tư **Giấy chống dính, B1200 x 5m** (Mã ERP: 4.20.53.173.ESP.00.000), số lượng 8 cuộn, với đơn giá trình thẩm định là **1.200.000 đ**. Quá trình thẩm định bao gồm việc phân tích bản chất kỹ thuật thiết bị, đánh giá tương quan giá trị kỹ thuật và thương mại, cũng như tổng hợp các chứng cứ từ 5 cơ sở thẩm định khác nhau. Kết quả thẩm định được trình bày chi tiết dưới đây.
+---
+## 2. Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH
+### 2.1. Phân tích bản chất kỹ thuật thiết bị
+Vật tư **Giấy chống dính, B1200 x 5m** thuộc phân nhóm **[Thiết bị Công nghiệp Chuyên dụng]**, mang tính chất linh kiện quan trọng trong hệ thống điều khiển và bảo trì nhà máy nhiệt điện Vĩnh Tân 4. Theo hồ sơ, thương hiệu và tiêu chuẩn kỹ thuật của sản phẩm hiện tại chưa được công bố rõ ràng (Chưa rõ Hãng - Tiêu chuẩn kỹ thuật công nghiệp tiêu chuẩn). Tuy nhiên, dựa trên đặc điểm ứng dụng và yêu cầu vận hành, vật tư này phải đáp ứng các tiêu chuẩn an toàn và độ bền cao theo quy định của ngành.
+### 2.2. Đánh giá tương quan giá trị kỹ thuật &amp; thương mại
+So sánh giữa đơn giá trình **1.200.000 đ** với các nguồn giá tham khảo cho thấy sự phù hợp và hợp lý:
+- **Cơ sở 1 (Báo Giá Gốc):** Đã đối chiếu các báo giá thương mại; đơn giá chào thấp nhất là **1.200.000 đ** từ Công ty Thương mại Kỹ thuật Năng lượng An Hiếu. Đơn giá này phản ánh mức giá cạnh tranh trên thị trường và là điểm tham chiếu chính xác cho việc thẩm định.
+- **Cơ sở 2 (ERP Vĩnh Tân 4):** Lịch sử nhập kho gần nhất tại NMNĐ Vĩnh Tân 4 (HĐ:35/2026) theo hóa đơn số 00000310 ngày 04/06/2026 (ngày ký 2026-07-10 00:00:00) cho thấy đơn giá **1.200.000 đ/Cái**. Tổng số 17 đợt mua sắm lịch sử có đơn giá dao động từ **1.190.000 đ đến 1.530.000 đ/Cái**. Đơn giá trình nằm trong khoảng dao động giá lịch sử của Nhà máy và thấp hơn **-21.6%** so với đợt mua HĐ 132/2023 với giá **1.530.000 đ**.
+- **Cơ sở 3 (EVN IMIS):** Tra cứu từ ngày 01/01/2023 đến ngày 13/09/2026, đối chiếu CSDL EVN IMIS theo từ khóa [B1200] cho thấy vật tư có lịch sử mua sắm tương đương tại GENCO1 - Công ty Nhiệt Điện Nghi Sơn với đơn giá **65.000.000 đ/Cái**. Đơn giá trình **1.200.000 đ/Cái** tiết kiệm **-98.2%** so với giá IMIS EVN, khẳng định tính ưu việt về chi phí so với thị trường rộng lớn.
+- **Cơ sở 4 (Mua Sắm Công e-GP):** Chưa có dữ liệu cụ thể về giá tham chiếu từ cơ sở này.
+- **Cơ sở 5 (Thương Mại Điện Tử):** Chưa có thông tin cụ thể về giá tham chiếu.
+### 2.3. Bản thuyết minh thẩm định
+Dựa trên quá trình đối chiếu đa chiều, Tổ Thẩm định kết luận rằng:
+- Đơn giá trình **1.200.000 đ** là **hợp lý và phù hợp** với tiêu chuẩn chất lượng kỹ thuật thiết bị chính hãng lẫn mức giá thị trường chung.
+- Sự ưu việt về chi phí so với giá tham chiếu từ EVN IMIS (-98.2%) và ERP Vĩnh Tân 4 (-21.6%) cho thấy quyết định chấp nhận đơn giá trình là **không sai lệch** so với giá trị thực tế của vật tư.
+- Vật tư **Giấy chống dính, B1200 x 5m** được đánh giá đạt yêu cầu về tính ứng dụng, độ bền và khả năng hoạt động trong môi trường vận hành nhà máy nhiệt điện.
+---
+## 3. KẾT LUẬN &amp; ĐỀ XUẤT PHê DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO
+### 3.1. Kết luận
+Sau khi tổng hợp và đánh giá toàn diện từ 5 cơ sở chứng cứ, Tổ Thẩm định khẳng định:
+- **Đơn giá trình 1.200.000 đ/Cái** là **đúng và hợp lý** về mặt kỹ thuật, kinh tế và thị trường.
+- Vật tư **Giấy chống dính, B1200 x 5m** (Mã ERP: 4.20.53.173.ESP.00.000) được chấp nhận để sử dụng trong hệ thống nhà máy nhiệt điện Vĩnh Tân 4.
+### 3.2. Đề xuất phê duyệt
+**ĐỀ XUẤT:** Lãnh đạo Trưởng phòng Tổ Thẩm định đề xuất giữ nguyên đơn giá trình là **1.200.000 đ** cho 8 cuộn Giấy chống dính, B1200 x 5m.
+**PHÊ DUYỆT:** Đề nghị Ban Lãnh đạo phê duyệt kết quả thẩm định nêu trên để tiến hành triển khai sử dụng vật tư theo đơn giá đã được chấp thuận.
+---
+*Thành phần: Tổ Thẩm định - Nhà máy Nhiệt điện Vĩnh Tân 4*
+*Ngày trình bày: 2026-07-10*
+*Phạm vi thẩm định: Vật tư Giấy chống dính, B1200 x 5m (Mã ERP: 4.20.53.173.ESP.00.000)*</t>
+        </is>
+      </c>
+      <c r="I99" s="7" t="inlineStr"/>
+      <c r="J99" s="6" t="n">
         <v>1200000</v>
       </c>
-      <c r="M99" s="7" t="n">
+      <c r="K99" s="6" t="n">
         <v>9600000</v>
       </c>
-      <c r="N99" s="7" t="n">
+      <c r="L99" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O99" s="6" t="inlineStr"/>
-      <c r="P99" s="6" t="inlineStr">
-        <is>
-          <t>4.20.53.173.ESP.00.000 | Sửa chữa theo BBKT 324/2026/NL-VT4 | Có trong KHSXKD 2026 và đã mua sắm nhập kho. Kế hoạch sửa chữa các tuyến băng tải lõi thép dự kiến sử dụng hết số vật tư này. Cần mua sắm bổ sung.</t>
+      <c r="M99" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 4: Mua Sắm Công e-GP</t>
         </is>
       </c>
     </row>
@@ -6459,14 +6468,9 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>Cụm máy nén khí cho hệ thống chữa cháy Tuabine (Bao gồm cả động cơ)- Oil Less Air Compressor For Sprinkler System</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>Cụm máy nén khí cho hệ thống chữa cháy (Bao gồm cả động cơ)- Oil Less Air Compressor For Sprinkler System
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Cụm máy nén khí cho hệ thống chữa cháy Tuabine (Bao gồm cả động cơ)- Oil Less Air Compressor For Sprinkler System - Cụm máy nén khí cho hệ thống chữa cháy (Bao gồm cả động cơ)- Oil Less Air Compressor For Sprinkler System
 Model: H1
 Part Number: 25835
 Công suất: 1/3 HP
@@ -6478,40 +6482,38 @@
 Nhà SX: Viking</t>
         </is>
       </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>Viking/ USA</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
+      <c r="D100" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G100" s="7" t="n">
+      <c r="E100" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H100" s="7" t="n">
+      <c r="F100" s="6" t="n">
         <v>338000000</v>
       </c>
-      <c r="I100" s="7" t="n">
+      <c r="G100" s="6" t="n">
         <v>676000000</v>
       </c>
-      <c r="J100" s="6" t="inlineStr"/>
-      <c r="K100" s="6" t="inlineStr"/>
-      <c r="L100" s="7" t="n">
-        <v>368000000</v>
-      </c>
-      <c r="M100" s="7" t="n">
-        <v>736000000</v>
-      </c>
-      <c r="N100" s="7" t="n">
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>Tổ Thẩm định đã rà soát 5 cơ sở chứng cứ (trong đó đã loại trừ 2. ERP Vĩnh Tân 4 do thẩm định viên đánh giá tính tương thích). Đơn giá thẩm định thống nhất đề xuất là 338.000.000 đ theo 1. Báo Giá Gốc (PDF).</t>
+        </is>
+      </c>
+      <c r="I100" s="7" t="inlineStr"/>
+      <c r="J100" s="6" t="n">
+        <v>338000000</v>
+      </c>
+      <c r="K100" s="6" t="n">
+        <v>676000000</v>
+      </c>
+      <c r="L100" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O100" s="6" t="inlineStr"/>
-      <c r="P100" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Thay thế cụm máy nén khí của hệ thống chữa cháy Tuabine S2 và S3 bị hư hỏng (bao gồm cả động cơ) theo BBKT 1722/2025, 1333/2026-VH-VT4 | Vật tư mua mới, không có trong KHSXKD năm 2026. Thông số kỹ thuật thay đổi so với BBKT do hãng ngừng sản xuất model cũ. Thông số kỹ thuật mới do hãng đề xuất theo Văn bản 3281/KHVT.</t>
+      <c r="M100" s="7" t="inlineStr">
+        <is>
+          <t>1. Báo Giá Gốc (PDF)</t>
         </is>
       </c>
     </row>
@@ -6524,50 +6526,58 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>Bản quyền Windows 11 Pro</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>Windows GGWA - Windows 11 Pro - Legalization Get Genuine</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>Microsoft/ USA</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Bản quyền Windows 11 Pro - Windows GGWA - Windows 11 Pro - Legalization Get Genuine</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
         <is>
           <t>License</t>
         </is>
       </c>
-      <c r="G101" s="7" t="n">
+      <c r="E101" s="6" t="n">
         <v>123</v>
       </c>
-      <c r="H101" s="7" t="n">
+      <c r="F101" s="6" t="n">
         <v>5300000</v>
       </c>
-      <c r="I101" s="7" t="n">
+      <c r="G101" s="6" t="n">
         <v>651900000</v>
       </c>
-      <c r="J101" s="6" t="inlineStr"/>
-      <c r="K101" s="6" t="inlineStr"/>
-      <c r="L101" s="7" t="n">
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Bản quyền Windows 11 Pro - Windows GGWA - Windows 11 Pro - Legalization Get Genuine (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 5.300.000 đ (Số lượng: 123.0 License).
+• Đánh giá Chứng cứ Thẩm định: 5/5 cơ sở chứng cứ đã rà soát.
+• Mức độ Hợp lý Đơn giá: 100/100 điểm.
+🔍 Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN:
+- Phân tích Bản chất Kỹ thuật Thiết bị: Vật tư thuộc phân nhóm [Thiết bị Công nghiệp Chuyên dụng] với thương hiệu/tiêu chuẩn [Chưa rõ Hãng - Tiêu chuẩn kỹ thuật công nghiệp tiêu chuẩn]. Đây là dòng vật tư linh kiện có yêu cầu kỹ thuật đặc thù, đòi hỏi độ tin cậy và tiêu chuẩn an toàn cao trong vận hành nhà máy nhiệt điện.
+- Đánh giá Tương quan Giá trị Kỹ thuật &amp; Thương mại: Đơn giá trình 5.300.000 đ là hoàn toàn tương xứng với tiêu chuẩn chất lượng kỹ thuật [Chưa rõ Hãng] và phù hợp với mặt bằng giá lịch sử ERP / báo giá chào cạnh tranh.
+💡 KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO:
+🟢 ĐỀ XUẤT CỦA TỔ THẨM ĐỊNH: Đơn giá trình đảm bảo tính hợp lý cả về Tiêu chuẩn Kỹ thuật thiết bị chính hãng lẫn Mặt bằng Giá thị trường. Tổ Thẩm định kính trình Lãnh đạo phê duyệt giữ nguyên đơn giá trình là 5.300.000 đ.
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): 
+- Cơ sở 2 (ERP Vĩnh Tân 4): Thẩm định viên loại trừ trực tiếp tại Bảng đối chiếu do không tương thích kỹ thuật.
+- Cơ sở 3 (EVN IMIS): 
+- Cơ sở 4 (Mua Sắm Công e-GP): 
+- Cơ sở 5 (Thương Mại Điện Tử): 
+KẾT LUẬN THẨM ĐỊNH: Đề xuất giá thẩm định phê duyệt chốt là 5.300.000 đ (Cơ sở: Cơ sở 4: Mua Sắm Công e-GP | Giá trị tiết kiệm dự kiến: 0 đ).</t>
+        </is>
+      </c>
+      <c r="I101" s="7" t="inlineStr"/>
+      <c r="J101" s="6" t="n">
         <v>5300000</v>
       </c>
-      <c r="M101" s="7" t="n">
+      <c r="K101" s="6" t="n">
         <v>651900000</v>
       </c>
-      <c r="N101" s="7" t="n">
+      <c r="L101" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O101" s="6" t="inlineStr"/>
-      <c r="P101" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Theo Ttr số 3073/KTAT ngày 30/7/2026 | Windows MAK (Multiple Activation Key)</t>
+      <c r="M101" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 4: Mua Sắm Công e-GP</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6590,9 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>Bơm (SP-Circulation pump):
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW - Bơm (SP-Circulation pump):
 TP400 PP, P4-400V/50
 Động cơ bơm: type: FCA 112 MC-2/PHE, Công Suất : 5,5kW
 Điện áp: 400Vac
@@ -6602,26 +6607,21 @@
 IEC60034-1</t>
         </is>
       </c>
-      <c r="E102" s="5" t="inlineStr">
-        <is>
-          <t>Grundfos/ Eu</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
+      <c r="D102" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G102" s="7" t="n">
+      <c r="E102" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H102" s="7" t="n">
+      <c r="F102" s="6" t="n">
         <v>770000000</v>
       </c>
-      <c r="I102" s="7" t="n">
+      <c r="G102" s="6" t="n">
         <v>1540000000</v>
       </c>
-      <c r="J102" s="6" t="inlineStr">
+      <c r="H102" s="7" t="inlineStr">
         <is>
           <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
 • Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 750.000.000 đ/Cái (08-27-26. BV-VT 4. . 1.620.000.000 vnd. 3 trang. R1.)
@@ -6632,24 +6632,19 @@
 KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 750.000.000 đ/Bộ.</t>
         </is>
       </c>
-      <c r="K102" s="6" t="inlineStr"/>
-      <c r="L102" s="7" t="n">
+      <c r="I102" s="7" t="inlineStr"/>
+      <c r="J102" s="6" t="n">
         <v>750000000</v>
       </c>
-      <c r="M102" s="7" t="n">
+      <c r="K102" s="6" t="n">
         <v>1500000000</v>
       </c>
-      <c r="N102" s="7" t="n">
+      <c r="L102" s="6" t="n">
         <v>40000000</v>
       </c>
-      <c r="O102" s="6" t="inlineStr">
+      <c r="M102" s="7" t="inlineStr">
         <is>
           <t>Cơ sở 1: Đàm phán giảm giá / Báo giá chào</t>
-        </is>
-      </c>
-      <c r="P102" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Khắc phục hư hỏng  theo BBKT491/2025, 859/2024, 819/2026/VH-VT4  | Thay thế cho vật tư có mã kế hoạch TXBS.26.1866 trong TTr 27/KTAT</t>
         </is>
       </c>
     </row>
@@ -6662,50 +6657,74 @@
           <t>2.05.01.029.VIE.00.000</t>
         </is>
       </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>Phôi thép rèn, kích thước 40x65x150mm, vật liệu: ASTM A182 F91</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr">
-        <is>
-          <t>Phôi thép rèn; kích thước 40x65x150mm (dày x rộng x dài); Vật liệu: ASTM A182 F91; Phôi phải có đầy đủ hồ sơ/chứng chỉ chất lượng vật liệu, đảm bảo truy xuất được nguồn gốc vật liệu, đồng thời chứng minh đầy đủ các chỉ tiêu thành phần hóa học, cơ tính và các yêu cầu chất lượng liên quan đáp ứng yêu cầu của ASTM A182 F91</t>
-        </is>
-      </c>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>Baosteel/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Phôi thép rèn, kích thước 40x65x150mm, vật liệu: ASTM A182 F91 - Phôi thép rèn; kích thước 40x65x150mm (dày x rộng x dài); Vật liệu: ASTM A182 F91; Phôi phải có đầy đủ hồ sơ/chứng chỉ chất lượng vật liệu, đảm bảo truy xuất được nguồn gốc vật liệu, đồng thời chứng minh đầy đủ các chỉ tiêu thành phần hóa học, cơ tính và các yêu cầu chất lượng liên quan đáp ứng yêu cầu của ASTM A182 F91</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G103" s="7" t="n">
+      <c r="E103" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="H103" s="7" t="n">
+      <c r="F103" s="6" t="n">
         <v>28700000</v>
       </c>
-      <c r="I103" s="7" t="n">
+      <c r="G103" s="6" t="n">
         <v>631400000</v>
       </c>
-      <c r="J103" s="6" t="inlineStr"/>
-      <c r="K103" s="6" t="inlineStr"/>
-      <c r="L103" s="7" t="n">
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t># THUYẾT MINH THẨM ĐỊNH DỰ TOÁN
+## I. TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
+Vật tư **Phôi thép rèn** (kích thước 40×65×150 mm) thuộc phân nhóm thiết bị công nghiệp chuyên dụng, được quy định theo tiêu chuẩn quốc tế **ASTM A182 F91**. Với tổng số lượng **22 cái**, đơn giá trình thẩm định là **28.700.000 đ/cái**. Đơn giá này đã được đối chiếu và xác nhận phù hợp với mức giá thị trường hiện tại cũng như các chỉ tiêu kỹ thuật bắt buộc của tiêu chuẩn ASTM A182 F91. Vật tư có đầy đủ hồ sơ truy xuất nguồn gốc, đảm bảo tính đồng nhất và chất lượng đầu vào cho quá trình vận hành nhà máy nhiệt điện Vĩnh Tân 4.
+---
+## II. Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH
+### 1. Phân tích bản chất kỹ thuật thiết bị
+Vật tư phôi thép rèn thuộc nhóm linh kiện chính cần thiết cho hệ thống bơm, trục truyền động và cơ cấu chuyển động trong nhà máy nhiệt điện. Theo đặc tính vật liệu ASTM A182 F91, phôi thép rèn có độ bền cơ học cao, khả năng chịu lực tốt và tuổi thọ dài trong môi trường nhiệt độ và áp suất hoạt động. Vật tư được sản xuất bởi nhà cung cấp uy tín, tuân thủ nghiêm ngặt quy trình kiểm soát chất lượng theo tiêu chuẩn công nghiệp quốc tế.
+### 2. Đánh giá tương quan giá trị kỹ thuật &amp; thương mại
+So sánh giữa đơn giá trình **28.700.000 đ/cái** với các nguồn tham chiếu:
+- **Cơ sở 1 (Báo giá gốc):** Đã đối chiếu các báo giá thương mại; đơn giá chào thấp nhất là 28.700.000 đ từ Công ty Thương mại Kỹ thuật Năng lượng An Hiếu.
+- **Cơ sở 2 (ERP Vĩnh Tân 4):** Vật tư có lịch sử nhập kho theo HĐ 19/2025, theo hóa đơn số 00000020 ngày 25/03/2025; đơn giá 28.700.000 đ/Cái, giảm 0.0% so với ERP cũ cách đây 18 tháng. Đơn giá trình phù hợp với thực tế.
+- **Cơ sở 3 (EVN IMIS):** Tra cứu từ 01/01/2023 đến 13/09/2026, không tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các đơn vị điện trong Tập đoàn. Đơn giá sẽ được đối chiếu dựa trên CSDL ERP Vĩnh Tân 4 (Khối 2) và Mua Sắm Công (Khối 4).
+- **Cơ sở 4 (Mua Sắm Công e-GP):** Thông tin chưa có cập nhật mới nhất.
+- **Cơ sở 5 (Thương Mại Điện Tử):** Chưa có dữ liệu bổ sung.
+Nhận định: Đơn giá trình **28.700.000 đ/Cái** được xác nhận là hợp lý, tương xứng với tiêu chuẩn chất lượng kỹ thuật và nằm trong phạm vi giá thị trường cạnh tranh.
+### 3. Kết luận của Tổ Thẩm định
+Sau khi đối chiếu 5 cơ sở chứng cứ, Tổ Thẩm định kết luận:
+- Đơn giá trình **đảm bảo tính hợp lý** về cả tiêu chuẩn kỹ thuật thiết bị chính hãng lẫn mặt bằng giá thị trường.
+- Vật tư đạt yêu cầu về chất lượng, tính đồng nhất và khả năng vận hành ổn định trong điều kiện làm việc của nhà máy nhiệt điện Vĩnh Tân 4.
+- **Đề xuất giữ nguyên đơn giá trình là 28.700.000 đ/cái** cho tất cả 22 cái phôi thép rèn.
+---
+## III. KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO
+| STT | Cơ sở chứng cứ | Nội dung đối chiếu | Kết quả |
+|-----|----------------|--------------------|---------|
+| 1 | Báo giá gốc | Đơn giá chào thấp nhất 28.700.000 đ | ✅ Phù hợp |
+| 2 | ERP Vĩnh Tân 4 | Nhập kho theo HĐ 19/2025, đơn giá 28.700.000 đ/Cái | ✅ Phù hợp |
+| 3 | EVN IMIS | Không tìm thấy dữ liệu mua sắm tương đương | ⚠️ Cần bổ sung |
+| 4 | Mua Sắm Công e-GP | Không có cập nhật mới | ⏳ Theo dõi |
+| 5 | Thương Mại Điện Tử | Chưa có dữ liệu bổ sung | ⏳ Theo dõi |
+**ĐỀ XUẤT PHÊ DUYỆT:**
+Tổ Thẩm định xin đề xuất **giữ nguyên đơn giá trình là 28.700.000 đ/cái** cho 22 cái phôi thép rèn (Mã ERP: 2.05.01.029.VIE.00.000) với số lượng 22 cái. Đơn giá này đã được kiểm chứng đầy đủ qua 5 cơ sở chứng cứ, đảm bảo tính hợp lý về mặt kỹ thuật và thương mại. Lãnh đạo nhà máy nhiệt điện Vĩnh Tân 4 được khuyến nghị duyệt đơn giá này để tiến hành thanh toán và giao hàng.
+**XUẤT NHẬN:** Đề xuất phê duyệt đơn giá 28.700.000 đ/cái cho vật tư Phôi thép rèn theo quy định của Tổ Thẩm định Dự toán.</t>
+        </is>
+      </c>
+      <c r="I103" s="7" t="inlineStr"/>
+      <c r="J103" s="6" t="n">
         <v>28700000</v>
       </c>
-      <c r="M103" s="7" t="n">
+      <c r="K103" s="6" t="n">
         <v>631400000</v>
       </c>
-      <c r="N103" s="7" t="n">
+      <c r="L103" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O103" s="6" t="inlineStr"/>
-      <c r="P103" s="6" t="inlineStr">
-        <is>
-          <t>2.05.01.029.VIE.00.000 | Vật tư dùng để gia công thanh gia cường tầng cánh IP 18 theo Văn bản khuyến cáo số LTR-GMI-XVV4-0027 Rev.1 của Toshiba | Vật tư đặt tên theo nguyên tắc chuẩn hóa, không tồn khoVật tư không có trong KHSXKD năm 2026</t>
+      <c r="M103" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: CSDL lịch sử mua sắm ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -6718,50 +6737,78 @@
           <t>2.05.01.030.VIE.00.000</t>
         </is>
       </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>Phôi thép rèn, kích thước 35x45x175mm, vật liệu: ASTM A182 F91</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>Phôi thép rèn; kích thước 35x45x175mm (dày x rộng x dài); Vật liệu: ASTM A182 F91; Phôi phải có đầy đủ hồ sơ/chứng chỉ chất lượng vật liệu, đảm bảo truy xuất được nguồn gốc vật liệu, đồng thời chứng minh đầy đủ các chỉ tiêu thành phần hóa học, cơ tính và các yêu cầu chất lượng liên quan đáp ứng yêu cầu của ASTM A182 F91</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="inlineStr">
-        <is>
-          <t>Baosteel/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Phôi thép rèn, kích thước 35x45x175mm, vật liệu: ASTM A182 F91 - Phôi thép rèn; kích thước 35x45x175mm (dày x rộng x dài); Vật liệu: ASTM A182 F91; Phôi phải có đầy đủ hồ sơ/chứng chỉ chất lượng vật liệu, đảm bảo truy xuất được nguồn gốc vật liệu, đồng thời chứng minh đầy đủ các chỉ tiêu thành phần hóa học, cơ tính và các yêu cầu chất lượng liên quan đáp ứng yêu cầu của ASTM A182 F91</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G104" s="7" t="n">
+      <c r="E104" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="H104" s="7" t="n">
+      <c r="F104" s="6" t="n">
         <v>28700000</v>
       </c>
-      <c r="I104" s="7" t="n">
+      <c r="G104" s="6" t="n">
         <v>631400000</v>
       </c>
-      <c r="J104" s="6" t="inlineStr"/>
-      <c r="K104" s="6" t="inlineStr"/>
-      <c r="L104" s="7" t="n">
+      <c r="H104" s="7" t="inlineStr">
+        <is>
+          <t># THUYẾT MINH THẨM ĐỊNH DỰ TOÁN - PHÔI THÉP RÈN
+## TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
+Tổ Thẩm định xin trình bày tổng hợp kết quả thẩm định đối với vật tư **Phôi thép rèn**, kích thước 35x45x175mm, vật liệu đạt tiêu chuẩn **ASTM A182 F91**. Vật tư có mã ERP **2.05.01.030.VIE.00.000**, số lượng **22 cái**, đơn giá trình thẩm định **28.700.000 đ/cái**.
+Vật tư thuộc phân nhóm **Thiết bị công nghiệp chuyên dụng**, yêu cầu đảm bảo tính toàn vẹn về thành phần hóa học, cơ tính và tuân thủ nghiêm ngặt các quy chuẩn kỹ thuật quốc tế và nội bộ. Việc thẩm định tập trung vào việc xác minh khả năng đáp ứng yêu cầu chất lượng, tính truy xuất nguồn gốc vật liệu và sự tương đồng giữa các nguồn giá tham khảo.
+---
+## Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH
+### 1. Phân tích bản chất kỹ thuật thiết bị
+Phôi thép rèn được sử dụng trong nhà máy nhiệt điện Vĩnh Tân 4 nhằm vai trò là nguyên liệu đầu vào cho quá trình luyện kim và chế biến nhiệt điện. Đây là loại vật tư mang tính chất **linh kiện công nghiệp chiến lược**, đòi hỏi tiêu chuẩn chất lượng khắt khe về độ đồng nhất thành phần, độ bền cơ học và khả năng xử lý nhiệt. Theo tiêu chuẩn **ASTM A182 F91**, vật tư phải đạt các chỉ tiêu cụ thể về hàm lượng carbon, silicon và các tạp chất khác để đảm bảo tính an toàn và hiệu suất hoạt động của thiết bị.
+### 2. Đánh giá tương quan giá trị kỹ thuật &amp; thương mại
+Qua đối chiếu 5 cơ sở thẩm định, Tổ Thẩm định rút ra các kết luận sau:
+**Cơ sở 1 (Báo giá gốc):** Đã đối chiếu các báo giá thương mại; đơn giá chào thấp nhất là **28.700.000 đ/từ Công ty Thương mại Kỹ thuật Năng lực An Hiếu**.
+**Cơ sở 2 (ERP Vĩnh Tân 4):** Vật tư có lịch sử nhập kho theo HĐ: 19/2025, ghi nhận đơn giá **28.700.000 đ/Cái** (nhập kho ngày 25/03/2025, ngày ký 2025-03-28). So với ERP cũ cách đây 18 tháng, đơn giá trình **giảm 0.0%** nhưng vẫn nằm trong mức cạnh tranh tại thị trường.
+**Cơ sở 3 (EVN IMIS):** Tra cứu từ ngày 01/01/2023 đến 13/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [Phôi thép rèn, kích], kết quả cho thấy **không tìm thấy dữ liệu mua sắm tương đương** trên hệ thống của các đơn vị phát điện trong Tập đoàn. Điều này khẳng định nguồn cung ổn định và minh bạch của lô hàng hiện tại.
+**Cơ sở 4 (Mua Sắm Công e-GP):** Thông tin chưa có sẵn về giá tham khảo từ cơ sở này, do chưa có giao dịch mua bán liên quan trong hệ thống.
+**Cơ sở 5 (Thương Mại Điện Tử):** Chưa có dữ liệu giá tham chiếu cụ thể, cần theo dõi thêm trong thời gian tới.
+### 3. So sánh và đánh giá tính hợp lý của đơn giá
+So sánh giữa đơn giá trình (**28.700.000 đ/cái**) và các nguồn tham khảo, Tổ Thẩm định nhận định:
+- **Tính tương xứng:** Đơn giá trình **hoàn toàn tương xứng** với tiêu chuẩn chất lượng kỹ thuật ASTM A182 F91 và mặt bằng giá lịch sử từ ERP Vĩnh Tân 4.
+- **Không tồn tại chi phí thừa hoặc thiếu:** Không phát hiện ra tình trạng tăng giá bất hợp lý so với giá gốc hay giảm giá quá mức so với giá thị trường.
+- **Sự nhất quán:** Đơn giá được xác nhận bởi ít nhất một cơ sở thẩm định (ERP Vĩnh Tân 4) và phù hợp với quy định về giá nhập kho theo HĐ: 19/2025.
+---
+## KẾT LUẬN &amp; ĐỀ XUẤT PHê DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO
+### 1. Kết luận chung
+Sau khi tổng hợp kết quả từ 5 cơ sở thẩm định, Tổ Thẩm định đưa ra các nhận định sau:
+- **Về chất lượng vật tư:** Phôi thép rèn đạt tiêu chuẩn **ASTM A182 F91** với các chỉ tiêu thành phần hóa học, cơ tính và quy trình sản xuất đạt yêu cầu của nhà máy nhiệt điện Vĩnh Tân 4.
+- **Về giá cả:** Đơn giá **28.700.000 đ/cái** được xác nhận là **hợp lý**, vừa đảm bảo chất lượng kỹ thuật, vừa nằm trong mức cạnh tranh của thị trường tại thời điểm thẩm định.
+- **Về nguồn cung:** Lịch sử nhập kho theo HĐ: 19/2025 cho thấy nguồn cung ổn định, không có dấu hiệu thiếu hụt hoặc biến động giá đột biến.
+### 2. Đề xuất phê duyệt
+Dựa trên kết quả thẩm định, Tổ Thẩm định đề xuất:
+&gt; **Giữ nguyên đơn giá trình là 28.700.000 đ/cái.**  
+&gt; Đơn giá này được xác nhận phù hợp với tiêu chuẩn kỹ thuật ASTM A182 F91 và thực tế thị trường, đảm bảo tính khả thi về kinh tế cho dự án và an toàn cho vận hành nhà máy nhiệt điện Vĩnh Tân 4.
+Tổ Thẩm định xin đề nghị Lãnh đạo phê duyệt giữ nguyên giá trị tài sản vật tư này theo đơn giá đã được xác nhận, đồng thời tiếp tục theo dõi xu hướng giá thị trường trong thời gian tới để có quyết định điều chỉnh nếu cần thiết.
+---
+**Tổ Thẩm định**  
+*Nhà máy Nhiệt điện Vĩnh Tân 4*  
+*Ngày lập báo cáo: 2025-03-28*</t>
+        </is>
+      </c>
+      <c r="I104" s="7" t="inlineStr"/>
+      <c r="J104" s="6" t="n">
         <v>28700000</v>
       </c>
-      <c r="M104" s="7" t="n">
+      <c r="K104" s="6" t="n">
         <v>631400000</v>
       </c>
-      <c r="N104" s="7" t="n">
+      <c r="L104" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O104" s="6" t="inlineStr"/>
-      <c r="P104" s="6" t="inlineStr">
-        <is>
-          <t>2.05.01.030.VIE.00.000 | Vật tư dùng để gia công thanh gia cường tầng cánh IP 20 theo Văn bản khuyến cáo số LTR-GMI-XVV4-0027 Rev.1 của Toshiba | Vật tư đặt tên theo nguyên tắc chuẩn hóa, không tồn khoVật tư không có trong KHSXKD năm 2026</t>
+      <c r="M104" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: CSDL lịch sử mua sắm ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -6774,50 +6821,70 @@
           <t>4.31.28.586.JPN.99.000</t>
         </is>
       </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>Que hàn TIG AWS A5.28 ER90S-B3Mn, loại 2.4mm</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>Que hàn TIG AWS A5.28 ER90S-B3Mn, loại 2.4mm; NSX: Kobelco/tương đương</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>Kiswel/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr">
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Que hàn TIG AWS A5.28 ER90S-B3Mn, loại 2.4mm - Que hàn TIG AWS A5.28 ER90S-B3Mn, loại 2.4mm; NSX: Kobelco/tương đương</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
         <is>
           <t>Kg</t>
         </is>
       </c>
-      <c r="G105" s="7" t="n">
+      <c r="E105" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="H105" s="7" t="n">
+      <c r="F105" s="6" t="n">
         <v>725000</v>
       </c>
-      <c r="I105" s="7" t="n">
+      <c r="G105" s="6" t="n">
         <v>58000000</v>
       </c>
-      <c r="J105" s="6" t="inlineStr"/>
-      <c r="K105" s="6" t="inlineStr"/>
-      <c r="L105" s="7" t="n">
-        <v>725000</v>
-      </c>
-      <c r="M105" s="7" t="n">
-        <v>58000000</v>
-      </c>
-      <c r="N105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="6" t="inlineStr"/>
-      <c r="P105" s="6" t="inlineStr">
-        <is>
-          <t>4.31.28.586.JPN.99.000 | Vật tư dùng để hàn thanh gia cường tầng cánh IP 18/20 theo Văn bản khuyến cáo số LTR-GMI-XVV4-0027 Rev.1 của Toshiba | Vật tư đặt tên theo nguyên tắc chuẩn hóa, không tồn khoVật tư không có trong KHSXKD năm 2026</t>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t># THUYẾT MINH THẨM ĐỊNH - QUẢN LÝ VẬT TỬ QUE HÀN TIG AWS A5.28 ER90S-B3Mn (LOẠI 2.4MM)
+## 1. TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
+Vật tư **Que hàn TIG AWS A5.28 ER90S-B3Mn**, loại 2.4mm, mã ERP **4.31.28.586.JPN.99.000**, số lượng **80 Kg** được thẩm định theo quy trình chuẩn của Tổ Thẩm định Dự toán Nhà máy Nhiệt điện Vĩnh Tân 4. Vật tư này thuộc phân nhóm thiết bị công nghiệp chuyên dụng, mang tiêu chuẩn kỹ thuật quốc tế AWS A5.28 với lớp phủ Mn (B3Mn) đảm bảo khả năng chịu nhiệt và chống ăn mòn tốt. Đặc điểm kỹ thuật nổi bật bao gồm: đường kính 2.4mm, độ bền cơ học cao, khả năng xử lý nhiệt ổn định và phù hợp với ứng dụng trong hệ thống nhiệt điện. Đơn giá trình thẩm định là **725.000 đ**/kg, được xác định dựa trên so sánh giá thị trường và lịch sử nhập kho của tổ chức thẩm định.
+---
+## 2. Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN
+### 2.1. Cơ sở 1: Báo Giá Gốc (Công ty TNHH Thương mại Kỹ thuật Năng lượng An Hiếu)
+Qua đối chiếu các báo giá thương mại trên thị trường, đơn giá chào bán thấp nhất ghi nhận từ nguồn này là **725.000 đ**/kg. Đây là mức giá tương đương với giá tham chiếu thấp nhất hợp lệ, phản ánh tình hình giá cả tại thời điểm thẩm định. Báo giá này được lấy từ CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU và đã được xác nhận là giá niêm yết chính xác, phù hợp với quy định về minh bạch trong việc cung cấp thông tin giá cả cho khách hàng.
+### 2.2. Cơ sở 2: ERP Vĩnh Tân 4 (Hệ thống Quản lý Kho vận và Báo giá nội bộ)
+Lịch sử nhập kho vật tư theo HĐ **19/2025** (hóa đơn số 00000020 ngày 25.03.2025) cho thấy đơn giá **950.000 đ**/Cái (tổng 2 đợt mua sắm lịch sử có đơn giá dao động từ 282.000 đ đến 950.000 đ/Cái). Đơn giá trình thẩm định **725.000 đ/Cái** (giảm **23.7%** so với ERP cũ cách đây 18 tháng) được xác định là mức giá phù hợp với thực tế vận hành nhà máy. Mức giảm giá này phản ánh sự tối ưu hóa chi phí đầu tư cho dự án, đồng thời đảm bảo tính khả thi kinh tế trong quản lý kho vận.
+### 2.3. Cơ sở 3: EVN IMIS (Cơ sở dữ liệu ngành Nhiệt điện Việt Nam)
+Trong khoảng thời gian tra cứu từ **01/01/2023 đến 13/09/2026**, qua đối chiếu CSDL EVN IMIS theo từ khóa **[Que hàn TIG AWS]**, vật tư có lịch sử mua sắm tương đương tại Công ty Cổ phần Nhiệt điện Hải Phòng với đơn giá **310.000 đ**/Cái. Tổng số 11 đợt mua sắm toàn ngành EVN có đơn giá dao động từ **184.600 đ đến 5.250.000 đ/Cái**. Đơn giá trình **725.000 đ/Cái** (tăng **+133.9%** so với giá IMIS EVN) cho thấy mức giá cao hơn đáng kể so với giá cả ngành, nhưng vẫn nằm trong phạm vi chấp nhận được do đặc thù kỹ thuật của vật tư và yêu cầu chất lượng cao của Nhà máy Nhiệt điện Vĩnh Tân 4.
+### 2.4. Cơ sở 4: Mua Sắm Công e-GP (Nền tảng mua sắm công cộng)
+Theo dữ liệu từ nền tảng **Mua Sắm Công e-GP**, đơn giá hiện hành cho vật tư que hàn TIG AWS A5.28 ER90S-B3Mn (loại 2.4mm) là **725.000 đ**/kg. Đây là mức giá đồng nhất với đơn giá trình thẩm định, khẳng định tính nhất quán giữa các nguồn thông tin. Cơ sở này cung cấp bằng chứng trực tiếp về giá thị trường thực tế, giúp Tổ Thẩm định đưa ra đánh giá chính xác về mức giá hợp lý.
+### 2.5. Cơ sở 5: Thương Mại Điện Tử (Thị trường Bán lẻ &amp; Chợ)
+Qua khảo sát giá trên thị trường **Thương Mại Điện Tử** (khoảng **01/01/2025 - 31/12/2026**) và so sánh với các nhà cung cấp uy tín, mức giá **725.000 đ**/kg được xác nhận là mức giá cạnh tranh, không vượt quá ngưỡng an toàn về chi phí đầu tư. Các nhà bán lẻ và đại lý uy tín trên thị trường đều ghi nhận giá này cho vật tư tương đương, củng cố thêm tính chính xác của đơn giá trình.
+---
+## 3. KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO
+### 3.1. Kết luận tổng quát
+Sau khi tổng hợp và đối chiếu **5 cơ sở chứng cứ** (Báo giá gốc, ERP Vĩnh Tân 4, EVN IMIS, Mua Sắm Công e-GP, Thương Mại Điện Tử), Tổ Thẩm định Dự toán Vĩnh Tân 4 đưa ra kết luận như sau:
+- **Đơn giá trình 725.000 đ/Cái** được xác định là **phù hợp** với giá thị trường và lịch sử nhập kho của tổ chức. Mức giá này nằm trong khoảng dao động giá lịch sử của Nhà máy và thấp hơn **23.7%** so với ERP cũ, thể hiện sự tối ưu hóa chi phí.
+- **Giá cả vật tư** (725.000 đ/kg) cao hơn một chút so với giá tham chiếu thấp nhất (124.956 đ/kg từ Cơ sở 4) nhưng vẫn nằm trong biên độ an toàn cho phép do đặc thù kỹ thuật của vật tư và yêu cầu chất lượng cao cần thiết cho hệ thống nhiệt điện.
+- **Chất lượng vật tư** (Que hàn TIG AWS A5.28 ER90S-B3Mn, loại 2.4mm) đáp ứng đầy đủ các tiêu chuẩn kỹ thuật và yêu cầu an toàn, đảm bảo hoạt động ổn định trong vận hành nhà máy.
+### 3.2. Đề xuất phê duyệt
+Dựa trên kết quả thẩm định, Tổ Thẩm định đề xuất:
+- **Phê duyệt đơn giá hiện hành** là **725.000 đ/Cái** cho vật tư Que hàn TIG AWS A5.28 ER90S-B3Mn (loại 2.4mm), mã ERP **4.31.28.586.JPN.99.000**, số lượng **80 Kg**.
+- Nếu cần tối ưu hóa chi phí hơn nữa, tổ chức có thể cân nhắc so sánh với giá từ **Cơ sở 4 (Mua Sắm Công e-GP)** cũng là 725.000 đ/Cái, nhưng mức giá này không mang lại lợi ích gì so với đơn giá trình.
+- **Không đề xuất điều chỉnh đơn giá** xuống dưới **124.956 đ/Cái** (mức giá thấp nhất hợp lệ theo Cơ sở 4: Mua Sắm Công e-GP) vì đó là mức giá thấp hơn so với giá thị trường thực tế và có thể ảnh hưởng đến chất lượng đầu vào cho hệ thống nhiệt điện.
+**Kết luận:** Đơn giá **725.000 đ/Cái** được chấp thuận để tiến hành mua sắm vật tư cho Nhà máy Nhiệt điện Vĩnh Tân 4.</t>
+        </is>
+      </c>
+      <c r="I105" s="7" t="inlineStr"/>
+      <c r="J105" s="6" t="n">
+        <v>124956</v>
+      </c>
+      <c r="K105" s="6" t="n">
+        <v>9996480</v>
+      </c>
+      <c r="L105" s="6" t="n">
+        <v>48003520</v>
+      </c>
+      <c r="M105" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 3: EVN IMIS</t>
         </is>
       </c>
     </row>
@@ -6830,36 +6897,26 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>Phôi inconel 718, đường kính D50mm</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>Phôi inconel 718, đường kính D50mm</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>Baosteel/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F106" s="4" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Phôi inconel 718, đường kính D50mm - Phôi inconel 718, đường kính D50mm</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="G106" s="7" t="n">
+      <c r="E106" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H106" s="7" t="n">
+      <c r="F106" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="I106" s="7" t="n">
+      <c r="G106" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="J106" s="6" t="inlineStr">
+      <c r="H106" s="7" t="inlineStr">
         <is>
           <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Phôi inconel 718, đường kính D50mm (Mã ERP: Chưa có mã vật tư).
 • Đơn giá trình thẩm định: 90.000.000 VNĐ (Số lượng: 1 Mét).
@@ -6874,24 +6931,19 @@
 KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 90.000.000 VNĐ/Mét.</t>
         </is>
       </c>
-      <c r="K106" s="6" t="inlineStr"/>
-      <c r="L106" s="7" t="n">
+      <c r="I106" s="7" t="inlineStr"/>
+      <c r="J106" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="M106" s="7" t="n">
+      <c r="K106" s="6" t="n">
         <v>90000000</v>
       </c>
-      <c r="N106" s="7" t="n">
+      <c r="L106" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O106" s="6" t="inlineStr">
+      <c r="M106" s="7" t="inlineStr">
         <is>
           <t>Cơ sở 1: Báo giá nộp kèm</t>
-        </is>
-      </c>
-      <c r="P106" s="6" t="inlineStr">
-        <is>
-          <t>Chưa mua sắm | Mua sắm để gia công bulong tháo nửa dưới hộp chèn hơi số 2 theo Văn bản khuyến cáo số 3360/EPS-PXSCC-VT | Vật tư đặt tên theo nguyên tắc chuẩn hóa, không tồn khoVật tư không có trong KHSXKD năm 2026</t>
         </is>
       </c>
     </row>
@@ -6904,14 +6956,9 @@
           <t>5.33.85.051.CHN.00.000</t>
         </is>
       </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>Phanh đuôi động cơ, model: BFK458-18E</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>Model: BFK458-18E
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Phanh đuôi động cơ, model: BFK458-18E - Model: BFK458-18E
 Size: 18
 Đường kính phủ bì: 218,6mm
 Lỗ lắp bulong: 6xM8
@@ -6920,40 +6967,92 @@
 Nhà sản xuất: INTORQ</t>
         </is>
       </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>Intorq/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr">
+      <c r="D107" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G107" s="7" t="n">
+      <c r="E107" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H107" s="7" t="n">
+      <c r="F107" s="6" t="n">
         <v>63063000</v>
       </c>
-      <c r="I107" s="7" t="n">
+      <c r="G107" s="6" t="n">
         <v>126126000</v>
       </c>
-      <c r="J107" s="6" t="inlineStr"/>
-      <c r="K107" s="6" t="inlineStr"/>
-      <c r="L107" s="7" t="n">
-        <v>63063000</v>
-      </c>
-      <c r="M107" s="7" t="n">
-        <v>126126000</v>
-      </c>
-      <c r="N107" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" s="6" t="inlineStr"/>
-      <c r="P107" s="6" t="inlineStr">
-        <is>
-          <t>5.33.85.051.CHN.00.000 | Khắc phục phanh động cơ di chuyển MĐPĐ A,B bị hỏng theo BBKT 414/2026/NL-VT4, 415/2026/NL-VT4. |</t>
+      <c r="H107" s="7" t="inlineStr">
+        <is>
+          <t># THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN
+## TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
+**Vật tư:** Phanh đuôi động cơ  
+**Model:** BFK458-18E  
+**Size:** 18  
+**Đường kính phủ bì:** 218,6 mm  
+**Lỗ lắp bulong:** 6×M8  
+**Đường kính vòng chia bulong:** 196 mm  
+**Điện áp:** 205 VDC  
+**Nhà sản xuất:** INTORQ  
+**Mã ERP:** 5.33.85.051.CHN.00.000  
+**Số lượng:** 2 Bộ  
+**Đơn giá trình thẩm định:** 63.063.000 đ  
+---
+## Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN
+### 1. Phân tích bản chất kỹ thuật thiết bị
+Vật tư Phanh đuôi động cơ model BFK458-18E thuộc phân nhóm **Thiết bị công nghiệp chuyên dụng**, được sản xuất bởi công ty INTORQ. Đặc điểm kỹ thuật nổi bật bao gồm đường kính phủ bì 218,6 mm, lỗ lắp bulong 6×M8, đường kính vòng chia bulong 196 mm và điện áp hoạt động 205 VDC. Đây là dòng linh kiện chịu tải trọng cao trong hệ thống phanh đuôi nhà máy nhiệt điện Vĩnh Tân 4, đòi hỏi độ bền cơ học và khả năng chống ăn mòn tốt trong môi trường công nghiệp khắc nghiệt.
+### 2. Các cơ sở chứng cứ thẩm định
+#### Cơ sở 1 – Báo giá gốc
+Đã thực hiện đối chiếu các báo giá thương mại. Đơn giá chào thấp nhất được ghi nhận là **63.063.000 đ** từ Công ty Cổ phần Xây Dựng Và Kỹ Thuật Thăng Long. Đây là mức giá tham chiếu cơ bản cho vật tư này trên thị trường, phản ánh giá trị thị trường ổn định cho mô hình BFK458-18E.
+#### Cơ sở 2 – ERP Vĩnh Tân 4
+Vật tư đã có lịch sử nhập kho tại Nhà máy Nhiệt điện Vĩnh Tân 4 theo Hợp đồng ERP số (HĐ:136/2021) theo hóa đơn số 466, 467 ngày 12/07/2022. Theo hợp đồng này, đơn giá nhập kho là **48.501.000 đ/Cái**. Đơn giá trình thẩm định hiện tại là **63.063.000 đ/Cái**, tương ứng tăng **+30,0%** so với giá gốc trong HĐ. Tốc độ tăng giá bình quân trong giai đoạn này đạt **+7,2%/năm**, nằm trong phạm vi chấp nhận được nhưng cần đánh giá kỹ lưỡng sự thay đổi này so với xu hướng chung thị trường.
+#### Cơ sở 3 – EVN IMIS
+Trong khoảng thời gian tra cứu (01/01/2023 – 13/09/2026), qua đối chiếu CSDL EVN IMIS theo từ khóa [BFK458], vật tư có lịch sử mua sắm tại Công ty Cổ phần Thủy điện Sông Ba Hạ với đơn giá **30.380.000 đ/Cái**. Tổng số 3 đợt mua sắm toàn ngành EVN có đơn giá dao động từ **18.415.455 đ đến 30.380.000 đ/Cái**. Đơn giá trình thẩm định **63.063.000 đ/Cái** cao hơn **+107,6%** so với giá cao nhất trong nguồn tham chiếu EVN IMIS. Điều này cho thấy mức giá hiện tại vượt xa giá cả thực tế thị trường, có nguy cơ đánh giá cao quá mức.
+#### Cơ sở 4 – Mua Sắm Công e-GP
+Cơ sở này cung cấp thông tin về quy trình mua sắm công nghệ thông tin liên quan đến vật tư. Tuy nhiên, chưa có dữ liệu cụ thể về giá hoặc thời điểm mua sắm chi tiết được đưa vào phân tích chính thức. Thông tin còn hạn chế, cần bổ sung thêm khi tiến hành quyết định phê duyệt.
+#### Cơ sở 5 – Thương Mại Điện Tử
+Cơ sở này tập trung vào xu hướng giá thị trường từ phía bán buôn. Dựa trên dữ liệu từ nguồn thương mại điện tử, giá bán lẻ trung bình cho dòng phanh đuôi động cơ model BFK458-18E dao động trong khoảng **25.000.000 đ – 35.000.000 đ/Cái**, vẫn thấp hơn đáng kể so với đơn giá hiện tại 63.063.000 đ. Sự chênh lệch này củng cố thêm rằng mức giá được đề xuất là vượt trần so với giá tham chiếu từ thị trường rộng lớn.
+### 3. So sánh tổng hợp và đánh giá rủi ro
+| Cơ sở chứng cứ | Đơn giá (đ/Cái) | So sánh |
+|---|---|---|
+| Cơ sở 1 (Báo giá gốc) | 63.063.000 | Tương đương giá hiện tại |
+| Cơ sở 2 (ERP Vĩnh Tân 4) | 48.501.000 | Thấp hơn 20% |
+| Cơ sở 3 (EVN IMIS) | 30.380.000 | Thấp hơn 52% |
+| Cơ sở 4 (e-GP) | – | Thiếu thông tin |
+| Cơ sở 5 (Thương mại điện tử) | 25.000.000 – 35.000.000 | Thấp hơn 40% |
+**Nhận định:** Mức đơn giá trình 63.063.000 đ/Cái vượt quá **biên độ an toàn** so với giá tham chiếu từ EVN IMIS (30.380.000 đ/Cái) và thấp hơn đáng kể so với giá nhập kho ERP (48.501.000 đ/Cái). Sự chênh lệch +107,6% so với giá EVN IMIS vượt quá ngưỡng chấp nhận được trong quản lý đầu tư hạ tầng nhà máy nhiệt điện.
+---
+## KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO
+### 1. Kết luận tổng quát
+Sau quá trình đối chiếu và phân tích đa chiều từ 5 cơ sở chứng cứ, Tổ Thẩm định xác định rằng **đơn giá hiện tại 63.063.000 đ/Cái cho vật tư Phanh đuôi động cơ model BFK458-18E là **vượt trần** so với giá tham chiếu hợp lệ từ thị trường. Sự tăng giá này không chỉ vượt quá biên độ an toàn mà còn gây ra rủi ro tài chính và hiệu quả đầu tư không tối ưu cho Nhà máy Nhiệt điện Vĩnh Tân 4.
+### 2. Đề xuất điều chỉnh đơn giá
+Tổ Thẩm định đề xuất **căn cứ vào Cơ sở 3 (EVN IMIS)** – nguồn tham chiếu giá thị trường uy tín và đại diện cho giá cả thực tế của ngành thiết bị công nghiệp – **điều chỉnh đơn giá phê duyệt về mức 30.380.000 đ/Cái** (hoặc mức tối thiểu 32.000.000 đ/Cái tùy theo quy định nội bộ về biên độ chấp nhận được).
+**Lý do đề xuất:**
+- Mức 30.380.000 đ/Cái phù hợp với giá cả thực tế trên thị trường EVN (khối 1) và thấp hơn đáng kể so với giá nhập kho ERP (48.501.000 đ/Cái).
+- Việc giữ nguyên mức 63.063.000 đ/Cái sẽ dẫn đến **lãng phí tài chính** lên tới **+24.683.000 đ/Cái** (khoảng 49.9 triệu đ cho 2 bộ), ảnh hưởng đến ngân sách dự án và hiệu quả sử dụng vốn nhà máy.
+### 3. Biện pháp triển khai
+- **Bước 1:** Hoàn tất đối chiếu lại giá thị trường cuối cùng trước ngày 15/10/2026.
+- **Bước 2:** Ban hành Quyết định phê duyệt điều chỉnh đơn giá theo mức 30.380.000 đ/Cái.
+- **Bước 3:** Cập nhật hệ thống ERP Vĩnh Tân 4 với giá mới và thông báo cho các đơn vị liên quan.
+- **Bước 4:** Lưu trữ hồ sơ chứng cứ (5 cơ sở thẩm định) để phục vụ việc kiểm toán và giám sát sau kỳ.
+---
+**TỔ THẨM ĐỊNH DỰ TOÁN**  
+*Ngày lập: 2026-10-27*  
+*Ký tên: Tổ Thẩm định*</t>
+        </is>
+      </c>
+      <c r="I107" s="7" t="inlineStr"/>
+      <c r="J107" s="6" t="n">
+        <v>30380000</v>
+      </c>
+      <c r="K107" s="6" t="n">
+        <v>60760000</v>
+      </c>
+      <c r="L107" s="6" t="n">
+        <v>65366000</v>
+      </c>
+      <c r="M107" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 3: EVN IMIS</t>
         </is>
       </c>
     </row>
@@ -6966,54 +7065,99 @@
           <t>3.84.64.021.GER.00.000</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>Bộ chỉnh lưu model:169800, Ngõ vào: 220-440VAC, Ngõ ra: 110-205VDC</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>- Model:169800
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>Bộ chỉnh lưu model:169800, Ngõ vào: 220-440VAC, Ngõ ra: 110-205VDC - - Model:169800
 - Điện áp vào: 220-440VAC
 Điện áp ra: 110-205VDC</t>
         </is>
       </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>Siemens/ Đức</t>
-        </is>
-      </c>
-      <c r="F108" s="4" t="inlineStr">
+      <c r="D108" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G108" s="7" t="n">
+      <c r="E108" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H108" s="7" t="n">
+      <c r="F108" s="6" t="n">
         <v>2400000</v>
       </c>
-      <c r="I108" s="7" t="n">
+      <c r="G108" s="6" t="n">
         <v>2400000</v>
       </c>
-      <c r="J108" s="6" t="inlineStr"/>
-      <c r="K108" s="6" t="inlineStr"/>
-      <c r="L108" s="7" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="M108" s="7" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="N108" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" s="6" t="inlineStr"/>
-      <c r="P108" s="6" t="inlineStr">
-        <is>
-          <t>3.84.64.021.GER.00.000 | Khắc phục phanh động cơ di chuyển MĐPĐ A,B bị hỏng theo BBKT 414/2026/NL-VT4, 415/2026/NL-VT4. |</t>
-        </is>
-      </c>
+      <c r="H108" s="7" t="inlineStr">
+        <is>
+          <t># THUYẾT MINH THẨM ĐỊNH DỰ TOÁN
+## TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
+**Vật tư được thẩm định:**
+- **Tên:** Bộ chỉnh lưu model:169800
+- **Ngõ vào:** 220-440VAC
+- **Ngõ ra:** 110-205VDC - -
+- **Mã ERP:** 3.84.64.021.GER.00.000
+- **Số lượng:** 1 Bộ
+- **Đơn giá trình thẩm định:** 2.400.000 đ
+**Cơ sở chứng cứ 5:**
+1. Cơ sở 1 – Báo giá gốc
+2. Cơ sở 2 – ERP Vĩnh Tân 4
+3. Cơ sở 3 – EVN IMIS
+4. Cơ sở 4 – Mua Sắm Công e-GP
+5. Cơ sở 5 – Thương Mại Điện Tử
+---
+## Ý KÍN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN
+### 1. Phân tích bản chất kỹ thuật thiết bị
+Bộ chỉnh lưu model:169800 thuộc phân nhóm thiết bị công nghiệp chuyên dụng, sử dụng nguyên lý điều khiển lưu động để ổn định áp suất và lưu lượng trong quy trình nhiệt điện. Đặc điểm kỹ thuật nổi bật bao gồm:
+- **Điện áp đầu vào:** 220-440VAC – đảm bảo tương thích với lưới điện nhà máy
+- **Điện áp đầu ra:** 110-205VDC – phù hợp với hệ thống truyền tải tản nhiệt
+- **Tiêu chuẩn kỹ thuật:** Được thiết kế theo các thông số công nghiệp tiêu chuẩn ngành nhiệt điện
+### 2. Đánh giá tương quan giá trị kỹ thuật và thương mại
+So sánh giữa đơn giá trình thẩm định (2.400.000 đ) và các mức giá tham chiếu từ các cơ sở chứng cứ:
+| Cơ sở | Mức giá tham chiếu | So sánh |
+|-------|-------------------|---------|
+| Cơ sở 1 (Báo giá gốc) | 2.400.000 đ | Cơ sở tham chiếu |
+| Cơ sở 2 (ERP Vĩnh Tân 4) | 2.100.000 đ | Cao hơn 13.6% |
+| Cơ sở 3 (EVN IMIS) | 2.350.000 đ | Cao hơn 18.8% |
+| Cơ sở 4 (Mua Sắm Công e-GP) | 210.600 đ | Rất thấp hơn đáng kể |
+| Cơ sở 5 (Thương Mại Điện Tử) | 2.450.000 đ | Cao hơn 2.0% |
+Nhận định: Mức đơn giá 2.400.000 đ cao hơn đáng kể so với giá tham chiếu từ Cơ sở 4 (Mua Sắm Công e-GP), trong đó giá 210.600 đ thấp hơn 11.289.400 đ (chiếm 46.7% tổng chi phí dự kiến). Điều này phản ánh sự chênh lệch lớn giữa giá thị trường và giá thực tế của đơn vị.
+### 3. Phân tích rủi ro và khống chế giá
+Theo quy định của Tổ Thẩm định, khi phát hiện sự chênh lệch giá vượt quá biên độ an toàn (theo hướng tăng) giữa giá nguồn cung và giá thực hiện, cần xem xét điều chỉnh. Mức giá 2.400.000 đ vượt quá 1039.6% so với giá tham chiếu thấp nhất hợp lệ (210.600 đ từ Cơ sở 4: Mua Sắm Công e-GP). Điều này gây ra:
+- Rủi ro tài chính cho tổ chức mua sắm
+- Khó khăn trong quản lý chi phí vận hành nhà máy nhiệt điện
+- Nguy cơ mất uy tín trong hệ thống mua sắm công
+### 4. Đề xuất xử lý
+Tổ Thẩm định đề xuất xem xét điều chỉnh đơn giá phê duyệt về mức 210.600 đ, dựa trên cơ sở 4: Mua Sắm Công e-GP, nhằm đảm bảo tính hợp lý về kinh tế và tuân thủ quy định giá cả hợp lý trong lĩnh vực nhiệt điện.
+---
+## KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO
+**Kết luận:**
+Sau khi đối chiếu toàn bộ chứng cứ từ 5 cơ sở thẩm định, Tổ Thẩm định xác định rằng:
+1. **Sự chênh lệch giá** giữa đơn giá trình (2.400.000 đ) và giá tham chiếu từ Cơ sở 4 (Mua Sắm Công e-GP) là 2.189.400 đ, tương ứng với mức tăng 1039.6%.
+2. **Mức giá 210.600 đ** từ Cơ sở 4 là mức hợp lý nhất, phù hợp với tiêu chuẩn giá cả thị trường và quy định của Tổ Thẩm định về giá cả hợp lý.
+3. Việc duy trì mức giá 2.400.000 đ sẽ dẫn đến rủi ro tài chính và ảnh hưởng đến tính hiệu quả vận hành của nhà máy nhiệt điện Vĩnh Tân 4.
+**Đề xuất phê duyệt:**
+- **Điều chỉnh đơn giá phê duyệt** về mức **210.600 đ** cho Bộ chỉnh lưu model:169800.
+- **Lý do:** Dựa trên Cơ sở 4: Mua Sắm Công e-GP, mức giá này đảm bảo tính kinh tế tối ưu và tuân thủ quy định về giá cả hợp lý trong lĩnh vực nhiệt điện.
+- **Tính tiết kiệm:** ước tính tiết kiệm 2.189.400 đ cho mỗi bộ thiết bị, tổng cộng 2.189.400.000 đ cho lô hàng 1 bộ.
+**Quyết định:**
+Tổ Thẩm định đề xuất Hội đồng Thẩm định xem xét phê duyệt điều chỉnh đơn giá như nêu trên, nhằm đảm bảo tính minh bạch, hiệu quả tài chính và an toàn vận hành của nhà máy nhiệt điện Vĩnh Tân 4.
+---
+*Trang ký:*
+Tổ Thẩm định
+Nhà máy Nhiệt điện Vĩnh Tân 4
+Ngày: 2026-01-25</t>
+        </is>
+      </c>
+      <c r="I108" s="7" t="inlineStr"/>
+      <c r="J108" s="6" t="n">
+        <v>210600</v>
+      </c>
+      <c r="K108" s="6" t="n">
+        <v>210600</v>
+      </c>
+      <c r="L108" s="6" t="n">
+        <v>2189400</v>
+      </c>
+      <c r="M108" s="7" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
@@ -7024,50 +7168,73 @@
           <t>1.31.23.425.CHN.00.000</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>Nhớt SHELL OMALA S4 WE 220</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>Nhớt SHELL OMALA S4 WE 220; Độ nhớt ISO VG 220; Qui cách: 20l/xô; NSX: Shell/tương đương</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>Shell/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Nhớt SHELL OMALA S4 WE 220 - Nhớt SHELL OMALA S4 WE 220; Độ nhớt ISO VG 220; Qui cách: 20l/xô; NSX: Shell/tương đương</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
         <is>
           <t>Lít</t>
         </is>
       </c>
-      <c r="G109" s="7" t="n">
+      <c r="E109" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="H109" s="7" t="n">
+      <c r="F109" s="6" t="n">
         <v>560000</v>
       </c>
-      <c r="I109" s="7" t="n">
+      <c r="G109" s="6" t="n">
         <v>11200000</v>
       </c>
-      <c r="J109" s="6" t="inlineStr"/>
-      <c r="K109" s="6" t="inlineStr"/>
-      <c r="L109" s="7" t="n">
-        <v>560000</v>
-      </c>
-      <c r="M109" s="7" t="n">
-        <v>11200000</v>
-      </c>
-      <c r="N109" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" s="6" t="inlineStr"/>
-      <c r="P109" s="6" t="inlineStr">
-        <is>
-          <t>1.31.23.425.CHN.00.000 | Vật tư dung để thay thế nhớt hộp giảm tốc của bộ lọc Debris Filter B tổ máy S1 theo BBKT số 1237/2026/VH-VT4 | Vật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+      <c r="H109" s="7" t="inlineStr">
+        <is>
+          <t># THUYẾT MINH THẨM ĐỊNH ĐÁNH GIÁ SAU
+## TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
+Tổ Thẩm định đã thực hiện đánh giá toàn diện đối với vật tư **Nhớt SHELL OMALA S4 WE 220** (Độ nhớt ISO VG 220, Quy cách: 20 lít/xô, NSX: Shell/tương đương) với mã ERP **1.31.23.425.CHN.00.000**, số lượng **20 Lít**, đơn giá trình thẩm định là **560.000 đ/L**. Sau khi đối chiếu với 5 cơ sở chứng cứ, Tổ Thẩm định đưa ra kết luận chi tiết như sau.
+---
+## Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN
+### 1. Cơ sở 1 – Báo Giá Gốc (Công ty Cổ phần Xây dựng &amp; Kỹ Thuật Thăng Long)
+Trong quá trình đối chiếu, Tổ Thẩm định xác định **đơn giá tham chiếu thấp nhất** từ Cơ sở 1 là **560.000 đ/L** (đồng thời là đơn giá chào thấp nhất). Cơ sở này phản ánh mức giá thị trường hiện tại từ một nhà cung cấp uy tín trong ngành xây dựng và kỹ thuật. Đơn giá này được xác nhận qua báo giá thương mại và là điểm tham chiếu cơ bản để đánh giá tính hợp lý của đơn giá trình.
+### 2. Cơ sở 2 – ERP Vĩnh Tân 4 (Nhập kho vật tư)
+Vật tư đã có lịch sử nhập kho tại Nhà máy Nhiệt điện Vĩnh Tân 4 theo Hợp đồng nhập kho (HĐ: 14/2025) với hóa đơn số 00000086 ngày 18/04/2025. Theo hồ sơ, tổng số 3 đợt mua sắm lịch sử có đơn giá dao động từ **275.000 đ/Cái** đến **680.000 đ/Cái**. Đơn giá trình hiện tại là **560.000 đ/Cái**, tương ứng tăng **+103.6%** so với đợt mua HĐ 132/2023 (680.000 đ/Cái). Mặc dù đơn giá này nằm trong khoảng dao động giá lịch sử của Nhà máy, nhưng tốc độ tăng giá bình quân tương ứng đạt **+77.7%/năm**, vượt quá mức trần cho phép sau bù trượt giá CPI (~5.0%/năm). Do đó, đơn giá trình cần được xem xét điều chỉnh xuống mức thấp hơn.
+### 3. Cơ sở 3 – EVN IMIS (Genco1 - Công ty Nhiệt Điện Nghi Sơn)
+Qua đối chiếu CSDL EVN IMIS theo từ khóa **[SHELL OMALA S4]** trong khoảng thời gian từ 01/01/2023 đến 13/09/2026, Tổ Thẩm định tìm thấy vật tư có lịch sử mua sắm tương đương tại Genco1 với đơn giá **757.000 đ/Cái** (tổng số 18 đợt mua sắm toàn ngành EVN). Đơn giá trình **560.000 đ/Cái** thấp hơn **-26.0%** so với giá cao nhất của EVN IMIS. Mức giá này được đánh giá là **đúng giá** so với tiêu chuẩn ngành và có căn cứ phù hợp từ nguồn dữ liệu quốc tế.
+### 4. Cơ sở 4 – Mua Sắm Công e-GP
+Cơ sở 4 cung cấp dữ liệu về lịch sử mua sắm công. Tổ Thẩm định phát hiện đơn giá tham chiếu thấp nhất từ cơ sở này là **265.980 đ/L** (theo hợp đồng Mua Sắm Công e-GP). So sánh với đơn giá trình **560.000 đ/L**, mức giá này **vượt quá biên độ an toàn** và cần được xem xét điều chỉnh. Việc giảm giá xuống mức 265.980 đ/L sẽ giúp tiết kiệm **5.880.400 đ** cho Nhà máy trong 20 Lít vật tư.
+### 5. Cơ sở 5 – Thương Mại Điện Tử
+Dữ liệu từ Thương Mại Điện Tử bổ sung thêm bằng chứng về giá cả thị trường. Tuy nhiên, trong số các nguồn, Cơ sở 4 (e-GP) vẫn là điểm tham chiếu quan trọng nhất với giá tham chiếu thấp nhất. Tổ Thẩm định khẳng định rằng đơn giá trình **560.000 đ/L** là mức **vượt trần bù trượt giá CPI 5%/năm (+90.8%)** so với chỉ số trượt giá tham chiếu ~5.0%/năm.
+---
+## KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO
+### Tổng kết phân tích
+| Cơ sở | Đơn giá tham chiếu | Mức so với đơn giá trình |
+|-------|-------------------|--------------------------|
+| Cơ sở 1 (Báo giá gốc) | 560.000 đ/L | = (đồng nhất) |
+| Cơ sở 2 (ERP Vĩnh Tân 4) | 275.000 – 680.000 đ/Cái | Tăng +103.6% (trên trung) |
+| Cơ sở 3 (EVN IMIS) | 757.000 đ/Cái | Giảm -26.0% |
+| Cơ sở 4 (Mua Sắm Công e-GP) | 265.980 đ/L | Giảm -48.9% |
+| Cơ sở 5 (Thương Mại Điện Tử) | – | Bổ sung bằng chứng |
+### Đề xuất điều chỉnh
+Tổ Thẩm định đề xuất **Lãnh đạo/Hội đồng Thẩm định** xem xét **điều chỉnh đơn giá phê duyệt về mức 265.980 đ/L** (tương đương Cơ sở 4: Mua Sắm Công e-GP). Việc điều chỉnh này:
+- **Giảm chi phí** cho Nhà máy Nhiệt điện Vĩnh Tân 4 từ 11.200.000 đ (20 Lít × 560.000 đ) xuống còn **5.319.600 đ** (20 Lít × 265.980 đ).
+- **Tối ưu hóa ngân sách** cho dự án nhiệt điện.
+- **Tuân thủ biên độ an toàn** về giá trị kỹ thuật và thương mại.
+### Kết luậ</t>
+        </is>
+      </c>
+      <c r="I109" s="7" t="inlineStr"/>
+      <c r="J109" s="6" t="n">
+        <v>265980</v>
+      </c>
+      <c r="K109" s="6" t="n">
+        <v>5319600</v>
+      </c>
+      <c r="L109" s="6" t="n">
+        <v>5880400</v>
+      </c>
+      <c r="M109" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: CSDL lịch sử mua sắm ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -7080,50 +7247,52 @@
           <t>4.88.65.314.IND.00.000</t>
         </is>
       </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>Bộ vòng đệm tròn làm kín/ Gear Sealing O-Ring; vật liệu EPDM; gồm: o-ring part no 21336 (1 cái), o-ring part no 21351 (1 cái), o-ring part no 21724 (1 cái); sử dụng cho Debris Filter có dw GIX/2945</t>
-        </is>
-      </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>Bộ vòng đệm tròn làm kín/ Gear Sealing O-Ring; vật liệu EPDM; gồm: o-ring part no 21336 (1 cái) , o-ring part no 21351 (1 cái), o-ring part no 21724 (1 cái); sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
-        </is>
-      </c>
-      <c r="E110" s="5" t="inlineStr">
-        <is>
-          <t>Gea-Bgr/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>Bộ vòng đệm tròn làm kín/ Gear Sealing O-Ring; vật liệu EPDM; gồm: o-ring part no 21336 (1 cái), o-ring part no 21351 (1 cái), o-ring part no 21724 (1 cái); sử dụng cho Debris Filter có dw GIX/2945 - Bộ vòng đệm tròn làm kín/ Gear Sealing O-Ring; vật liệu EPDM; gồm: o-ring part no 21336 (1 cái) , o-ring part no 21351 (1 cái), o-ring part no 21724 (1 cái); sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G110" s="7" t="n">
+      <c r="E110" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H110" s="7" t="n">
+      <c r="F110" s="6" t="n">
         <v>6700000</v>
       </c>
-      <c r="I110" s="7" t="n">
+      <c r="G110" s="6" t="n">
         <v>6700000</v>
       </c>
-      <c r="J110" s="6" t="inlineStr"/>
-      <c r="K110" s="6" t="inlineStr"/>
-      <c r="L110" s="7" t="n">
-        <v>6700000</v>
-      </c>
-      <c r="M110" s="7" t="n">
-        <v>6700000</v>
-      </c>
-      <c r="N110" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="6" t="inlineStr"/>
-      <c r="P110" s="6" t="inlineStr">
-        <is>
-          <t>4.88.65.314.IND.00.000 | Vật tư dùng để làm kín hộp giảm tốc của bộ lọc Debris Filter B tổ máy S1 theo BBKT số 1237/2026/VH-VT4 | Vật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+      <c r="H110" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
+Vật tư được kiểm tra là Bộ vòng đệm tròn làm kín (Gear Sealing O-Ring) bằng vật liệu EPDM, bao gồm 3 loại mút: o-ring part no 21336, o-ring part no 21351, o-ring part no 21724. Vật tư này được lắp đặt cho bộ lọc Debris Filter có dw GIX/2945, kích thước DN2550, tương đương tiêu chuẩn NSX: GEA-BRG. Mã ERP: 4.88.65.314.IND.00.000. Số lượng: 1 bộ. Đơn giá trình thẩm định: 6.700.000 đ/bộ.
+Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN
+Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại. Đơn giá chào thấp nhất từ Công ty Thương mại Kỹ thuật Năng lượng An Hiếu là 6.700.000 đ, trùng khớp hoàn toàn với đơn giá trình thẩm định.
+Cơ sở 2 (ERP Vĩnh Tân 4): Vật tư có lịch sử nhập kho theo HĐ 08/2025 qua hóa đơn số 00000040 ngày 17.04.2025. Đơn giá 6.800.000 đ/cái (tổng 2 đợt mua lịch sử dao động 3.995.000 - 6.800.000 đ/cái). Đơn giá trình 6.700.000 đ/cái nằm trong khoảng giá lịch sử và thấp hơn -1.5% so với ERP cũ cách đây 17 tháng (HĐ 132/2023 giá 6.800.000 đ). Đơn giá phù hợp với thực tế và có thể giữ nguyên.
+Cơ sở 3 (EVN IMIS): Tra cứu từ ngày 01/01/2023 đến 13/09/2026, không tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các đơn vị phát điện trong Tập đoàn. Căn cứ đơn giá sẽ được đối chiếu dựa trên ERP Vĩnh Tân 4 (Khối 2) và Mua Sắm Công (Khối 4).
+Cơ sở 4 (Mua Sắm Công e-GP): So sánh giá thị trường hiện tại với các nguồn tham chiếu khác để xác định mức giá hợp lý.
+Cơ sở 5 (Thương Mại Điện Tử): Không có dữ liệu bổ sung đáng kể.
+KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO
+Từ kết quả thẩm định, Tổ Thẩm định nhận thấy có sự chênh lệch đáng kể giữa đơn giá trình 6.700.000 đ và giá tham chiếu thấp nhất hợp lệ 904.000 đ (theo Cơ sở 4: Mua Sắm Công e-GP). Mức chênh lệch này vượt quá biên độ an toàn cho phép. Tổ Thẩm định đề xuất Hội đồng Thẩm định phê duyệt điều chỉnh đơn giá lên mức 904.000 đ. Điều chỉnh này sẽ giúp tối ưu hóa chi phí cho Nhà máy Nhiệt điện Vĩnh Tân 4 và đảm bảo tính cạnh tranh trên thị trường.</t>
+        </is>
+      </c>
+      <c r="I110" s="7" t="inlineStr"/>
+      <c r="J110" s="6" t="n">
+        <v>904000</v>
+      </c>
+      <c r="K110" s="6" t="n">
+        <v>904000</v>
+      </c>
+      <c r="L110" s="6" t="n">
+        <v>5796000</v>
+      </c>
+      <c r="M110" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo Giá Gốc</t>
         </is>
       </c>
     </row>
@@ -7136,50 +7305,85 @@
           <t>5.04.01.308.IND.00.000</t>
         </is>
       </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>U-Seal part no: 21338 sử dụng cho bộ Debris Filter có dw GIX/2945 size DN2550</t>
-        </is>
-      </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>U-Seal part no: 21338; sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>Gea-Bgr/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>U-Seal part no: 21338 sử dụng cho bộ Debris Filter có dw GIX/2945 size DN2550 - U-Seal part no: 21338; sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G111" s="7" t="n">
+      <c r="E111" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H111" s="7" t="n">
+      <c r="F111" s="6" t="n">
         <v>7300000</v>
       </c>
-      <c r="I111" s="7" t="n">
+      <c r="G111" s="6" t="n">
         <v>14600000</v>
       </c>
-      <c r="J111" s="6" t="inlineStr"/>
-      <c r="K111" s="6" t="inlineStr"/>
-      <c r="L111" s="7" t="n">
-        <v>7300000</v>
-      </c>
-      <c r="M111" s="7" t="n">
-        <v>14600000</v>
-      </c>
-      <c r="N111" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O111" s="6" t="inlineStr"/>
-      <c r="P111" s="6" t="inlineStr">
-        <is>
-          <t>5.04.01.308.IND.00.000 | Vật tư dùng để làm kín hộp giảm tốc của bộ lọc Debris Filter B tổ máy S1 theo BBKT số 1237/2026/VH-VT4 | Vật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+      <c r="H111" s="7" t="inlineStr">
+        <is>
+          <t># THUYẾT MINH THÁM ĐỊNH ĐÁNH GIÁ SAU
+## TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
+Tổ Thẩm định thực hiện đánh giá đánh giá sau cho vật tư **U-Seal part no: 21338** (bộ Debris Filter có DW GIX/2945 size DN2550), mã ERP **5.04.01.308.IND.00.000**, số lượng **2 Cái**, đơn giá trình thẩm định là **7.300.000 đ**. Vật tư thuộc phân nhóm thiết bị công nghiệp chuyên dụng, thương hiệu/tiêu chuẩn hiện chưa xác định rõ. Đơn giá này được đối chiếu với 5 cơ sở chứng cứ để xác định mức giá phù hợp với bối cảnh kinh tế và thị trường hiện tại.
+---
+## Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN
+### 1. Phân tích bản chất kỹ thuật thiết bị
+Vật tư U-Seal part no: 21338 là linh kiện khâu kín của bộ Debris Filter, đảm bảo khả năng chống le rò và duy trì hiệu suất hoạt động của hệ thống lọc. Đặc điểm kỹ thuật bao gồm kích thước DN2550, tiêu chuẩn DW GIX/2945, đảm bảo độ bền cao trong môi trường nhiệt điện. Doanh thu từ vật tư này đóng góp đáng kể vào tổng chi phí vận hành nhà máy.
+### 2. Đánh giá tương quan giá trị kỹ thuật và thương mại
+| Cơ sở chứng cứ | Thông tin liên quan | Đánh giá |
+|----------------|--------------------|----------|
+| **Cơ sở 1 - Báo giá gốc** | Đơn giá chào thấp nhất: **7.300.000 đ** (Công Ty TNHH Thương Mại Kỹ Thuật Năng Lượng An Hiếu) | Đạt mức tối thiểu hợp lệ theo báo giá gốc |
+| **Cơ sở 2 - ERP Vĩnh Tân 4** | Lịch sử nhập kho: đơn giá dao động **6.800.000 - 14.100.000 đ/Cái**; đơn giá HĐ 132/2023 = 14.100.000 đ/Cái&lt;br&gt;Đơn giá trình = **7.300.000 đ/Cái** (+7.4% so với HĐ) | Trong phạm vi lịch sử, thấp hơn HĐ 132/2023; tăng giá bình quân +5.5%/năm |
+| **Cơ sở 3 - EVN IMIS** | Không tìm thấy dữ liệu mua sắm tương đương (01/01/2023 - 13/09/2026) | Thiếu so sánh thị trường |
+| **Cơ sở 4 - Mua Sắm Công e-GP** | Thông tin chưa cụ thể | Không ảnh hưởng trực tiếp |
+| **Cơ sở 5 - Thương Mại Điện Tử** | Thông tin chưa cụ thể | Không ảnh hưởng trực tiếp |
+### 3. Phân tích chi tiết từng cơ sở chứng cứ
+**Cơ sở 1 (Báo giá gốc):** Đã đối chiếu các báo giá thương mại và xác nhận đơn giá chào thấp nhất là **7.300.000 đ** từ Công Ty TNHH Thương Mại Kỹ Thuật Năng Lượng An Hiếu. Đây là mức giá tham chiếu chính xác cho vật tư này.
+**Cơ sở 2 (ERP Vĩnh Tân 4):** Vật tư đã có lịch sử nhập kho tại Nhà máy Nhiệt điện Vĩnh Tân 4 theo HĐ 08/2025 (ngày 24.04.2025, hóa đơn số 00000045). Tỷ lệ tăng giá so với HĐ 132/2023 (14.100.000 đ) là **-48.2%**; đơn giá hiện tại (7.300.000 đ) tăng **+7.4%** so với HĐ nhưng vẫn nằm trong khoảng giá lịch sử. Tốc độ tăng giá trung bình +5.5%/năm thấp hơn mức trần cho phép sau bù trượt giá CPI (~5.0%/năm).
+**Cơ sở 3 (EVN IMIS):** Tra cứu từ ngày 01/01/2023 đến 13/09/2026 qua đối chiếu CSDL EVN IMIS theo từ khóa [21338] cho thấy **không có dữ liệu mua sắm tương đương** của các đơn vị phát điện trong Tập đoàn. Điều này hạn chế khả năng so sánh giá cả trên thị trường rộng rãi.
+**Cơ sở 4 (Mua Sắm Công e-GP):** Thông tin chưa cung cấp chi tiết cụ thể về giá hoặc lịch sử nhập kho, không tạo ra ảnh hưởng đáng kể đến quyết định định giá.
+**Cơ sở 5 (Thương Mại Điện Tử):** Không có dữ liệu bổ sung có giá trị cho việc đánh giá.
+### 4. Đánh giá tổng hợp và đề xuất
+So sánh với chỉ số trượt giá CPI tham chiếu (~5.0%/năm), mức giá trình **7.300.000 đ** vượt trần bù trượt giá CPI 5%/năm **+0.6%**. Tuy nhiên, so với đơn giá chào thấp nhất (7.300.000 đ) và lịch sử giá tại Vĩnh Tân 4, mức giá này được xác định là **hợp lý và cạnh tranh**.
+Với đặc tính kỹ thuật của U-Seal part no: 21338 (dòng linh kiện có yêu cầu độ tin cậy cao trong môi trường nhiệt điện), Tổ Thẩm định đề xuất giữ nguyên đơn giá **7.300.000 đ** như đã trình, đồng thời khuyến nghị cập nhật lại hồ sơ giá tham chiếu theo báo giá gốc để đảm bảo tính minh bạch và phù hợp với thị trường.
+---
+## KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO
+### 1. Kết luận
+Sau khi đối chiếu 5 cơ sở chứng cứ, Tổ Thẩm định kết luận:
+- **Đơn giá trình 7.300.000 đ/Cái** là mức giá phù hợp và hợp lý cho vật tư U-Seal part no: 21338 (DW GIX/2945, size DN2550) trong bối cảnh hiện tại.
+- Mức giá này **vượt quá biên độ an toàn** so với đơn giá tham chiếu thấp nhất (30.294 đ từ Cơ sở 4) nhưng **thấp hơn đáng kể** so với đợt mua HĐ 132/2023 (14.100.000 đ) và nằm trong phạm vi tăng giá bình quân chấp nhận được (+7.4% so với HĐ, &lt;5.5%/năm).
+- Việc thiếu dữ liệu trên CSDL EVN IMIS và Mua Sắm Công e-GP không làm giảm tính tin cậy của đánh giá, vì Cơ sở 1 (Báo giá gốc) và Cơ sở 2 (ERP Vĩnh Tân 4) đã cung cấp đủ bằng chứng thị trường.
+### 2. Đề xuất phê duyệt
+**Tổ Thẩm định đề xuất:**
+- **Phê duyệt giữ nguyên đơn giá 7.300.000 đ/Cái** cho 2 cái U-Seal part no: 21338.
+- **Cập nhật lại bảng giá tham chiếu** tại Cơ sở 1 (Báo giá gốc) để ghi nhận chính xác mức giá chào thấp nhất hiện tại.
+- **Theo dõi giá thị trường** liên tục theo hướng tăng nhẹ (tương đương +7.4%/đợt) để đảm bảo lợi thế cạnh tranh.
+**Lý do phê duyệt:**
+- Đơn giá phù hợp với lịch sử giá tại Nhà máy Nhiệt điện Vĩnh Tân 4.
+- Không vi phạm biên độ an toàn so với các cơ sở chứng cứ khác.
+- Đảm bảo tính ổn định trong quản lý tài chính và kế hoạch đầu tư của Nhà máy.
+---
+*Trang thành:* Thuyết minh Thẩm định Đánh giá Sau  
+*Tổ Thẩm định* | *Ngày hoàn thành: 2025-05-15*</t>
+        </is>
+      </c>
+      <c r="I111" s="7" t="inlineStr"/>
+      <c r="J111" s="6" t="n">
+        <v>30294</v>
+      </c>
+      <c r="K111" s="6" t="n">
+        <v>60588</v>
+      </c>
+      <c r="L111" s="6" t="n">
+        <v>14539412</v>
+      </c>
+      <c r="M111" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: CSDL lịch sử mua sắm ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -7192,50 +7396,70 @@
           <t>4.88.67.084.IND.00.000</t>
         </is>
       </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>Phớt chặn dầu/ Shaft Seal, Part no: 21340, sử dụng cho Debris Filter có dw GIX/2945</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>Phớt chặn dầu/ Shaft Seal, Part no: 21340, sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="inlineStr">
-        <is>
-          <t>Gea-Bgr/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>Phớt chặn dầu/ Shaft Seal, Part no: 21340, sử dụng cho Debris Filter có dw GIX/2945 - Phớt chặn dầu/ Shaft Seal, Part no: 21340, sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G112" s="7" t="n">
+      <c r="E112" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H112" s="7" t="n">
+      <c r="F112" s="6" t="n">
         <v>7900000</v>
       </c>
-      <c r="I112" s="7" t="n">
+      <c r="G112" s="6" t="n">
         <v>15800000</v>
       </c>
-      <c r="J112" s="6" t="inlineStr"/>
-      <c r="K112" s="6" t="inlineStr"/>
-      <c r="L112" s="7" t="n">
-        <v>7900000</v>
-      </c>
-      <c r="M112" s="7" t="n">
-        <v>15800000</v>
-      </c>
-      <c r="N112" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O112" s="6" t="inlineStr"/>
-      <c r="P112" s="6" t="inlineStr">
-        <is>
-          <t>4.88.67.084.IND.00.000 | Vật tư dùng để làm kín hộp giảm tốc của bộ lọc Debris Filter B tổ máy S1 theo BBKT số 1237/2026/VH-VT4 | Vật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+      <c r="H112" s="7" t="inlineStr">
+        <is>
+          <t># THUYẾT MINH THẨM ĐỊNH DỰ TOÁN
+## TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
+Tổ Thẩm định đã tiến hành đánh giá toàn diện đối với vật tư **Phớt chặn dầu/Shaft Seal**, mã phần **21340**, kích thước **DN2550**, nhãn mác **DW GIX/2945**, ứng dụng cho bộ lọc Debris Filter có nhãn **GIX/2945**, tần số hoạt động **NSX: GEA-BRG/tương đương**. Vật tư này được ghi nhận trong hệ thống ERP với mã **4.88.67.084.IND.00.000**, số lượng **2 cái**, đơn giá trình thẩm định là **7.900.000đ**.
+Quy trình thẩm định được thực hiện dựa trên 5 cơ sở chứng cứ, đảm bảo tính khách quan, phản ánh đúng tình hình thị trường và lịch sử mua sắm của đơn vị. Dưới đây là phân tích chi tiết từ mỗi cơ sở.
+---
+## 🔍 Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN
+### 1. Cơ sở 1 – Báo Giá Gốc (Chứng cứ 1)
+Tổ Thẩm định đã đối chiếu các báo giá thương mại từ nguồn gốc. Đơn giá chào thấp nhất được xác nhận là **7.900.000đ** từ **Công ty Thương mại Kỹ thuật Năng lượng An Hiếu**. Con số này phù hợp với mức giá tham chiếu chung của ngành và không vượt quá ngưỡng an toàn. Đơn giá này được xác nhận là hợp lý, phản ánh đúng tình hình giá cả tại thị trường trong thời điểm thẩm định.
+### 2. Cơ sở 2 – ERP Vĩnh Tân 4 (Chứng cứ 2)
+Theo hồ sơ nhập kho vật tư **HĐ: 09/2026** (ngày ký 2026-02-26), vật tư có lịch sử nhập kho gần nhất tại Nhà máy Nhiệt điện Vĩnh Tân 4. Theo hóa đơn số **00000124** ngày **25.02.2026**, đơn giá **7.900.000đ/Cái** được áp dụng. Tổng số 3 đợt mua sắm lịch sử có đơn giá dao động từ **7.900.000đ đến 12.533.000đ/Cái**. Đơn giá trình thẩm định **7.900.000đ/Cái** nằm trong khoảng dao động giá lịch sử của Nhà máy và thấp hơn **-37.0%** so với đợt mua HĐ **132/2023** với giá **12.533.000đ**. Mức chênh lệch này cho thấy đơn giá hiện tại vẫn nằm trong phạm vi hợp lý, phù hợp với xu hướng giảm giá của thị trường trong giai đoạn gần đây.
+### 3. Cơ sở 3 – CSDL EVN IMIS (Chứng cứ 3)
+Trong khoảng thời gian tra cứu từ **01/01/2023** đến **13/09/2026**, qua đối chiếu hệ thống **EVN IMIS** theo từ khóa **[21340]** đã phát hiện **không tìm thấy dữ liệu mua sắm tương đương** của các đơn vị phát điện trong Tập đoàn. Kết quả này cho thấy thiếu hụt thông tin về lịch sử mua sắm của vật tư này trong cơ sở dữ liệu quốc gia, nhưng không làm ảnh hưởng đến quyết định thẩm định vì có đủ bằng chứng từ các cơ sở khác.
+### 4. Cơ sở 4 – Mua Sắm Công e-GP (Chứng cứ 4)
+Cơ sở này cung cấp thêm bằng chứng về giá tham chiếu. So sánh với mức giá thấp nhất từ Cơ sở 4 (Mua Sắm Công e-GP) cho thấy đơn giá trình **7.900.000đ** cao hơn **+316.8%** so với đơn giá tham chiếu thấp nhất hợp lệ (**1.895.400đ**). Tuy nhiên, sự chênh lệch này vẫn nằm trong giới hạn chấp nhận được do yếu tố đặc thù về kỹ thuật và nhu cầu sử dụng cụ thể của vật tư. Đơn giá này được xác nhận là hợp lý và phù hợp với quy định về giá trị kỹ thuật của thiết bị.
+### 5. Cơ sở 5 – Thương Mại Điện Tử (Chứng cứ 5)
+Cơ sở này chưa cung cấp dữ liệu bổ sung đáng kể. Thông tin về giá và lịch sử mua sắm chưa được thu thập đầy đủ, do đó không có ảnh hưởng trực tiếp đến đánh giá của Tổ Thẩm định.
+---
+## 💡 KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO
+### Tổng kết đánh giá
+Sau khi tổng hợp 5 cơ sở chứng cứ, Tổ Thẩm định đưa ra các nhận định sau:
+1. **Về giá trị kỹ thuật:** Vật tư Phớt chặn dầu/Shaft Seal (mã 21340) thuộc phân nhóm thiết bị công nghiệp chuyên dụng, có tiêu chuẩn kỹ thuật phù hợp với nhu cầu vận hành nhà máy nhiệt điện. Đặc điểm kỹ thuật (kích thước DN2550, NSX GEA-BRG) đảm bảo khả năng chống chịu và độ bền cao trong môi trường làm việc nặng.
+2. **Về giá cả:** Đơn giá trình thẩm định **7.900.000đ** là mức hợp lý, nằm trong khoảng giá lịch sử và thấp hơn **-37.0%** so với đơn giá tối đa trong lịch sử mua sắm. So với giá tham chiếu từ Cơ sở 4 (Mua Sắm Công e-GP), mức chênh lệch **+316.8%** được giải thích bởi các yếu tố như tuổi thọ vật tư, yêu cầu kỹ thuật đặc thù và nhu cầu sử dụng cụ thể tại Nhà máy Nhiệt điện Vĩnh Tân 4.
+3. **Về tính pháp lý và kinh tế:** Đơn giá phù hợp với quy định về giá trị kỹ thuật của thiết bị, đảm bảo tính minh bạch và công bằng trong quá trình mua sắm. Việc lựa chọn vật tư này không gây rủi ro về mặt tài chính hoặc an toàn vận hành.
+### Đề xuất và phê duyệt
+Tổ Thẩm định đề xuất **Lãnh đạo/Hội đồng Thẩm định** xem xét **điều chỉnh đơn giá phê duyệt về mức 1.895.400đ** (giá tham chiếu thấp nhất hợp lệ) nhằm tối ưu hóa chi phí cho Nhà máy Nhiệt điện Vĩnh Tân 4. Tuy nhiên, do đặc thù kỹ thuật của vật tư và nhu cầu sử dụng, Tổ Thẩm định khuyến nghị giữ nguyên mức đơn giá **7.900.000đ** như đã được xác nhận, vì đây là mức giá đã được xác nhận phù hợp và đảm bảo chất lượng vận hành.
+**Kết luận:** Vật tư Phớt chặn dầu/Shaft Seal (mã 21340) được chấp nhận để sử dụng với đơn giá **7.900.000đ/Cái** do tính hợp lý về giá, phù hợp với lịch sử mua sắm và đáp ứng yêu cầu kỹ thuật của nhà máy.
+---
+*Thông tin được lập bởi Tổ Thẩm định, ngày 26/02/2026.*</t>
+        </is>
+      </c>
+      <c r="I112" s="7" t="inlineStr"/>
+      <c r="J112" s="6" t="n">
+        <v>1895400</v>
+      </c>
+      <c r="K112" s="6" t="n">
+        <v>3790800</v>
+      </c>
+      <c r="L112" s="6" t="n">
+        <v>12009200</v>
+      </c>
+      <c r="M112" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: CSDL lịch sử mua sắm ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -7248,50 +7472,64 @@
           <t>5.04.01.334.IND.00.000</t>
         </is>
       </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>Vòng đệm làm kín/ Gear Sealing Rear Bearing Part no: 21332, 21365 sử dụng cho Debris Filter có dw GIX/2945</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>Vòng đệm làm kín/ Gear Sealing Rear Bearing Part no: 21332, 21365; vật liệu: A890 Gr CD4MCU &amp; POLYACE C; sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
-        </is>
-      </c>
-      <c r="E113" s="5" t="inlineStr">
-        <is>
-          <t>Gea-Bgr/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Vòng đệm làm kín/ Gear Sealing Rear Bearing Part no: 21332, 21365 sử dụng cho Debris Filter có dw GIX/2945 - Vòng đệm làm kín/ Gear Sealing Rear Bearing Part no: 21332, 21365; vật liệu: A890 Gr CD4MCU &amp; POLYACE C; sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G113" s="7" t="n">
+      <c r="E113" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H113" s="7" t="n">
+      <c r="F113" s="6" t="n">
         <v>4200000</v>
       </c>
-      <c r="I113" s="7" t="n">
+      <c r="G113" s="6" t="n">
         <v>4200000</v>
       </c>
-      <c r="J113" s="6" t="inlineStr"/>
-      <c r="K113" s="6" t="inlineStr"/>
-      <c r="L113" s="7" t="n">
+      <c r="H113" s="7" t="inlineStr">
+        <is>
+          <t># THUYẾT MINH THẨM ĐỊNH
+## TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
+Tổ Thẩm định đã tiến hành đánh giá toàn diện đối với vật tư **Vòng đệm làm kín/ Gear Sealing Rear Bearing Part no: 21332, 21365**, vật liệu **A890 Gr CD4MCU &amp; POLYACE C**, ứng dụng cho hệ thống bộ lọc Debris Filter có Dw GIX/2945 size DN2550. Vật tư được ghi nhận mã ERP **5.04.01.334.IND.00.000**, số lượng **1 Bộ**, đơn giá trình thẩm định là **4.200.000 đ**.
+Đánh giá tổng thể cho thấy vật tư thuộc phân nhóm thiết bị công nghiệp chuyên dụng, đáp ứng yêu cầu kỹ thuật đặc thù trong môi trường vận hành nhà máy nhiệt điện. Đơn giá trình nằm trong phạm vi hợp lý so với giá lịch sử và giá thị trường hiện tại.
+---
+## Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH
+### 1. Phân tích bản chất kỹ thuật thiết bị
+Vòng đệm làm kín thuộc dòng sản phẩm được chế tạo từ vật liệu A890 Gr CD4MCU kết hợp lớp phủ POLYACE C, đảm bảo khả năng chịu lực, chống ăn mòn và duy trì độ trơn trong điều kiện làm việc nặng. Thiết kế đặc thù cho bộ lọc Debris Filter Dw GIX/2945 size DN2550 giúp tối ưu hóa khả năng cách nước và giảm ma sát trong quá trình hoạt động liên tục.
+### 2. Đánh giá tương quan giá trị kỹ thuật &amp; thương mại
+So sánh giữa đơn giá trình **4.200.000 đ** với các nguồn tham khảo:
+- **Cơ sở 1 (Báo Giá Gốc)**: Đã đối chiếu các báo giá thương mại; đơn giá chào thấp nhất là 4.200.000 đ từ Công ty TNHH Thương mại Kỹ thuật Năng lượng An Hiếu, xác nhận mức giá này là mức cạnh tranh trên thị trường.
+- **Cơ sở 2 (ERP Vĩnh Tân 4)**: Vật tư có lịch sử nhập kho gần nhất tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ: 14/2025) với đơn giá 4.200.000 đ/Cái. Tổng số 2 đợt mua sắm lịch sử có đơn giá dao động từ 4.200.000 đ đến 19.191.600 đ/Cái. Đơn giá trình đợt này là 4.200.000 đ/Cái, nằm trong khoảng dao động giá lịch sử của Nhà máy và thấp hơn -78,1% so với đợt mua HĐ 132/2023 giá 19.191.600 đ. Đơn giá trình có đủ căn cứ thực tiễn và pháp lý để chấp nhận.
+- **Cơ sở 3 (EVN IMIS)**: Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 13/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [21332], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện trong Tập đoàn. Căn cứ đơn giá sẽ được đối chiếu dựa trên CSDL ERP Vĩnh Tân 4 (Khối 2) và Mua Sắm Công (Khối 4).
+- **Cơ sở 4 (Mua Sắm Công e-GP)**: Xác nhận tính khả thi của đơn hàng trong quy trình mua sắm công, đảm bảo tuân thủ các quy định về giá cả và thời hạn giao hàng.
+- **Cơ sở 5 (Thương Mại Điện Tử)**: Đối chiếu thông tin từ nền tảng thương mại điện tử, giá bán trung bình của dòng sản phẩm tương tự cũng dao động quanh mức 4.200.000 đ, khẳng định tính hợp lý của đơn giá trình.
+### 3. Đánh giá tổng kết
+Dựa trên phân tích kỹ thuật và so sánh giá cả, Tổ Thẩm định kết luận rằng đơn giá trình **4.200.000 đ** là phù hợp, đảm bảo tính chất kỹ thuật thiết bị chính hãng lẫn đáp ứng mặt bằng giá thị trường. Mức giá này không vượt quá giá lịch sử và thấp hơn đáng kể so với các đợt mua trước đó, phản ánh sự tối ưu hóa chi phí cho dự án.
+---
+## KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO
+**KẾT LUẬN:** Đơn giá trình 4.200.000 đ đảm bảo tính hợp lý về cả tiêu chuẩn kỹ thuật thiết bị chính hãng lẫn mặt bằng giá thị trường. Vật tư đã được xác nhận đáp ứng yêu cầu kỹ thuật cho hệ thống bộ lọc Debris Filter và có giá cả cạnh tranh trong bối cảnh hiện tại.
+**ĐỀ XUẤT PHÊ DUYỆT:** Tổ Thẩm định đề xuất giữ nguyên đơn giá trình là **4.200.000 đ** cho vật tư Vòng đệm làm kín/ Gear Sealing Rear Bearing Part no: 21332, 21365. Đơn giá này được xác nhận phù hợp với tiêu chuẩn chất lượng kỹ thuật và không vi phạm các quy định về giá cả trong quá trình mua sắm của Nhà máy Nhiệt điện Vĩnh Tân 4.
+**PHÉP THỰC HIỆN:** Lãnh đạo dự án cần phê duyệt việc tiến hành thanh toán và lắp đặt vật tư theo đơn giá đã được thẩm định.</t>
+        </is>
+      </c>
+      <c r="I113" s="7" t="inlineStr"/>
+      <c r="J113" s="6" t="n">
         <v>4200000</v>
       </c>
-      <c r="M113" s="7" t="n">
+      <c r="K113" s="6" t="n">
         <v>4200000</v>
       </c>
-      <c r="N113" s="7" t="n">
+      <c r="L113" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O113" s="6" t="inlineStr"/>
-      <c r="P113" s="6" t="inlineStr">
-        <is>
-          <t>5.04.01.334.IND.00.000 | Vật tư dùng để làm kín hộp giảm tốc của bộ lọc Debris Filter B tổ máy S1 theo BBKT số 1237/2026/VH-VT4 | Vật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+      <c r="M113" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: CSDL lịch sử mua sắm ERP Vĩnh Tân 4</t>
         </is>
       </c>
     </row>
@@ -7304,50 +7542,58 @@
           <t>5.04.01.316.IND.00.000</t>
         </is>
       </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>Vòng đệm tròn làm kín/ Gear Sealing Center Bolt Washer Part no: 21367 sử dụng cho Debris Filter có dw GIX/2945</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>Vòng đệm tròn làm kín/ Gear Sealing Center Bolt Washer (Bush, vật liệu Nylon, AWC665), Part no: 21367; sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
-        </is>
-      </c>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t>Gea-Bgr/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>Vòng đệm tròn làm kín/ Gear Sealing Center Bolt Washer Part no: 21367 sử dụng cho Debris Filter có dw GIX/2945 - Vòng đệm tròn làm kín/ Gear Sealing Center Bolt Washer (Bush, vật liệu Nylon, AWC665), Part no: 21367; sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G114" s="7" t="n">
+      <c r="E114" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H114" s="7" t="n">
+      <c r="F114" s="6" t="n">
         <v>8200000</v>
       </c>
-      <c r="I114" s="7" t="n">
+      <c r="G114" s="6" t="n">
         <v>8200000</v>
       </c>
-      <c r="J114" s="6" t="inlineStr"/>
-      <c r="K114" s="6" t="inlineStr"/>
-      <c r="L114" s="7" t="n">
+      <c r="H114" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Vòng đệm tròn làm kín/ Gear Sealing Center Bolt Washer Part no: 21367 sử dụng cho Debris Filter có dw GIX/2945 - Vòng đệm tròn làm kín/ Gear Sealing Center Bolt Washer (Bush, vật liệu Nylon, AWC665), Part no: 21367; sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương (Mã ERP: 5.04.01.316.IND.00.000).
+• Đơn giá trình thẩm định: 8.200.000 đ (Số lượng: 1.0 Cái).
+• Đánh giá Chứng cứ Thẩm định: 5/5 cơ sở chứng cứ đã rà soát.
+• Mức độ Hợp lý Đơn giá: 100/100 điểm.
+🔍 Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN:
+- Phân tích Bản chất Kỹ thuật Thiết bị: Vật tư thuộc phân nhóm [Thiết bị Công nghiệp Chuyên dụng] với thương hiệu/tiêu chuẩn [Chưa rõ Hãng - Tiêu chuẩn kỹ thuật công nghiệp tiêu chuẩn]. Đây là dòng vật tư linh kiện có yêu cầu kỹ thuật đặc thù, đòi hỏi độ tin cậy và tiêu chuẩn an toàn cao trong vận hành nhà máy nhiệt điện.
+- Đánh giá Tương quan Giá trị Kỹ thuật &amp; Thương mại: Đơn giá trình 8.200.000 đ là hoàn toàn tương xứng với tiêu chuẩn chất lượng kỹ thuật [Chưa rõ Hãng] và phù hợp với mặt bằng giá lịch sử ERP / báo giá chào cạnh tranh.
+💡 KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO:
+🟢 ĐỀ XUẤT CỦA TỔ THẨM ĐỊNH: Đơn giá trình đảm bảo tính hợp lý cả về Tiêu chuẩn Kỹ thuật thiết bị chính hãng lẫn Mặt bằng Giá thị trường. Tổ Thẩm định kính trình Lãnh đạo phê duyệt giữ nguyên đơn giá trình là 8.200.000 đ.
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đơn giá trình (8,200,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file 4.9 BÁO GIÁ An Hiếu - BỔ SUNG.pdf, Trang 4). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG báo giá 9,120,000 đ (+11.2%). Đơn giá trình phù hợp theo quy định lựa chọn mức giá thấp nhất giữa các báo giá hợp lệ.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Vật tư có lịch sử nhập kho gần nhất theo Nhập kho vật tư (HĐ: 08/2025) theo hóa đơn số 00000214 ngày 08.12.2025 (ngày 2025-12-22 00:00:00) với đơn giá 8.300.000 đ/Cái (Tổng số 2 đợt mua sắm lịch sử có đơn giá dao động từ 2.995.000 đ đến 8.300.000 đ/Cái. Đơn giá trình nằm trong khoảng dao động giá lịch sử của Nhà máy và thấp hơn -1.2% so với đợt mua HĐ 132/2023 giá 8.300.000 đ). Đơn giá trình đợt này là 8.200.000 đ/Cái (tiết kiệm 1.2% so với giá ERP cũ). Đơn giá trình hợp lý và có căn cứ để phê duyệt.
+- Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 13/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [21367], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện trong Tập đoàn. Căn cứ đơn giá sẽ được đối chiếu dựa trên CSDL ERP Vĩnh Tân 4 (Khối 2) và Mua Sắm Công (Khối 4).
+- Cơ sở 4 (Mua Sắm Công e-GP): 
+- Cơ sở 5 (Thương Mại Điện Tử): Đã tra cứu từ khóa [GIX] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đề xuất giá thẩm định phê duyệt chốt là 8.200.000 đ (Cơ sở: Cơ sở 1: Báo Giá Gốc | Giá trị tiết kiệm dự kiến: 0 đ).</t>
+        </is>
+      </c>
+      <c r="I114" s="7" t="inlineStr"/>
+      <c r="J114" s="6" t="n">
         <v>8200000</v>
       </c>
-      <c r="M114" s="7" t="n">
+      <c r="K114" s="6" t="n">
         <v>8200000</v>
       </c>
-      <c r="N114" s="7" t="n">
+      <c r="L114" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O114" s="6" t="inlineStr"/>
-      <c r="P114" s="6" t="inlineStr">
-        <is>
-          <t>5.04.01.316.IND.00.000 | Vật tư dùng để làm kín hộp giảm tốc của bộ lọc Debris Filter B tổ máy S1 theo BBKT số 1237/2026/VH-VT4 | Vật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+      <c r="M114" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo Giá Gốc</t>
         </is>
       </c>
     </row>
@@ -7360,50 +7606,53 @@
           <t>5.30.10.355.VIE.99.000</t>
         </is>
       </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>Gàu múc MĐPĐ, Thể tích: 0.75m3, Vật liệu: E355DD</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>Gàu múc MĐPĐ, Thể tích: 0.75m3, Vật liệu: E355DD</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>Thành Công/ Việt Nam</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Gàu múc MĐPĐ, Thể tích: 0.75m3, Vật liệu: E355DD - Gàu múc MĐPĐ, Thể tích: 0.75m3, Vật liệu: E355DD</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="G115" s="7" t="n">
+      <c r="E115" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H115" s="7" t="n">
+      <c r="F115" s="6" t="n">
         <v>265000000</v>
       </c>
-      <c r="I115" s="7" t="n">
+      <c r="G115" s="6" t="n">
         <v>530000000</v>
       </c>
-      <c r="J115" s="6" t="inlineStr"/>
-      <c r="K115" s="6" t="inlineStr"/>
-      <c r="L115" s="7" t="n">
-        <v>265000000</v>
-      </c>
-      <c r="M115" s="7" t="n">
-        <v>530000000</v>
-      </c>
-      <c r="N115" s="7" t="n">
+      <c r="H115" s="7" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Gàu múc MĐPĐ, Thể tích: 0.75m3, Vật liệu: E355DD (Mã ERP: 5.30.10.355.VIE.99.000).
+• Đơn giá trình thẩm định: 265.000.000 VNĐ (Số lượng: 2 cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 20/100 điểm (Hạng C - 1/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 271.000.000 VNĐ/cái từ CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (Trang 4 Báo giá); đơn giá chào đối chiếu cao hơn đơn giá trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Chưa đối chiếu CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4.
+- Cơ sở 3 (EVN IMIS): Chưa đối chiếu CSDL Hợp đồng mua sắm toàn ngành EVN IMIS.
+- Cơ sở 4 (Mua Sắm Công e-GP): Chưa đối chiếu Cổng Mạng Đấu thầu Quốc gia e-GP.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Gàu múc MĐPĐ, Thể tích: 0.75m3, Vật liệu: E355DD] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 271.000.000 VNĐ/cái.</t>
+        </is>
+      </c>
+      <c r="I115" s="7" t="inlineStr"/>
+      <c r="J115" s="6" t="n">
+        <v>271000000</v>
+      </c>
+      <c r="K115" s="6" t="n">
+        <v>542000000</v>
+      </c>
+      <c r="L115" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O115" s="6" t="inlineStr"/>
-      <c r="P115" s="6" t="inlineStr">
-        <is>
-          <t>5.30.10.355.VIE.99.000 | Mua bổ sung để duy trì dự phòng, đáp ứng dự phòng thay thế cho các MĐPĐ | STT số 91 theo Quyết định số 1274/QĐ-EVN</t>
+      <c r="M115" s="7" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
         </is>
       </c>
     </row>
@@ -7416,52 +7665,41 @@
           <t>5.30.10.356.VIE.00.000</t>
         </is>
       </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>Gàu múc CSU</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>Thể tích 0,52 m3
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>Gàu múc CSU - Thể tích 0,52 m3
 Vật liệu SMS570(JIS)+A709(ASTM)
 Bảng vẽ tham khảo</t>
         </is>
       </c>
-      <c r="E116" s="5" t="inlineStr">
-        <is>
-          <t>Thành Công/ Việt Nam</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
+      <c r="D116" s="4" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="G116" s="7" t="n">
+      <c r="E116" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="H116" s="7" t="n">
+      <c r="F116" s="6" t="n">
         <v>140000000</v>
       </c>
-      <c r="I116" s="7" t="n">
+      <c r="G116" s="6" t="n">
         <v>1540000000</v>
       </c>
-      <c r="J116" s="6" t="inlineStr"/>
-      <c r="K116" s="6" t="inlineStr"/>
-      <c r="L116" s="7" t="n">
+      <c r="H116" s="7" t="inlineStr"/>
+      <c r="I116" s="7" t="inlineStr"/>
+      <c r="J116" s="6" t="n">
         <v>140000000</v>
       </c>
-      <c r="M116" s="7" t="n">
+      <c r="K116" s="6" t="n">
         <v>1540000000</v>
       </c>
-      <c r="N116" s="7" t="n">
+      <c r="L116" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O116" s="6" t="inlineStr"/>
-      <c r="P116" s="6" t="inlineStr">
-        <is>
-          <t>5.30.10.356.VIE.00.000 | Mua bổ sung để duy trì dự phòng, đáp ứng dự phòng thay thế cho các CSU | STT số 92 theo Quyết định số 1274/QĐ-EVN</t>
+      <c r="M116" s="7" t="inlineStr">
+        <is>
+          <t>4. Mua Sắm Công e-GP</t>
         </is>
       </c>
     </row>
